--- a/docs/reports/內在價值報告_20260916.xlsx
+++ b/docs/reports/內在價值報告_20260916.xlsx
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>24.46</v>
+        <v>24.76</v>
       </c>
       <c r="E2" s="3" t="inlineStr"/>
       <c r="F2" s="2" t="inlineStr">
@@ -832,22 +832,22 @@
       </c>
       <c r="H2" s="3" t="inlineStr"/>
       <c r="I2" s="4" t="n">
-        <v>71.7371</v>
+        <v>71.7338</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>41.3365</v>
+        <v>41.3348</v>
       </c>
       <c r="K2" s="4" t="n">
         <v>67.77670000000001</v>
       </c>
       <c r="L2" s="5" t="n">
-        <v>-65.90000000000001</v>
+        <v>-65.5</v>
       </c>
       <c r="M2" s="5" t="n">
         <v>25</v>
       </c>
       <c r="N2" s="4" t="n">
-        <v>53.8028</v>
+        <v>53.8004</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
       </c>
       <c r="AE2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AF2" s="3" t="inlineStr">
@@ -939,7 +939,7 @@
         </is>
       </c>
       <c r="D3" s="4" t="n">
-        <v>3.295</v>
+        <v>3.325</v>
       </c>
       <c r="E3" s="3" t="inlineStr"/>
       <c r="F3" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
         <v>11.2318</v>
       </c>
       <c r="L3" s="5" t="n">
-        <v>-75.09999999999999</v>
+        <v>-74.90000000000001</v>
       </c>
       <c r="M3" s="5" t="n">
         <v>25</v>
@@ -1035,7 +1035,7 @@
       </c>
       <c r="AE3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AF3" s="3" t="inlineStr">
@@ -1061,7 +1061,7 @@
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>9.91</v>
+        <v>9.994999999999999</v>
       </c>
       <c r="E4" s="3" t="inlineStr"/>
       <c r="F4" s="2" t="inlineStr">
@@ -1076,22 +1076,22 @@
       </c>
       <c r="H4" s="3" t="inlineStr"/>
       <c r="I4" s="4" t="n">
-        <v>22.9966</v>
+        <v>22.9934</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>14.8296</v>
+        <v>14.8151</v>
       </c>
       <c r="K4" s="4" t="n">
         <v>15.5519</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>-56.9</v>
+        <v>-56.5</v>
       </c>
       <c r="M4" s="5" t="n">
         <v>25</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>17.2474</v>
+        <v>17.2451</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
       </c>
       <c r="AE4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AF4" s="3" t="inlineStr">
@@ -1183,7 +1183,7 @@
         </is>
       </c>
       <c r="D5" s="4" t="n">
-        <v>38.61</v>
+        <v>38.23</v>
       </c>
       <c r="E5" s="3" t="inlineStr"/>
       <c r="F5" s="2" t="inlineStr">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="H5" s="3" t="inlineStr"/>
       <c r="I5" s="4" t="n">
-        <v>142.5253</v>
+        <v>142.5472</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>55.8024</v>
@@ -1207,13 +1207,13 @@
         <v>151.0522</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>-72.90000000000001</v>
+        <v>-73.2</v>
       </c>
       <c r="M5" s="5" t="n">
         <v>25</v>
       </c>
       <c r="N5" s="4" t="n">
-        <v>106.8939</v>
+        <v>106.9104</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="AE5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AF5" s="3" t="inlineStr"/>
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="D7" s="4" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="E7" s="3" t="inlineStr"/>
       <c r="F7" s="2" t="inlineStr">
@@ -1438,22 +1438,22 @@
       </c>
       <c r="H7" s="3" t="inlineStr"/>
       <c r="I7" s="4" t="n">
-        <v>3.8023</v>
+        <v>3.8031</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>2.2076</v>
+        <v>2.2079</v>
       </c>
       <c r="K7" s="4" t="n">
         <v>2.9007</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>-66.59999999999999</v>
+        <v>-67.09999999999999</v>
       </c>
       <c r="M7" s="5" t="n">
         <v>25</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>2.8517</v>
+        <v>2.8523</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
       </c>
       <c r="AE7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AF7" s="3" t="inlineStr">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>51.45</v>
+        <v>51.25</v>
       </c>
       <c r="E8" s="3" t="inlineStr"/>
       <c r="F8" s="2" t="inlineStr">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="AE8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AF8" s="3" t="inlineStr">
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="D9" s="4" t="n">
-        <v>18.76</v>
+        <v>18.78</v>
       </c>
       <c r="E9" s="3" t="inlineStr"/>
       <c r="F9" s="2" t="inlineStr">
@@ -1689,7 +1689,7 @@
         <v>62.7</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>-64.90000000000001</v>
+        <v>-64.8</v>
       </c>
       <c r="M9" s="5" t="n">
         <v>25</v>
@@ -1761,7 +1761,7 @@
       </c>
       <c r="AE9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AF9" s="3" t="inlineStr"/>
@@ -1898,21 +1898,21 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>00939</t>
+          <t>00386</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>建设银行</t>
+          <t>中国石油化工股份</t>
         </is>
       </c>
       <c r="D11" s="4" t="n">
-        <v>9.654999999999999</v>
+        <v>4.58</v>
       </c>
       <c r="E11" s="3" t="inlineStr"/>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>financial</t>
+          <t>mature</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1922,22 +1922,22 @@
       </c>
       <c r="H11" s="3" t="inlineStr"/>
       <c r="I11" s="4" t="n">
-        <v>130.7854</v>
+        <v>9.313599999999999</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>7.1079</v>
+        <v>3.5349</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>20.1692</v>
+        <v>6.2714</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>-92.59999999999999</v>
+        <v>-50.8</v>
       </c>
       <c r="M11" s="5" t="n">
         <v>25</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>98.0891</v>
+        <v>6.9852</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>非常便宜</t>
+          <t>便宜</t>
         </is>
       </c>
       <c r="R11" s="2" t="n">
@@ -1963,31 +1963,33 @@
         </is>
       </c>
       <c r="T11" s="2" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="U11" s="2" t="n">
         <v>4.5</v>
       </c>
-      <c r="U11" s="2" t="n">
-        <v>5.5</v>
-      </c>
       <c r="V11" s="2" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="W11" s="2" t="n">
-        <v>87.40000000000001</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t>連續十年獲利、ROE穩定約9%，但成長溫和、槓桿極高</t>
+          <t>獲利極薄、營收衰退，但現金流穩健且連續派息</t>
         </is>
       </c>
       <c r="Y11" s="5" t="n">
-        <v>9.1</v>
+        <v>4.2</v>
       </c>
       <c r="Z11" s="5" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="AA11" s="5" t="inlineStr"/>
+        <v>3.5</v>
+      </c>
+      <c r="AA11" s="5" t="n">
+        <v>23.5</v>
+      </c>
       <c r="AB11" s="5" t="n">
-        <v>91.90000000000001</v>
+        <v>54.4</v>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
@@ -2001,12 +2003,12 @@
       </c>
       <c r="AE11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AF11" s="3" t="inlineStr">
         <is>
-          <t>行情總股本(261,600,381,459)與財報EPS反推(2,818,008,461,538)差異&gt;25%，已改用反推值 / 缺關鍵科目：revenue,cash,total_debt,current_assets,current_li</t>
+          <t>缺關鍵科目：capex / 報表幣別 CNY → 交易幣別 HKD，匯率 1.1641</t>
         </is>
       </c>
     </row>
@@ -2018,16 +2020,16 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>01398</t>
+          <t>00939</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>工商银行</t>
+          <t>建设银行</t>
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>7.495</v>
+        <v>9.625</v>
       </c>
       <c r="E12" s="3" t="inlineStr"/>
       <c r="F12" s="2" t="inlineStr">
@@ -2042,22 +2044,22 @@
       </c>
       <c r="H12" s="3" t="inlineStr"/>
       <c r="I12" s="4" t="n">
-        <v>98.4873</v>
+        <v>130.7854</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>5.5194</v>
+        <v>7.1079</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>13.1093</v>
+        <v>20.1692</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>-92.40000000000001</v>
+        <v>-92.59999999999999</v>
       </c>
       <c r="M12" s="5" t="n">
         <v>25</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>73.8655</v>
+        <v>98.0891</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -2075,39 +2077,39 @@
         </is>
       </c>
       <c r="R12" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>★★☆☆☆</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="n">
         <v>4.5</v>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>★★☆☆☆</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="n">
-        <v>4</v>
       </c>
       <c r="U12" s="2" t="n">
         <v>5.5</v>
       </c>
       <c r="V12" s="2" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="W12" s="2" t="n">
-        <v>87.8</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t>十年穩定獲利派息，ROE約8.7%，成長溫和但財務體質穩健</t>
+          <t>連續十年獲利、ROE穩定約9%，但成長溫和、槓桿極高</t>
         </is>
       </c>
       <c r="Y12" s="5" t="n">
-        <v>8.6</v>
+        <v>9.1</v>
       </c>
       <c r="Z12" s="5" t="n">
-        <v>8.699999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="AA12" s="5" t="inlineStr"/>
       <c r="AB12" s="5" t="n">
-        <v>92.40000000000001</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
@@ -2121,12 +2123,12 @@
       </c>
       <c r="AE12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AF12" s="3" t="inlineStr">
         <is>
-          <t>行情總股本(356,406,257,089)與財報EPS反推(4,244,259,000,000)差異&gt;25%，已改用反推值 / 缺關鍵科目：revenue,cash,total_debt,current_assets,current_li</t>
+          <t>行情總股本(261,600,381,459)與財報EPS反推(2,818,008,461,538)差異&gt;25%，已改用反推值 / 缺關鍵科目：revenue,cash,total_debt,current_assets,current_li</t>
         </is>
       </c>
     </row>
@@ -2138,16 +2140,16 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>02318</t>
+          <t>01398</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>中国平安</t>
+          <t>工商银行</t>
         </is>
       </c>
       <c r="D13" s="4" t="n">
-        <v>53.5</v>
+        <v>7.505</v>
       </c>
       <c r="E13" s="3" t="inlineStr"/>
       <c r="F13" s="2" t="inlineStr">
@@ -2162,13 +2164,13 @@
       </c>
       <c r="H13" s="3" t="inlineStr"/>
       <c r="I13" s="4" t="n">
-        <v>699.6943</v>
+        <v>98.4873</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>44.8893</v>
+        <v>5.5194</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>136.5623</v>
+        <v>13.1093</v>
       </c>
       <c r="L13" s="5" t="n">
         <v>-92.40000000000001</v>
@@ -2177,7 +2179,7 @@
         <v>25</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>524.7707</v>
+        <v>73.8655</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -2203,193 +2205,191 @@
         </is>
       </c>
       <c r="T13" s="2" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="U13" s="2" t="n">
         <v>5.5</v>
       </c>
       <c r="V13" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="W13" s="2" t="n">
+        <v>87.8</v>
+      </c>
+      <c r="X13" s="3" t="inlineStr">
+        <is>
+          <t>十年穩定獲利派息，ROE約8.7%，成長溫和但財務體質穩健</t>
+        </is>
+      </c>
+      <c r="Y13" s="5" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="Z13" s="5" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="AA13" s="5" t="inlineStr"/>
+      <c r="AB13" s="5" t="n">
+        <v>92.40000000000001</v>
+      </c>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="AD13" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AE13" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AF13" s="3" t="inlineStr">
+        <is>
+          <t>行情總股本(356,406,257,089)與財報EPS反推(4,244,259,000,000)差異&gt;25%，已改用反推值 / 缺關鍵科目：revenue,cash,total_debt,current_assets,current_li</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>02318</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>中国平安</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>53.05</v>
+      </c>
+      <c r="E14" s="3" t="inlineStr"/>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>financial</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr"/>
+      <c r="I14" s="4" t="n">
+        <v>699.6943</v>
+      </c>
+      <c r="J14" s="4" t="n">
+        <v>44.8893</v>
+      </c>
+      <c r="K14" s="4" t="n">
+        <v>136.5623</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>-92.40000000000001</v>
+      </c>
+      <c r="M14" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="N14" s="4" t="n">
+        <v>524.7707</v>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P14" s="6" t="inlineStr">
+        <is>
+          <t>非常便宜</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>非常便宜</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>★★☆☆☆</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U14" s="2" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="V14" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="W13" s="2" t="n">
+      <c r="W14" s="2" t="n">
         <v>91.2</v>
       </c>
-      <c r="X13" s="3" t="inlineStr">
+      <c r="X14" s="3" t="inlineStr">
         <is>
           <t>現金流充沛但獲利波動大、槓桿高，防禦檢查僅過2/7</t>
         </is>
       </c>
-      <c r="Y13" s="5" t="n">
+      <c r="Y14" s="5" t="n">
         <v>15.5</v>
       </c>
-      <c r="Z13" s="5" t="inlineStr"/>
-      <c r="AA13" s="5" t="n">
+      <c r="Z14" s="5" t="inlineStr"/>
+      <c r="AA14" s="5" t="n">
         <v>-178.5</v>
       </c>
-      <c r="AB13" s="5" t="n">
+      <c r="AB14" s="5" t="n">
         <v>89.8</v>
       </c>
-      <c r="AC13" s="2" t="inlineStr">
+      <c r="AC14" s="2" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="AD13" s="2" t="inlineStr">
+      <c r="AD14" s="2" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="AE13" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="AF13" s="3" t="inlineStr">
+      <c r="AE14" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AF14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">行情總股本(18,107,641,995)與財報EPS反推(130,262,890,625)差異&gt;25%，已改用反推值 / 缺關鍵科目：total_debt,current_assets,current_liab / 報表幣別 CNY → </t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>HK</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>03998</t>
-        </is>
-      </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>波司登</t>
-        </is>
-      </c>
-      <c r="D14" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="E14" s="8" t="inlineStr"/>
-      <c r="F14" s="7" t="inlineStr">
-        <is>
-          <t>growth</t>
-        </is>
-      </c>
-      <c r="G14" s="7" t="inlineStr">
-        <is>
-          <t>HKD</t>
-        </is>
-      </c>
-      <c r="H14" s="8" t="inlineStr"/>
-      <c r="I14" s="9" t="n">
-        <v>8.3028</v>
-      </c>
-      <c r="J14" s="9" t="n">
-        <v>3.8731</v>
-      </c>
-      <c r="K14" s="9" t="n">
-        <v>7.0634</v>
-      </c>
-      <c r="L14" s="10" t="n">
-        <v>-48.2</v>
-      </c>
-      <c r="M14" s="10" t="n">
-        <v>25</v>
-      </c>
-      <c r="N14" s="9" t="n">
-        <v>6.2271</v>
-      </c>
-      <c r="O14" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P14" s="11" t="inlineStr">
-        <is>
-          <t>便宜</t>
-        </is>
-      </c>
-      <c r="Q14" s="7" t="inlineStr">
-        <is>
-          <t>便宜</t>
-        </is>
-      </c>
-      <c r="R14" s="7" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="S14" s="7" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-      <c r="T14" s="7" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="U14" s="7" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="V14" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="W14" s="7" t="n">
-        <v>93.09999999999999</v>
-      </c>
-      <c r="X14" s="8" t="inlineStr">
-        <is>
-          <t>連續十年獲利、ROIC達28%，現金流充沛且負債極低</t>
-        </is>
-      </c>
-      <c r="Y14" s="10" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="Z14" s="10" t="n">
-        <v>28.2</v>
-      </c>
-      <c r="AA14" s="10" t="n">
-        <v>57.2</v>
-      </c>
-      <c r="AB14" s="10" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="AC14" s="7" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="AD14" s="7" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="AE14" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="AF14" s="8" t="inlineStr">
-        <is>
-          <t>報表幣別 CNY → 交易幣別 HKD，匯率 1.1641</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>603605</t>
+          <t>03998</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>珀莱雅</t>
+          <t>波司登</t>
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>56.71</v>
+        <v>4.215</v>
       </c>
       <c r="E15" s="8" t="inlineStr"/>
       <c r="F15" s="7" t="inlineStr">
@@ -2399,27 +2399,27 @@
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>CNY</t>
+          <t>HKD</t>
         </is>
       </c>
       <c r="H15" s="8" t="inlineStr"/>
       <c r="I15" s="9" t="n">
-        <v>100.9416</v>
+        <v>8.303100000000001</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>56.4547</v>
+        <v>3.8731</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>94.1225</v>
+        <v>7.0636</v>
       </c>
       <c r="L15" s="10" t="n">
-        <v>-43.8</v>
+        <v>-49.2</v>
       </c>
       <c r="M15" s="10" t="n">
         <v>25</v>
       </c>
       <c r="N15" s="9" t="n">
-        <v>75.7062</v>
+        <v>6.2274</v>
       </c>
       <c r="O15" s="7" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         </is>
       </c>
       <c r="R15" s="7" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="S15" s="7" t="inlineStr">
         <is>
@@ -2445,99 +2445,103 @@
         </is>
       </c>
       <c r="T15" s="7" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="U15" s="7" t="n">
         <v>8.5</v>
       </c>
       <c r="V15" s="7" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="W15" s="7" t="n">
-        <v>93.3</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="X15" s="8" t="inlineStr">
         <is>
-          <t>ROIC 83.9%、淨現金44億、自由現金流率15.7%，財務體質極強</t>
+          <t>連續十年獲利、ROIC達28%，現金流充沛且負債極低</t>
         </is>
       </c>
       <c r="Y15" s="10" t="n">
-        <v>28.5</v>
+        <v>21.9</v>
       </c>
       <c r="Z15" s="10" t="n">
-        <v>83.90000000000001</v>
+        <v>28.2</v>
       </c>
       <c r="AA15" s="10" t="n">
-        <v>73.7</v>
+        <v>57.2</v>
       </c>
       <c r="AB15" s="10" t="n">
-        <v>33.7</v>
+        <v>37.5</v>
       </c>
       <c r="AC15" s="7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="AD15" s="7" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="AE15" s="7" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="AF15" s="8" t="inlineStr"/>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AF15" s="8" t="inlineStr">
+        <is>
+          <t>報表幣別 CNY → 交易幣別 HKD，匯率 1.1641</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>09999</t>
+          <t>603605</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>网易</t>
+          <t>珀莱雅</t>
         </is>
       </c>
       <c r="D16" s="9" t="n">
-        <v>187.2</v>
+        <v>56</v>
       </c>
       <c r="E16" s="8" t="inlineStr"/>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>mature</t>
+          <t>growth</t>
         </is>
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
-          <t>HKD</t>
+          <t>CNY</t>
         </is>
       </c>
       <c r="H16" s="8" t="inlineStr"/>
       <c r="I16" s="9" t="n">
-        <v>300.1348</v>
+        <v>100.9447</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>153.3619</v>
+        <v>56.4713</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>378.6999</v>
+        <v>94.1225</v>
       </c>
       <c r="L16" s="10" t="n">
-        <v>-37.6</v>
+        <v>-44.5</v>
       </c>
       <c r="M16" s="10" t="n">
         <v>25</v>
       </c>
       <c r="N16" s="9" t="n">
-        <v>225.1011</v>
+        <v>75.7086</v>
       </c>
       <c r="O16" s="7" t="inlineStr">
         <is>
@@ -2555,7 +2559,7 @@
         </is>
       </c>
       <c r="R16" s="7" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="S16" s="7" t="inlineStr">
         <is>
@@ -2563,33 +2567,33 @@
         </is>
       </c>
       <c r="T16" s="7" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="U16" s="7" t="n">
         <v>8.5</v>
       </c>
       <c r="V16" s="7" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="W16" s="7" t="n">
-        <v>84.8</v>
+        <v>93.3</v>
       </c>
       <c r="X16" s="8" t="inlineStr">
         <is>
-          <t>淨現金充裕、自由現金流率逾42%，財務體質極穩健</t>
+          <t>ROIC 83.9%、淨現金44億、自由現金流率15.7%，財務體質極強</t>
         </is>
       </c>
       <c r="Y16" s="10" t="n">
-        <v>19.5</v>
+        <v>28.5</v>
       </c>
       <c r="Z16" s="10" t="n">
-        <v>777.9</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="AA16" s="10" t="n">
-        <v>67.2</v>
+        <v>73.7</v>
       </c>
       <c r="AB16" s="10" t="n">
-        <v>26.1</v>
+        <v>33.7</v>
       </c>
       <c r="AC16" s="7" t="inlineStr">
         <is>
@@ -2603,63 +2607,59 @@
       </c>
       <c r="AE16" s="7" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="AF16" s="8" t="inlineStr">
-        <is>
-          <t>報表幣別 CNY → 交易幣別 HKD，匯率 1.1641</t>
-        </is>
-      </c>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AF16" s="8" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>300274</t>
+          <t>09999</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>阳光电源</t>
+          <t>网易</t>
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>84.58</v>
+        <v>183.8</v>
       </c>
       <c r="E17" s="8" t="inlineStr"/>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>growth</t>
+          <t>mature</t>
         </is>
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>CNY</t>
+          <t>HKD</t>
         </is>
       </c>
       <c r="H17" s="8" t="inlineStr"/>
       <c r="I17" s="9" t="n">
-        <v>126.3725</v>
+        <v>300.141</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>67.53319999999999</v>
+        <v>153.3892</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>166.782</v>
+        <v>378.6999</v>
       </c>
       <c r="L17" s="10" t="n">
-        <v>-33.1</v>
+        <v>-38.8</v>
       </c>
       <c r="M17" s="10" t="n">
         <v>25</v>
       </c>
       <c r="N17" s="9" t="n">
-        <v>94.7794</v>
+        <v>225.1058</v>
       </c>
       <c r="O17" s="7" t="inlineStr">
         <is>
@@ -2685,33 +2685,33 @@
         </is>
       </c>
       <c r="T17" s="7" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="U17" s="7" t="n">
         <v>8.5</v>
       </c>
       <c r="V17" s="7" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="W17" s="7" t="n">
-        <v>85.90000000000001</v>
+        <v>84.8</v>
       </c>
       <c r="X17" s="8" t="inlineStr">
         <is>
-          <t>ROIC逾41%、淨現金充裕，連續十年獲利且現金流強勁</t>
+          <t>淨現金充裕、自由現金流率逾42%，財務體質極穩健</t>
         </is>
       </c>
       <c r="Y17" s="10" t="n">
-        <v>21.7</v>
+        <v>19.5</v>
       </c>
       <c r="Z17" s="10" t="n">
-        <v>41.1</v>
+        <v>777.9</v>
       </c>
       <c r="AA17" s="10" t="n">
-        <v>32</v>
+        <v>67.2</v>
       </c>
       <c r="AB17" s="10" t="n">
-        <v>58.2</v>
+        <v>26.1</v>
       </c>
       <c r="AC17" s="7" t="inlineStr">
         <is>
@@ -2725,59 +2725,63 @@
       </c>
       <c r="AE17" s="7" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="AF17" s="8" t="inlineStr"/>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AF17" s="8" t="inlineStr">
+        <is>
+          <t>報表幣別 CNY → 交易幣別 HKD，匯率 1.1641</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>00700</t>
+          <t>300274</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>腾讯控股</t>
+          <t>阳光电源</t>
         </is>
       </c>
       <c r="D18" s="9" t="n">
-        <v>437.8</v>
+        <v>83.75</v>
       </c>
       <c r="E18" s="8" t="inlineStr"/>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>mature</t>
+          <t>growth</t>
         </is>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>HKD</t>
+          <t>CNY</t>
         </is>
       </c>
       <c r="H18" s="8" t="inlineStr"/>
       <c r="I18" s="9" t="n">
-        <v>659.799</v>
+        <v>126.3758</v>
       </c>
       <c r="J18" s="9" t="n">
-        <v>459.3207</v>
+        <v>67.5508</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>609.7471</v>
+        <v>166.782</v>
       </c>
       <c r="L18" s="10" t="n">
-        <v>-33.6</v>
+        <v>-33.7</v>
       </c>
       <c r="M18" s="10" t="n">
         <v>25</v>
       </c>
       <c r="N18" s="9" t="n">
-        <v>494.8493</v>
+        <v>94.7818</v>
       </c>
       <c r="O18" s="7" t="inlineStr">
         <is>
@@ -2795,7 +2799,7 @@
         </is>
       </c>
       <c r="R18" s="7" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="S18" s="7" t="inlineStr">
         <is>
@@ -2812,24 +2816,24 @@
         <v>7.5</v>
       </c>
       <c r="W18" s="7" t="n">
-        <v>95.90000000000001</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="X18" s="8" t="inlineStr">
         <is>
-          <t>高毛利、ROE逾20%、自由現金流充沛的成熟平台企業</t>
+          <t>ROIC逾41%、淨現金充裕，連續十年獲利且現金流強勁</t>
         </is>
       </c>
       <c r="Y18" s="10" t="n">
-        <v>20.7</v>
+        <v>21.7</v>
       </c>
       <c r="Z18" s="10" t="n">
-        <v>18.7</v>
+        <v>41.1</v>
       </c>
       <c r="AA18" s="10" t="n">
-        <v>57.4</v>
+        <v>32</v>
       </c>
       <c r="AB18" s="10" t="n">
-        <v>43.4</v>
+        <v>58.2</v>
       </c>
       <c r="AC18" s="7" t="inlineStr">
         <is>
@@ -2843,14 +2847,10 @@
       </c>
       <c r="AE18" s="7" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="AF18" s="8" t="inlineStr">
-        <is>
-          <t>報表幣別 CNY → 交易幣別 HKD，匯率 1.1641</t>
-        </is>
-      </c>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AF18" s="8" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
@@ -2860,16 +2860,16 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>00762</t>
+          <t>00700</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>中国联通</t>
+          <t>腾讯控股</t>
         </is>
       </c>
       <c r="D19" s="9" t="n">
-        <v>5.91</v>
+        <v>434.2</v>
       </c>
       <c r="E19" s="8" t="inlineStr"/>
       <c r="F19" s="7" t="inlineStr">
@@ -2884,22 +2884,22 @@
       </c>
       <c r="H19" s="8" t="inlineStr"/>
       <c r="I19" s="9" t="n">
-        <v>11.4397</v>
+        <v>660.375</v>
       </c>
       <c r="J19" s="9" t="n">
-        <v>8.3782</v>
+        <v>459.7468</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>12.385</v>
+        <v>610.2885</v>
       </c>
       <c r="L19" s="10" t="n">
-        <v>-48.3</v>
+        <v>-34.2</v>
       </c>
       <c r="M19" s="10" t="n">
         <v>25</v>
       </c>
       <c r="N19" s="9" t="n">
-        <v>8.579800000000001</v>
+        <v>495.2813</v>
       </c>
       <c r="O19" s="7" t="inlineStr">
         <is>
@@ -2925,33 +2925,33 @@
         </is>
       </c>
       <c r="T19" s="7" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="U19" s="7" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="V19" s="7" t="n">
         <v>7.5</v>
       </c>
-      <c r="U19" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="V19" s="7" t="n">
-        <v>6.5</v>
-      </c>
       <c r="W19" s="7" t="n">
-        <v>93.7</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="X19" s="8" t="inlineStr">
         <is>
-          <t>連續十年獲利、淨現金穩健，惟ROE僅4.2%反映重資產低回報本質</t>
+          <t>高毛利、ROE逾20%、自由現金流充沛的成熟平台企業</t>
         </is>
       </c>
       <c r="Y19" s="10" t="n">
-        <v>4.2</v>
+        <v>20.7</v>
       </c>
       <c r="Z19" s="10" t="n">
-        <v>3.4</v>
+        <v>18.7</v>
       </c>
       <c r="AA19" s="10" t="n">
-        <v>69</v>
+        <v>57.4</v>
       </c>
       <c r="AB19" s="10" t="n">
-        <v>44.4</v>
+        <v>43.4</v>
       </c>
       <c r="AC19" s="7" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
       </c>
       <c r="AE19" s="7" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AF19" s="8" t="inlineStr">
@@ -2982,16 +2982,16 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>02688</t>
+          <t>00762</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>新奥能源</t>
+          <t>中国联通</t>
         </is>
       </c>
       <c r="D20" s="9" t="n">
-        <v>48.72</v>
+        <v>5.78</v>
       </c>
       <c r="E20" s="8" t="inlineStr"/>
       <c r="F20" s="7" t="inlineStr">
@@ -3006,22 +3006,22 @@
       </c>
       <c r="H20" s="8" t="inlineStr"/>
       <c r="I20" s="9" t="n">
-        <v>84.23309999999999</v>
+        <v>11.4444</v>
       </c>
       <c r="J20" s="9" t="n">
-        <v>83.2593</v>
+        <v>8.3788</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>106.0289</v>
+        <v>12.385</v>
       </c>
       <c r="L20" s="10" t="n">
-        <v>-42.2</v>
+        <v>-49.5</v>
       </c>
       <c r="M20" s="10" t="n">
         <v>25</v>
       </c>
       <c r="N20" s="9" t="n">
-        <v>63.1748</v>
+        <v>8.583299999999999</v>
       </c>
       <c r="O20" s="7" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         </is>
       </c>
       <c r="R20" s="7" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="S20" s="7" t="inlineStr">
         <is>
@@ -3047,33 +3047,33 @@
         </is>
       </c>
       <c r="T20" s="7" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="U20" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="V20" s="7" t="n">
         <v>6.5</v>
       </c>
-      <c r="U20" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="V20" s="7" t="n">
-        <v>7</v>
-      </c>
       <c r="W20" s="7" t="n">
-        <v>93</v>
+        <v>93.7</v>
       </c>
       <c r="X20" s="8" t="inlineStr">
         <is>
-          <t>獲利穩定現金流充沛，成長趨緩、流動性偏緊</t>
+          <t>連續十年獲利、淨現金穩健，惟ROE僅4.2%反映重資產低回報本質</t>
         </is>
       </c>
       <c r="Y20" s="10" t="n">
-        <v>12.8</v>
+        <v>4.2</v>
       </c>
       <c r="Z20" s="10" t="n">
-        <v>11.4</v>
+        <v>3.4</v>
       </c>
       <c r="AA20" s="10" t="n">
-        <v>11.9</v>
+        <v>69</v>
       </c>
       <c r="AB20" s="10" t="n">
-        <v>48.6</v>
+        <v>44.4</v>
       </c>
       <c r="AC20" s="7" t="inlineStr">
         <is>
@@ -3087,12 +3087,12 @@
       </c>
       <c r="AE20" s="7" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AF20" s="8" t="inlineStr">
         <is>
-          <t>缺關鍵科目：d_and_a / 報表幣別 CNY → 交易幣別 HKD，匯率 1.1641</t>
+          <t>報表幣別 CNY → 交易幣別 HKD，匯率 1.1641</t>
         </is>
       </c>
     </row>
@@ -3104,16 +3104,16 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>09961</t>
+          <t>02688</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>携程集团-S</t>
+          <t>新奥能源</t>
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>308</v>
+        <v>50.4</v>
       </c>
       <c r="E21" s="8" t="inlineStr"/>
       <c r="F21" s="7" t="inlineStr">
@@ -3128,22 +3128,22 @@
       </c>
       <c r="H21" s="8" t="inlineStr"/>
       <c r="I21" s="9" t="n">
-        <v>430.8789</v>
+        <v>84.1023</v>
       </c>
       <c r="J21" s="9" t="n">
-        <v>252.0972</v>
+        <v>83.2593</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>428.4491</v>
+        <v>106.0289</v>
       </c>
       <c r="L21" s="10" t="n">
-        <v>-28.5</v>
+        <v>-40.1</v>
       </c>
       <c r="M21" s="10" t="n">
         <v>25</v>
       </c>
       <c r="N21" s="9" t="n">
-        <v>323.1591</v>
+        <v>63.0767</v>
       </c>
       <c r="O21" s="7" t="inlineStr">
         <is>
@@ -3161,41 +3161,41 @@
         </is>
       </c>
       <c r="R21" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="S21" s="7" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+      <c r="T21" s="7" t="n">
         <v>6.5</v>
       </c>
-      <c r="S21" s="7" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-      <c r="T21" s="7" t="n">
-        <v>5</v>
-      </c>
       <c r="U21" s="7" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="V21" s="7" t="n">
         <v>7</v>
       </c>
       <c r="W21" s="7" t="n">
-        <v>89.2</v>
+        <v>93</v>
       </c>
       <c r="X21" s="8" t="inlineStr">
         <is>
-          <t>毛利率近90%、淨現金充裕，但ROE穩定度為零、淨利率含非營業收益</t>
+          <t>獲利穩定現金流充沛，成長趨緩、流動性偏緊</t>
         </is>
       </c>
       <c r="Y21" s="10" t="n">
-        <v>19.1</v>
+        <v>12.8</v>
       </c>
       <c r="Z21" s="10" t="n">
-        <v>11.7</v>
+        <v>11.4</v>
       </c>
       <c r="AA21" s="10" t="n">
-        <v>89.7</v>
+        <v>11.9</v>
       </c>
       <c r="AB21" s="10" t="n">
-        <v>36.7</v>
+        <v>48.6</v>
       </c>
       <c r="AC21" s="7" t="inlineStr">
         <is>
@@ -3204,17 +3204,17 @@
       </c>
       <c r="AD21" s="7" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="AE21" s="7" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AF21" s="8" t="inlineStr">
         <is>
-          <t>報表幣別 CNY → 交易幣別 HKD，匯率 1.1641</t>
+          <t>缺關鍵科目：d_and_a / 報表幣別 CNY → 交易幣別 HKD，匯率 1.1641</t>
         </is>
       </c>
     </row>
@@ -3226,16 +3226,16 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>00386</t>
+          <t>09961</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>中国石油化工股份</t>
+          <t>携程集团-S</t>
         </is>
       </c>
       <c r="D22" s="9" t="n">
-        <v>4.67</v>
+        <v>303.6</v>
       </c>
       <c r="E22" s="8" t="inlineStr"/>
       <c r="F22" s="7" t="inlineStr">
@@ -3250,22 +3250,22 @@
       </c>
       <c r="H22" s="8" t="inlineStr"/>
       <c r="I22" s="9" t="n">
-        <v>9.299799999999999</v>
+        <v>430.9458</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>3.5319</v>
+        <v>252.0972</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>6.2659</v>
+        <v>428.4491</v>
       </c>
       <c r="L22" s="10" t="n">
-        <v>-49.8</v>
+        <v>-29.6</v>
       </c>
       <c r="M22" s="10" t="n">
         <v>25</v>
       </c>
       <c r="N22" s="9" t="n">
-        <v>6.9748</v>
+        <v>323.2093</v>
       </c>
       <c r="O22" s="7" t="inlineStr">
         <is>
@@ -3283,41 +3283,41 @@
         </is>
       </c>
       <c r="R22" s="7" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="S22" s="7" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+      <c r="T22" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="S22" s="7" t="inlineStr">
-        <is>
-          <t>★★☆☆☆</t>
-        </is>
-      </c>
-      <c r="T22" s="7" t="n">
-        <v>5.5</v>
-      </c>
       <c r="U22" s="7" t="n">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="V22" s="7" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="W22" s="7" t="n">
-        <v>92.59999999999999</v>
+        <v>89.2</v>
       </c>
       <c r="X22" s="8" t="inlineStr">
         <is>
-          <t>獲利極薄、營收衰退，但現金流穩健且連續派息</t>
+          <t>毛利率近90%、淨現金充裕，但ROE穩定度為零、淨利率含非營業收益</t>
         </is>
       </c>
       <c r="Y22" s="10" t="n">
-        <v>4.2</v>
+        <v>19.1</v>
       </c>
       <c r="Z22" s="10" t="n">
-        <v>3.5</v>
+        <v>11.7</v>
       </c>
       <c r="AA22" s="10" t="n">
-        <v>23.5</v>
+        <v>89.7</v>
       </c>
       <c r="AB22" s="10" t="n">
-        <v>54.4</v>
+        <v>36.7</v>
       </c>
       <c r="AC22" s="7" t="inlineStr">
         <is>
@@ -3326,17 +3326,17 @@
       </c>
       <c r="AD22" s="7" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="AE22" s="7" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AF22" s="8" t="inlineStr">
         <is>
-          <t>缺關鍵科目：capex / 報表幣別 CNY → 交易幣別 HKD，匯率 1.1641</t>
+          <t>報表幣別 CNY → 交易幣別 HKD，匯率 1.1641</t>
         </is>
       </c>
     </row>
@@ -3479,7 +3479,7 @@
         </is>
       </c>
       <c r="D24" s="14" t="n">
-        <v>1276.81</v>
+        <v>1264.75</v>
       </c>
       <c r="E24" s="13" t="inlineStr"/>
       <c r="F24" s="12" t="inlineStr">
@@ -3494,22 +3494,22 @@
       </c>
       <c r="H24" s="13" t="inlineStr"/>
       <c r="I24" s="14" t="n">
-        <v>1186.8346</v>
+        <v>1186.8348</v>
       </c>
       <c r="J24" s="14" t="n">
-        <v>838.7845</v>
+        <v>838.7854</v>
       </c>
       <c r="K24" s="14" t="n">
         <v>2058.441</v>
       </c>
       <c r="L24" s="15" t="n">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="M24" s="15" t="n">
         <v>25</v>
       </c>
       <c r="N24" s="14" t="n">
-        <v>890.1259</v>
+        <v>890.1261</v>
       </c>
       <c r="O24" s="12" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
       </c>
       <c r="AE24" s="12" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AF24" s="13" t="inlineStr"/>
@@ -3597,7 +3597,7 @@
         </is>
       </c>
       <c r="D25" s="14" t="n">
-        <v>85.59999999999999</v>
+        <v>85.59</v>
       </c>
       <c r="E25" s="13" t="inlineStr"/>
       <c r="F25" s="12" t="inlineStr">
@@ -3612,7 +3612,7 @@
       </c>
       <c r="H25" s="13" t="inlineStr"/>
       <c r="I25" s="14" t="n">
-        <v>113.1287</v>
+        <v>113.1288</v>
       </c>
       <c r="J25" s="14" t="n">
         <v>55.5052</v>
@@ -3627,7 +3627,7 @@
         <v>25</v>
       </c>
       <c r="N25" s="14" t="n">
-        <v>84.84650000000001</v>
+        <v>84.8466</v>
       </c>
       <c r="O25" s="12" t="inlineStr">
         <is>
@@ -3693,7 +3693,7 @@
       </c>
       <c r="AE25" s="12" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AF25" s="13" t="inlineStr">
@@ -3719,7 +3719,7 @@
         </is>
       </c>
       <c r="D26" s="14" t="n">
-        <v>87.89</v>
+        <v>86</v>
       </c>
       <c r="E26" s="13" t="inlineStr"/>
       <c r="F26" s="12" t="inlineStr">
@@ -3734,22 +3734,22 @@
       </c>
       <c r="H26" s="13" t="inlineStr"/>
       <c r="I26" s="14" t="n">
-        <v>107.1602</v>
+        <v>107.1841</v>
       </c>
       <c r="J26" s="14" t="n">
-        <v>68.9901</v>
+        <v>69.0992</v>
       </c>
       <c r="K26" s="14" t="n">
         <v>136.1654</v>
       </c>
       <c r="L26" s="15" t="n">
-        <v>-18</v>
+        <v>-19.8</v>
       </c>
       <c r="M26" s="15" t="n">
         <v>25</v>
       </c>
       <c r="N26" s="14" t="n">
-        <v>80.3702</v>
+        <v>80.38809999999999</v>
       </c>
       <c r="O26" s="12" t="inlineStr">
         <is>
@@ -3815,7 +3815,7 @@
       </c>
       <c r="AE26" s="12" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AF26" s="13" t="inlineStr"/>
@@ -3837,7 +3837,7 @@
         </is>
       </c>
       <c r="D27" s="14" t="n">
-        <v>79.2</v>
+        <v>79.25</v>
       </c>
       <c r="E27" s="13" t="inlineStr"/>
       <c r="F27" s="12" t="inlineStr">
@@ -3852,10 +3852,10 @@
       </c>
       <c r="H27" s="13" t="inlineStr"/>
       <c r="I27" s="14" t="n">
-        <v>89.6084</v>
+        <v>89.608</v>
       </c>
       <c r="J27" s="14" t="n">
-        <v>87.05289999999999</v>
+        <v>87.05110000000001</v>
       </c>
       <c r="K27" s="14" t="n">
         <v>92.48090000000001</v>
@@ -3867,7 +3867,7 @@
         <v>25</v>
       </c>
       <c r="N27" s="14" t="n">
-        <v>67.2063</v>
+        <v>67.206</v>
       </c>
       <c r="O27" s="12" t="inlineStr">
         <is>
@@ -3933,7 +3933,7 @@
       </c>
       <c r="AE27" s="12" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AF27" s="13" t="inlineStr">
@@ -3959,7 +3959,7 @@
         </is>
       </c>
       <c r="D28" s="14" t="n">
-        <v>159.68</v>
+        <v>158.92</v>
       </c>
       <c r="E28" s="13" t="inlineStr"/>
       <c r="F28" s="12" t="inlineStr">
@@ -3974,22 +3974,22 @@
       </c>
       <c r="H28" s="13" t="inlineStr"/>
       <c r="I28" s="14" t="n">
-        <v>200.3015</v>
+        <v>200.3016</v>
       </c>
       <c r="J28" s="14" t="n">
-        <v>116.6307</v>
+        <v>116.6312</v>
       </c>
       <c r="K28" s="14" t="n">
         <v>176.872</v>
       </c>
       <c r="L28" s="15" t="n">
-        <v>-20.3</v>
+        <v>-20.7</v>
       </c>
       <c r="M28" s="15" t="n">
         <v>25</v>
       </c>
       <c r="N28" s="14" t="n">
-        <v>150.2261</v>
+        <v>150.2262</v>
       </c>
       <c r="O28" s="12" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
       </c>
       <c r="AE28" s="12" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AF28" s="13" t="inlineStr"/>
@@ -4077,7 +4077,7 @@
         </is>
       </c>
       <c r="D29" s="14" t="n">
-        <v>9.02</v>
+        <v>8.984999999999999</v>
       </c>
       <c r="E29" s="13" t="inlineStr"/>
       <c r="F29" s="12" t="inlineStr">
@@ -4092,22 +4092,22 @@
       </c>
       <c r="H29" s="13" t="inlineStr"/>
       <c r="I29" s="14" t="n">
-        <v>11.5457</v>
+        <v>11.5478</v>
       </c>
       <c r="J29" s="14" t="n">
-        <v>5.7686</v>
+        <v>5.7784</v>
       </c>
       <c r="K29" s="14" t="n">
         <v>14.7897</v>
       </c>
       <c r="L29" s="15" t="n">
-        <v>-21.9</v>
+        <v>-22.2</v>
       </c>
       <c r="M29" s="15" t="n">
         <v>25</v>
       </c>
       <c r="N29" s="14" t="n">
-        <v>8.6593</v>
+        <v>8.6608</v>
       </c>
       <c r="O29" s="12" t="inlineStr">
         <is>
@@ -4142,7 +4142,7 @@
         <v>5.5</v>
       </c>
       <c r="W29" s="12" t="n">
-        <v>85.90000000000001</v>
+        <v>86</v>
       </c>
       <c r="X29" s="13" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
       </c>
       <c r="AE29" s="12" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AF29" s="13" t="inlineStr">
@@ -4199,7 +4199,7 @@
         </is>
       </c>
       <c r="D30" s="14" t="n">
-        <v>27.16</v>
+        <v>26.04</v>
       </c>
       <c r="E30" s="13" t="inlineStr"/>
       <c r="F30" s="12" t="inlineStr">
@@ -4214,22 +4214,22 @@
       </c>
       <c r="H30" s="13" t="inlineStr"/>
       <c r="I30" s="14" t="n">
-        <v>28.7613</v>
+        <v>28.765</v>
       </c>
       <c r="J30" s="14" t="n">
         <v>18.8996</v>
       </c>
       <c r="K30" s="14" t="n">
-        <v>26.4501</v>
+        <v>26.4515</v>
       </c>
       <c r="L30" s="15" t="n">
-        <v>-5.6</v>
+        <v>-9.5</v>
       </c>
       <c r="M30" s="15" t="n">
         <v>25</v>
       </c>
       <c r="N30" s="14" t="n">
-        <v>21.571</v>
+        <v>21.5738</v>
       </c>
       <c r="O30" s="12" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
       </c>
       <c r="AE30" s="12" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AF30" s="13" t="inlineStr">
@@ -4321,7 +4321,7 @@
         </is>
       </c>
       <c r="D31" s="14" t="n">
-        <v>106.3</v>
+        <v>105.2</v>
       </c>
       <c r="E31" s="13" t="inlineStr"/>
       <c r="F31" s="12" t="inlineStr">
@@ -4336,22 +4336,22 @@
       </c>
       <c r="H31" s="13" t="inlineStr"/>
       <c r="I31" s="14" t="n">
-        <v>136.1812</v>
+        <v>136.1718</v>
       </c>
       <c r="J31" s="14" t="n">
         <v>59.7871</v>
       </c>
       <c r="K31" s="14" t="n">
-        <v>129.2918</v>
+        <v>129.2469</v>
       </c>
       <c r="L31" s="15" t="n">
-        <v>-21.9</v>
+        <v>-22.7</v>
       </c>
       <c r="M31" s="15" t="n">
         <v>25</v>
       </c>
       <c r="N31" s="14" t="n">
-        <v>102.1359</v>
+        <v>102.1288</v>
       </c>
       <c r="O31" s="12" t="inlineStr">
         <is>
@@ -4417,7 +4417,7 @@
       </c>
       <c r="AE31" s="12" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AF31" s="13" t="inlineStr">
@@ -4443,7 +4443,7 @@
         </is>
       </c>
       <c r="D32" s="14" t="n">
-        <v>32.04</v>
+        <v>31.94</v>
       </c>
       <c r="E32" s="13" t="inlineStr"/>
       <c r="F32" s="12" t="inlineStr">
@@ -4461,13 +4461,13 @@
         <v>31.6387</v>
       </c>
       <c r="J32" s="14" t="n">
-        <v>16.8792</v>
+        <v>16.8789</v>
       </c>
       <c r="K32" s="14" t="n">
         <v>19.8445</v>
       </c>
       <c r="L32" s="15" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="M32" s="15" t="n">
         <v>25</v>
@@ -4539,7 +4539,7 @@
       </c>
       <c r="AE32" s="12" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AF32" s="13" t="inlineStr">
@@ -4565,7 +4565,7 @@
         </is>
       </c>
       <c r="D33" s="14" t="n">
-        <v>33.22</v>
+        <v>32.8</v>
       </c>
       <c r="E33" s="13" t="inlineStr"/>
       <c r="F33" s="12" t="inlineStr">
@@ -4580,7 +4580,7 @@
       </c>
       <c r="H33" s="13" t="inlineStr"/>
       <c r="I33" s="14" t="n">
-        <v>41.0439</v>
+        <v>41.1148</v>
       </c>
       <c r="J33" s="14" t="n">
         <v>11.3883</v>
@@ -4589,13 +4589,13 @@
         <v>52.1359</v>
       </c>
       <c r="L33" s="15" t="n">
-        <v>-19.1</v>
+        <v>-20.2</v>
       </c>
       <c r="M33" s="15" t="n">
         <v>35</v>
       </c>
       <c r="N33" s="14" t="n">
-        <v>26.6785</v>
+        <v>26.7246</v>
       </c>
       <c r="O33" s="12" t="inlineStr">
         <is>
@@ -4630,7 +4630,7 @@
         <v>4</v>
       </c>
       <c r="W33" s="12" t="n">
-        <v>82.09999999999999</v>
+        <v>82.2</v>
       </c>
       <c r="X33" s="13" t="inlineStr">
         <is>
@@ -4661,7 +4661,7 @@
       </c>
       <c r="AE33" s="12" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AF33" s="13" t="inlineStr">
@@ -4809,7 +4809,7 @@
         </is>
       </c>
       <c r="D35" s="19" t="n">
-        <v>542</v>
+        <v>492.2</v>
       </c>
       <c r="E35" s="18" t="inlineStr"/>
       <c r="F35" s="17" t="inlineStr">
@@ -4828,7 +4828,7 @@
         </is>
       </c>
       <c r="I35" s="19" t="n">
-        <v>382.6044</v>
+        <v>382.8678</v>
       </c>
       <c r="J35" s="19" t="n">
         <v>170.1471</v>
@@ -4837,13 +4837,13 @@
         <v>309.2126</v>
       </c>
       <c r="L35" s="20" t="n">
-        <v>41.7</v>
+        <v>28.6</v>
       </c>
       <c r="M35" s="20" t="n">
         <v>25</v>
       </c>
       <c r="N35" s="19" t="n">
-        <v>286.9533</v>
+        <v>287.1508</v>
       </c>
       <c r="O35" s="17" t="inlineStr">
         <is>
@@ -4909,7 +4909,7 @@
       </c>
       <c r="AE35" s="17" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AF35" s="18" t="inlineStr">
@@ -4935,7 +4935,7 @@
         </is>
       </c>
       <c r="D36" s="19" t="n">
-        <v>28.5</v>
+        <v>28.36</v>
       </c>
       <c r="E36" s="18" t="inlineStr"/>
       <c r="F36" s="17" t="inlineStr">
@@ -4950,7 +4950,7 @@
       </c>
       <c r="H36" s="18" t="inlineStr"/>
       <c r="I36" s="19" t="n">
-        <v>20.5648</v>
+        <v>20.5689</v>
       </c>
       <c r="J36" s="19" t="n">
         <v>16.2467</v>
@@ -4959,13 +4959,13 @@
         <v>22.7622</v>
       </c>
       <c r="L36" s="20" t="n">
-        <v>38.6</v>
+        <v>37.9</v>
       </c>
       <c r="M36" s="20" t="n">
         <v>25</v>
       </c>
       <c r="N36" s="19" t="n">
-        <v>15.4236</v>
+        <v>15.4266</v>
       </c>
       <c r="O36" s="17" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="AE36" s="17" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AF36" s="18" t="inlineStr"/>
@@ -5053,7 +5053,7 @@
         </is>
       </c>
       <c r="D37" s="19" t="n">
-        <v>3.015</v>
+        <v>3.04</v>
       </c>
       <c r="E37" s="18" t="inlineStr"/>
       <c r="F37" s="17" t="inlineStr">
@@ -5077,7 +5077,7 @@
         <v>3.9797</v>
       </c>
       <c r="L37" s="20" t="n">
-        <v>30.2</v>
+        <v>31.3</v>
       </c>
       <c r="M37" s="20" t="n">
         <v>25</v>
@@ -5149,7 +5149,7 @@
       </c>
       <c r="AE37" s="17" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AF37" s="18" t="inlineStr">
@@ -5175,7 +5175,7 @@
         </is>
       </c>
       <c r="D38" s="19" t="n">
-        <v>29</v>
+        <v>28.69</v>
       </c>
       <c r="E38" s="18" t="inlineStr"/>
       <c r="F38" s="17" t="inlineStr">
@@ -5190,7 +5190,7 @@
       </c>
       <c r="H38" s="18" t="inlineStr"/>
       <c r="I38" s="19" t="n">
-        <v>23.0611</v>
+        <v>23.0627</v>
       </c>
       <c r="J38" s="19" t="n">
         <v>8.570600000000001</v>
@@ -5199,13 +5199,13 @@
         <v>15.399</v>
       </c>
       <c r="L38" s="20" t="n">
-        <v>25.8</v>
+        <v>24.4</v>
       </c>
       <c r="M38" s="20" t="n">
         <v>25</v>
       </c>
       <c r="N38" s="19" t="n">
-        <v>17.2958</v>
+        <v>17.297</v>
       </c>
       <c r="O38" s="17" t="inlineStr">
         <is>
@@ -5271,7 +5271,7 @@
       </c>
       <c r="AE38" s="17" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AF38" s="18" t="inlineStr">
@@ -5297,7 +5297,7 @@
         </is>
       </c>
       <c r="D39" s="24" t="n">
-        <v>196</v>
+        <v>196.8</v>
       </c>
       <c r="E39" s="23" t="inlineStr"/>
       <c r="F39" s="22" t="inlineStr">
@@ -5312,22 +5312,22 @@
       </c>
       <c r="H39" s="23" t="inlineStr"/>
       <c r="I39" s="24" t="n">
-        <v>103.1559</v>
+        <v>103.1534</v>
       </c>
       <c r="J39" s="24" t="n">
-        <v>66.46680000000001</v>
+        <v>66.4631</v>
       </c>
       <c r="K39" s="24" t="n">
-        <v>111.9693</v>
+        <v>111.9667</v>
       </c>
       <c r="L39" s="25" t="n">
-        <v>90</v>
+        <v>90.8</v>
       </c>
       <c r="M39" s="25" t="n">
         <v>25</v>
       </c>
       <c r="N39" s="24" t="n">
-        <v>77.3669</v>
+        <v>77.36499999999999</v>
       </c>
       <c r="O39" s="22" t="inlineStr">
         <is>
@@ -5393,7 +5393,7 @@
       </c>
       <c r="AE39" s="22" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AF39" s="23" t="inlineStr">
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="D40" s="24" t="n">
-        <v>43.26</v>
+        <v>43.22</v>
       </c>
       <c r="E40" s="23" t="inlineStr"/>
       <c r="F40" s="22" t="inlineStr">
@@ -5440,10 +5440,10 @@
         <v>16.153</v>
       </c>
       <c r="K40" s="24" t="n">
-        <v>22.6237</v>
+        <v>22.6238</v>
       </c>
       <c r="L40" s="25" t="n">
-        <v>51.9</v>
+        <v>51.8</v>
       </c>
       <c r="M40" s="25" t="n">
         <v>25</v>
@@ -5515,7 +5515,7 @@
       </c>
       <c r="AE40" s="22" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AF40" s="23" t="inlineStr"/>
@@ -5537,7 +5537,7 @@
         </is>
       </c>
       <c r="D41" s="24" t="n">
-        <v>161.4</v>
+        <v>160.6</v>
       </c>
       <c r="E41" s="23" t="inlineStr"/>
       <c r="F41" s="22" t="inlineStr">
@@ -5561,7 +5561,7 @@
         <v>147.3001</v>
       </c>
       <c r="L41" s="25" t="n">
-        <v>74.40000000000001</v>
+        <v>73.5</v>
       </c>
       <c r="M41" s="25" t="n">
         <v>25</v>
@@ -5631,12 +5631,12 @@
       </c>
       <c r="AE41" s="22" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AF41" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">行情總股本(17,160,032,183)與財報EPS反推(163,822,314,050)差異&gt;25%，已改用反推值 / 缺關鍵科目：revenue,cash,total_debt,current_assets,current_liab </t>
+          <t xml:space="preserve">行情總股本(17,159,502,183)與財報EPS反推(163,822,314,050)差異&gt;25%，已改用反推值 / 缺關鍵科目：revenue,cash,total_debt,current_assets,current_liab </t>
         </is>
       </c>
     </row>
@@ -5657,7 +5657,7 @@
         </is>
       </c>
       <c r="D42" s="24" t="n">
-        <v>118.28</v>
+        <v>116.82</v>
       </c>
       <c r="E42" s="23" t="inlineStr"/>
       <c r="F42" s="22" t="inlineStr">
@@ -5672,7 +5672,7 @@
       </c>
       <c r="H42" s="23" t="inlineStr"/>
       <c r="I42" s="24" t="n">
-        <v>50.5519</v>
+        <v>50.5532</v>
       </c>
       <c r="J42" s="24" t="n">
         <v>39.5892</v>
@@ -5681,13 +5681,13 @@
         <v>50.2832</v>
       </c>
       <c r="L42" s="25" t="n">
-        <v>134</v>
+        <v>131.1</v>
       </c>
       <c r="M42" s="25" t="n">
         <v>25</v>
       </c>
       <c r="N42" s="24" t="n">
-        <v>37.9139</v>
+        <v>37.9149</v>
       </c>
       <c r="O42" s="22" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
       </c>
       <c r="AE42" s="22" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AF42" s="23" t="inlineStr"/>
@@ -5775,7 +5775,7 @@
         </is>
       </c>
       <c r="D43" s="24" t="n">
-        <v>328.65</v>
+        <v>339.53</v>
       </c>
       <c r="E43" s="23" t="inlineStr"/>
       <c r="F43" s="22" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="H43" s="23" t="inlineStr"/>
       <c r="I43" s="24" t="n">
-        <v>79.0136</v>
+        <v>79.0124</v>
       </c>
       <c r="J43" s="24" t="n">
         <v>56.4053</v>
@@ -5799,13 +5799,13 @@
         <v>76.496</v>
       </c>
       <c r="L43" s="25" t="n">
-        <v>315.9</v>
+        <v>329.7</v>
       </c>
       <c r="M43" s="25" t="n">
         <v>25</v>
       </c>
       <c r="N43" s="24" t="n">
-        <v>59.2602</v>
+        <v>59.2593</v>
       </c>
       <c r="O43" s="22" t="inlineStr">
         <is>
@@ -5871,7 +5871,7 @@
       </c>
       <c r="AE43" s="22" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AF43" s="23" t="inlineStr">
@@ -6019,7 +6019,7 @@
         </is>
       </c>
       <c r="D45" s="24" t="n">
-        <v>396</v>
+        <v>393.6</v>
       </c>
       <c r="E45" s="23" t="inlineStr"/>
       <c r="F45" s="22" t="inlineStr">
@@ -6043,7 +6043,7 @@
         <v>215.7121</v>
       </c>
       <c r="L45" s="25" t="n">
-        <v>152.7</v>
+        <v>151.1</v>
       </c>
       <c r="M45" s="25" t="n">
         <v>25</v>
@@ -6111,7 +6111,7 @@
       </c>
       <c r="AE45" s="22" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AF45" s="23" t="inlineStr">
@@ -6137,7 +6137,7 @@
         </is>
       </c>
       <c r="D46" s="24" t="n">
-        <v>106.7</v>
+        <v>106.6</v>
       </c>
       <c r="E46" s="23" t="inlineStr"/>
       <c r="F46" s="22" t="inlineStr">
@@ -6152,22 +6152,22 @@
       </c>
       <c r="H46" s="23" t="inlineStr"/>
       <c r="I46" s="24" t="n">
-        <v>68.1771</v>
+        <v>68.1778</v>
       </c>
       <c r="J46" s="24" t="n">
         <v>58.5967</v>
       </c>
       <c r="K46" s="24" t="n">
-        <v>63.9875</v>
+        <v>63.9907</v>
       </c>
       <c r="L46" s="25" t="n">
-        <v>56.5</v>
+        <v>56.4</v>
       </c>
       <c r="M46" s="25" t="n">
         <v>25</v>
       </c>
       <c r="N46" s="24" t="n">
-        <v>51.1328</v>
+        <v>51.1333</v>
       </c>
       <c r="O46" s="22" t="inlineStr">
         <is>
@@ -6233,7 +6233,7 @@
       </c>
       <c r="AE46" s="22" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AF46" s="23" t="inlineStr">
@@ -6259,7 +6259,7 @@
         </is>
       </c>
       <c r="D47" s="24" t="n">
-        <v>21.58</v>
+        <v>21.14</v>
       </c>
       <c r="E47" s="23" t="inlineStr"/>
       <c r="F47" s="22" t="inlineStr">
@@ -6274,22 +6274,22 @@
       </c>
       <c r="H47" s="23" t="inlineStr"/>
       <c r="I47" s="24" t="n">
-        <v>12.2091</v>
+        <v>12.2115</v>
       </c>
       <c r="J47" s="24" t="n">
-        <v>6.6242</v>
+        <v>6.6237</v>
       </c>
       <c r="K47" s="24" t="n">
         <v>9.681699999999999</v>
       </c>
       <c r="L47" s="25" t="n">
-        <v>76.8</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="M47" s="25" t="n">
         <v>25</v>
       </c>
       <c r="N47" s="24" t="n">
-        <v>9.1568</v>
+        <v>9.1586</v>
       </c>
       <c r="O47" s="22" t="inlineStr">
         <is>
@@ -6355,7 +6355,7 @@
       </c>
       <c r="AE47" s="22" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AF47" s="23" t="inlineStr">
@@ -6745,7 +6745,7 @@
         </is>
       </c>
       <c r="D51" s="24" t="n">
-        <v>61.82</v>
+        <v>60.94</v>
       </c>
       <c r="E51" s="23" t="inlineStr"/>
       <c r="F51" s="22" t="inlineStr">
@@ -6760,22 +6760,22 @@
       </c>
       <c r="H51" s="23" t="inlineStr"/>
       <c r="I51" s="24" t="n">
-        <v>35.7611</v>
+        <v>35.7648</v>
       </c>
       <c r="J51" s="24" t="n">
-        <v>25.558</v>
+        <v>25.5798</v>
       </c>
       <c r="K51" s="24" t="n">
-        <v>36.6872</v>
+        <v>36.6885</v>
       </c>
       <c r="L51" s="25" t="n">
-        <v>72.90000000000001</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="M51" s="25" t="n">
         <v>25</v>
       </c>
       <c r="N51" s="24" t="n">
-        <v>26.8208</v>
+        <v>26.8236</v>
       </c>
       <c r="O51" s="22" t="inlineStr">
         <is>
@@ -6810,7 +6810,7 @@
         <v>3</v>
       </c>
       <c r="W51" s="22" t="n">
-        <v>92.2</v>
+        <v>92.3</v>
       </c>
       <c r="X51" s="23" t="inlineStr">
         <is>
@@ -6841,7 +6841,7 @@
       </c>
       <c r="AE51" s="22" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AF51" s="23" t="inlineStr">
@@ -6867,7 +6867,7 @@
         </is>
       </c>
       <c r="D52" s="24" t="n">
-        <v>281.34</v>
+        <v>279.49</v>
       </c>
       <c r="E52" s="23" t="inlineStr"/>
       <c r="F52" s="22" t="inlineStr">
@@ -6891,7 +6891,7 @@
         <v>12.8567</v>
       </c>
       <c r="L52" s="25" t="n">
-        <v>2602.7</v>
+        <v>2585</v>
       </c>
       <c r="M52" s="25" t="n">
         <v>25</v>
@@ -6963,7 +6963,7 @@
       </c>
       <c r="AE52" s="22" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AF52" s="23" t="inlineStr"/>
@@ -8083,7 +8083,7 @@
         </is>
       </c>
       <c r="D62" s="24" t="n">
-        <v>473.18</v>
+        <v>462.6</v>
       </c>
       <c r="E62" s="23" t="inlineStr"/>
       <c r="F62" s="22" t="inlineStr">
@@ -8111,7 +8111,7 @@
         <v>8.4762</v>
       </c>
       <c r="L62" s="25" t="n">
-        <v>6983</v>
+        <v>6824.6</v>
       </c>
       <c r="M62" s="25" t="n">
         <v>25</v>
@@ -8183,7 +8183,7 @@
       </c>
       <c r="AE62" s="22" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AF62" s="23" t="inlineStr"/>
@@ -8205,7 +8205,7 @@
         </is>
       </c>
       <c r="D63" s="24" t="n">
-        <v>61.45</v>
+        <v>61.35</v>
       </c>
       <c r="E63" s="23" t="inlineStr"/>
       <c r="F63" s="22" t="inlineStr">
@@ -8220,22 +8220,22 @@
       </c>
       <c r="H63" s="23" t="inlineStr"/>
       <c r="I63" s="24" t="n">
-        <v>6.9171</v>
+        <v>6.917</v>
       </c>
       <c r="J63" s="24" t="n">
         <v>3.7772</v>
       </c>
       <c r="K63" s="24" t="n">
-        <v>10.413</v>
+        <v>10.4125</v>
       </c>
       <c r="L63" s="25" t="n">
-        <v>788.4</v>
+        <v>786.9</v>
       </c>
       <c r="M63" s="25" t="n">
         <v>25</v>
       </c>
       <c r="N63" s="24" t="n">
-        <v>5.1879</v>
+        <v>5.1877</v>
       </c>
       <c r="O63" s="22" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="AE63" s="22" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AF63" s="23" t="inlineStr">
@@ -8327,7 +8327,7 @@
         </is>
       </c>
       <c r="D64" s="24" t="n">
-        <v>1.265</v>
+        <v>1.2</v>
       </c>
       <c r="E64" s="23" t="inlineStr"/>
       <c r="F64" s="22" t="inlineStr">
@@ -8351,7 +8351,7 @@
         <v>0.1246</v>
       </c>
       <c r="L64" s="25" t="n">
-        <v>1213.6</v>
+        <v>1146.1</v>
       </c>
       <c r="M64" s="25" t="n">
         <v>25</v>
@@ -8423,7 +8423,7 @@
       </c>
       <c r="AE64" s="22" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AF64" s="23" t="inlineStr">
@@ -8449,7 +8449,7 @@
         </is>
       </c>
       <c r="D65" s="24" t="n">
-        <v>75.45</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="E65" s="23" t="inlineStr"/>
       <c r="F65" s="22" t="inlineStr">
@@ -8473,7 +8473,7 @@
         <v>58.1316</v>
       </c>
       <c r="L65" s="25" t="n">
-        <v>440.4</v>
+        <v>429.3</v>
       </c>
       <c r="M65" s="25" t="n">
         <v>25</v>
@@ -8545,7 +8545,7 @@
       </c>
       <c r="AE65" s="22" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AF65" s="23" t="inlineStr">
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="D67" s="29" t="n">
-        <v>5.315</v>
+        <v>5.27</v>
       </c>
       <c r="E67" s="28" t="inlineStr"/>
       <c r="F67" s="27" t="inlineStr">
@@ -8717,7 +8717,7 @@
         <v>62.1445</v>
       </c>
       <c r="L67" s="30" t="n">
-        <v>-96.59999999999999</v>
+        <v>-96.7</v>
       </c>
       <c r="M67" s="30" t="n">
         <v>35</v>
@@ -8789,7 +8789,7 @@
       </c>
       <c r="AE67" s="27" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AF67" s="28" t="inlineStr">
@@ -8815,7 +8815,7 @@
         </is>
       </c>
       <c r="D68" s="29" t="n">
-        <v>5.49</v>
+        <v>5.36</v>
       </c>
       <c r="E68" s="28" t="inlineStr"/>
       <c r="F68" s="27" t="inlineStr">
@@ -8830,22 +8830,22 @@
       </c>
       <c r="H68" s="28" t="inlineStr"/>
       <c r="I68" s="29" t="n">
-        <v>3.8971</v>
+        <v>3.934</v>
       </c>
       <c r="J68" s="29" t="n">
-        <v>2.6191</v>
+        <v>2.6682</v>
       </c>
       <c r="K68" s="29" t="n">
         <v>79.6524</v>
       </c>
       <c r="L68" s="30" t="n">
-        <v>40.9</v>
+        <v>36.2</v>
       </c>
       <c r="M68" s="30" t="n">
         <v>25</v>
       </c>
       <c r="N68" s="29" t="n">
-        <v>2.9229</v>
+        <v>2.9505</v>
       </c>
       <c r="O68" s="27" t="inlineStr">
         <is>
@@ -8911,7 +8911,7 @@
       </c>
       <c r="AE68" s="27" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AF68" s="28" t="inlineStr">
@@ -8937,7 +8937,7 @@
         </is>
       </c>
       <c r="D69" s="29" t="n">
-        <v>0.171</v>
+        <v>0.17</v>
       </c>
       <c r="E69" s="28" t="inlineStr"/>
       <c r="F69" s="27" t="inlineStr">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="AE69" s="27" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AF69" s="28" t="inlineStr">
@@ -9316,7 +9316,7 @@
         </is>
       </c>
       <c r="C2" s="34" t="n">
-        <v>161.4</v>
+        <v>160.6</v>
       </c>
       <c r="D2" s="34" t="n">
         <v>92.5639</v>
@@ -9371,10 +9371,10 @@
         </is>
       </c>
       <c r="C3" s="34" t="n">
-        <v>5.49</v>
+        <v>5.36</v>
       </c>
       <c r="D3" s="34" t="n">
-        <v>3.8971</v>
+        <v>3.934</v>
       </c>
       <c r="E3" s="34" t="inlineStr"/>
       <c r="F3" s="34" t="inlineStr"/>
@@ -9383,7 +9383,7 @@
         <v>7.7314</v>
       </c>
       <c r="I3" s="34" t="n">
-        <v>2.6191</v>
+        <v>2.6682</v>
       </c>
       <c r="J3" s="34" t="inlineStr"/>
       <c r="K3" s="34" t="inlineStr"/>
@@ -9391,7 +9391,7 @@
         <v>79.6524</v>
       </c>
       <c r="M3" s="34" t="n">
-        <v>5.92</v>
+        <v>5.89</v>
       </c>
       <c r="N3" s="34" t="n">
         <v>8.99</v>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="Q3" s="33" t="inlineStr">
         <is>
-          <t>{"ncav": {"NCAV/股": 0.0, "NNWC/股": -12.4752, "net-net買點": 0.0}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 4103328460.0, "g1": -0.0263, "永續g": 0.03, "門檻報酬r": 0.0905, "非營運投資(折70%)": 4890900000.0}, "epv": {"常態營業利益率": 0.1444, "常態NOPAT": 4677046636.0, "WACC": 0.0592, "淨現金": -63645000000.0}, "damodaran_fcff": {"銷售/資本": 0.8, "g1": 0.0373, "永續g": 0.03, "目標營業利益率": 0.1444, "WACC": 0.0592, "終值WACC": 0.0995, "有效稅率": 0.2199, "終值佔比": 0.547}, "ddm": {"DPS": 0.7376, "g": 0.0799, "r": 0.0899}}</t>
+          <t>{"ncav": {"NCAV/股": 0.0, "NNWC/股": -12.4752, "net-net買點": 0.0}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 4103328460.0, "g1": -0.0263, "永續g": 0.03, "門檻報酬r": 0.0905, "非營運投資(折70%)": 4890900000.0}, "epv": {"常態營業利益率": 0.1444, "常態NOPAT": 4677046636.0, "WACC": 0.0589, "淨現金": -63645000000.0}, "damodaran_fcff": {"銷售/資本": 0.8, "g1": 0.0373, "永續g": 0.03, "目標營業利益率": 0.1444, "WACC": 0.0589, "終值WACC": 0.0995, "有效稅率": 0.2199, "終值佔比": 0.547}, "ddm": {"DPS": 0.7376, "g": 0.0799, "r": 0.0899}}</t>
         </is>
       </c>
     </row>
@@ -9422,7 +9422,7 @@
         </is>
       </c>
       <c r="C4" s="34" t="n">
-        <v>1.265</v>
+        <v>1.2</v>
       </c>
       <c r="D4" s="34" t="n">
         <v>0.0963</v>
@@ -9440,7 +9440,7 @@
       </c>
       <c r="L4" s="34" t="inlineStr"/>
       <c r="M4" s="34" t="n">
-        <v>10.27</v>
+        <v>10.22</v>
       </c>
       <c r="N4" s="34" t="n">
         <v>11.23</v>
@@ -9471,10 +9471,10 @@
         </is>
       </c>
       <c r="C5" s="34" t="n">
-        <v>87.89</v>
+        <v>86</v>
       </c>
       <c r="D5" s="34" t="n">
-        <v>107.1602</v>
+        <v>107.1841</v>
       </c>
       <c r="E5" s="34" t="n">
         <v>58.438</v>
@@ -9489,10 +9489,10 @@
         <v>163.0545</v>
       </c>
       <c r="I5" s="34" t="n">
-        <v>68.9901</v>
+        <v>69.0992</v>
       </c>
       <c r="J5" s="34" t="n">
-        <v>88.2576</v>
+        <v>88.26609999999999</v>
       </c>
       <c r="K5" s="34" t="n">
         <v>136.1654</v>
@@ -9501,7 +9501,7 @@
         <v>111.3681</v>
       </c>
       <c r="M5" s="34" t="n">
-        <v>8.220000000000001</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="N5" s="34" t="n">
         <v>8.9</v>
@@ -9516,7 +9516,7 @@
       </c>
       <c r="Q5" s="33" t="inlineStr">
         <is>
-          <t>{"graham_number": {"EPS(3年均)": 5.44, "BVPS": 27.9003}, "graham_formula": {"g(上限10%)": 0.081, "Y公司債": 0.04}, "ncav": {"NCAV/股": 2.5941, "NNWC/股": -33.0932, "net-net買點": 1.7303}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 51588560000.0, "g1": 0.1206, "永續g": 0.021, "門檻報酬r": 0.085, "非營運投資(折70%)": 3239763800.0}, "epv": {"常態營業利益率": 0.1079, "常態NOPAT": 41817135357.0, "WACC": 0.0822, "淨現金": 14272378000.0}, "damodaran_fcff": {"銷售/資本": 2.353, "g1": 0.0987, "永續g": 0.021, "目標營業利益率": 0.1079, "WACC": 0.0822, "終值WACC": 0.089, "有效稅率": 0.1704, "終值佔比": 0.576}, "ri_pb": {"常態ROE": 0.2332, "股權成本r": 0.089, "留存成長g": 0.0518, "合理PB": 4.88}, "ddm": {"DPS": 4.5318, "g": 0.0464, "r": 0.089}}</t>
+          <t>{"graham_number": {"EPS(3年均)": 5.44, "BVPS": 27.9003}, "graham_formula": {"g(上限10%)": 0.081, "Y公司債": 0.04}, "ncav": {"NCAV/股": 2.5941, "NNWC/股": -33.0932, "net-net買點": 1.7303}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 51588560000.0, "g1": 0.1206, "永續g": 0.021, "門檻報酬r": 0.085, "非營運投資(折70%)": 3239763800.0}, "epv": {"常態營業利益率": 0.1079, "常態NOPAT": 41817135357.0, "WACC": 0.082, "淨現金": 14272378000.0}, "damodaran_fcff": {"銷售/資本": 2.353, "g1": 0.0987, "永續g": 0.021, "目標營業利益率": 0.1079, "WACC": 0.082, "終值WACC": 0.089, "有效稅率": 0.1704, "終值佔比": 0.576}, "ri_pb": {"常態ROE": 0.2332, "股權成本r": 0.089, "留存成長g": 0.0518, "合理PB": 4.88}, "ddm": {"DPS": 4.5318, "g": 0.0464, "r": 0.089}}</t>
         </is>
       </c>
     </row>
@@ -9532,10 +9532,10 @@
         </is>
       </c>
       <c r="C6" s="34" t="n">
-        <v>38.61</v>
+        <v>38.23</v>
       </c>
       <c r="D6" s="34" t="n">
-        <v>142.5253</v>
+        <v>142.5472</v>
       </c>
       <c r="E6" s="34" t="n">
         <v>55.8024</v>
@@ -9550,10 +9550,10 @@
         <v>216.1553</v>
       </c>
       <c r="I6" s="34" t="n">
-        <v>62.3056</v>
+        <v>62.4086</v>
       </c>
       <c r="J6" s="34" t="n">
-        <v>48.7428</v>
+        <v>48.7482</v>
       </c>
       <c r="K6" s="34" t="n">
         <v>808.3745</v>
@@ -9562,7 +9562,7 @@
         <v>151.0522</v>
       </c>
       <c r="M6" s="34" t="n">
-        <v>7.03</v>
+        <v>7.01</v>
       </c>
       <c r="N6" s="34" t="n">
         <v>8.9</v>
@@ -9577,7 +9577,7 @@
       </c>
       <c r="Q6" s="33" t="inlineStr">
         <is>
-          <t>{"graham_number": {"EPS(3年均)": 5.22, "BVPS": 26.5126}, "graham_formula": {"g(上限10%)": 0.0699, "Y公司債": 0.04}, "ncav": {"NCAV/股": 1.6956, "NNWC/股": -16.537, "net-net買點": 1.131}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 44665803686.0, "g1": 0.15, "永續g": 0.021, "門檻報酬r": 0.085, "非營運投資(折70%)": 1998879714.0}, "epv": {"常態營業利益率": 0.1603, "常態NOPAT": 21250243163.0, "WACC": 0.0703, "淨現金": 44611454148.0}, "damodaran_fcff": {"銷售/資本": 1.571, "g1": -0.0345, "永續g": 0.021, "目標營業利益率": 0.1603, "WACC": 0.0703, "終值WACC": 0.089, "有效稅率": 0.1876, "終值佔比": 0.445}, "ri_pb": {"常態ROE": 0.2365, "股權成本r": 0.089, "留存成長g": 0.084, "合理PB": 30.49}, "ddm": {"DPS": 3.1751, "g": 0.0666, "r": 0.089}}</t>
+          <t>{"graham_number": {"EPS(3年均)": 5.22, "BVPS": 26.5126}, "graham_formula": {"g(上限10%)": 0.0699, "Y公司債": 0.04}, "ncav": {"NCAV/股": 1.6956, "NNWC/股": -16.537, "net-net買點": 1.131}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 44665803686.0, "g1": 0.15, "永續g": 0.021, "門檻報酬r": 0.085, "非營運投資(折70%)": 1998879714.0}, "epv": {"常態營業利益率": 0.1603, "常態NOPAT": 21250243163.0, "WACC": 0.0701, "淨現金": 44611454148.0}, "damodaran_fcff": {"銷售/資本": 1.571, "g1": -0.0345, "永續g": 0.021, "目標營業利益率": 0.1603, "WACC": 0.0701, "終值WACC": 0.089, "有效稅率": 0.1876, "終值佔比": 0.445}, "ri_pb": {"常態ROE": 0.2365, "股權成本r": 0.089, "留存成長g": 0.084, "合理PB": 30.49}, "ddm": {"DPS": 3.1751, "g": 0.0666, "r": 0.089}}</t>
         </is>
       </c>
     </row>
@@ -9593,10 +9593,10 @@
         </is>
       </c>
       <c r="C7" s="34" t="n">
-        <v>29</v>
+        <v>28.69</v>
       </c>
       <c r="D7" s="34" t="n">
-        <v>23.0611</v>
+        <v>23.0627</v>
       </c>
       <c r="E7" s="34" t="n">
         <v>15.399</v>
@@ -9611,10 +9611,10 @@
         <v>57.4509</v>
       </c>
       <c r="I7" s="34" t="n">
-        <v>10.1115</v>
+        <v>10.12</v>
       </c>
       <c r="J7" s="34" t="n">
-        <v>8.278</v>
+        <v>8.277900000000001</v>
       </c>
       <c r="K7" s="34" t="n">
         <v>8.570600000000001</v>
@@ -9623,7 +9623,7 @@
         <v>13.1089</v>
       </c>
       <c r="M7" s="34" t="n">
-        <v>8.300000000000001</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="N7" s="34" t="n">
         <v>8.9</v>
@@ -9638,7 +9638,7 @@
       </c>
       <c r="Q7" s="33" t="inlineStr">
         <is>
-          <t>{"graham_number": {"EPS(3年均)": 0.83, "BVPS": 12.6977}, "graham_formula": {"g(上限10%)": 0.1, "Y公司債": 0.04}, "ncav": {"NCAV/股": 1.8941, "NNWC/股": -7.9563, "net-net買點": 1.2634}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 1097085527.0, "g1": 0.15, "永續g": 0.021, "門檻報酬r": 0.085, "非營運投資(折70%)": 3335130.0}, "epv": {"常態營業利益率": 0.0665, "常態NOPAT": 508532212.0, "WACC": 0.083, "淨現金": -906634291.0}, "damodaran_fcff": {"銷售/資本": 1.113, "g1": 0.1305, "永續g": 0.021, "目標營業利益率": 0.0665, "WACC": 0.083, "終值WACC": 0.089, "有效稅率": 0.08, "終值佔比": 1.044}, "ri_pb": {"常態ROE": 0.0708, "股權成本r": 0.089, "留存成長g": 0.0331, "合理PB": 0.675}, "ddm": {"DPS": 0.5995, "g": 0.0414, "r": 0.089}}</t>
+          <t>{"graham_number": {"EPS(3年均)": 0.83, "BVPS": 12.6977}, "graham_formula": {"g(上限10%)": 0.1, "Y公司債": 0.04}, "ncav": {"NCAV/股": 1.8941, "NNWC/股": -7.9563, "net-net買點": 1.2634}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 1097085527.0, "g1": 0.15, "永續g": 0.021, "門檻報酬r": 0.085, "非營運投資(折70%)": 3335130.0}, "epv": {"常態營業利益率": 0.0665, "常態NOPAT": 508532212.0, "WACC": 0.0829, "淨現金": -906634291.0}, "damodaran_fcff": {"銷售/資本": 1.113, "g1": 0.1305, "永續g": 0.021, "目標營業利益率": 0.0665, "WACC": 0.0829, "終值WACC": 0.089, "有效稅率": 0.08, "終值佔比": 1.044}, "ri_pb": {"常態ROE": 0.0708, "股權成本r": 0.089, "留存成長g": 0.0331, "合理PB": 0.675}, "ddm": {"DPS": 0.5995, "g": 0.0414, "r": 0.089}}</t>
         </is>
       </c>
     </row>
@@ -9654,10 +9654,10 @@
         </is>
       </c>
       <c r="C8" s="34" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="D8" s="34" t="n">
-        <v>3.8023</v>
+        <v>3.8031</v>
       </c>
       <c r="E8" s="34" t="n">
         <v>2.8029</v>
@@ -9672,10 +9672,10 @@
         <v>7.9395</v>
       </c>
       <c r="I8" s="34" t="n">
-        <v>2.3837</v>
+        <v>2.3871</v>
       </c>
       <c r="J8" s="34" t="n">
-        <v>2.2076</v>
+        <v>2.2079</v>
       </c>
       <c r="K8" s="34" t="n">
         <v>1.2252</v>
@@ -9684,7 +9684,7 @@
         <v>2.9007</v>
       </c>
       <c r="M8" s="34" t="n">
-        <v>8.619999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="N8" s="34" t="n">
         <v>9.949999999999999</v>
@@ -9699,7 +9699,7 @@
       </c>
       <c r="Q8" s="33" t="inlineStr">
         <is>
-          <t>{"graham_number": {"EPS(3年均)": 0.1511, "BVPS": 1.7052}, "graham_formula": {"g(上限10%)": 0.1, "Y公司債": 0.056}, "ncav": {"NCAV/股": 0.4212, "NNWC/股": -0.3809, "net-net買點": 0.281}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 1650620000.0, "g1": 0.15, "永續g": 0.03, "門檻報酬r": 0.0905, "非營運投資(折70%)": 1933444800.0}, "epv": {"常態營業利益率": 0.0458, "常態NOPAT": 894448196.0, "WACC": 0.0862, "淨現金": 2074648000.0}, "damodaran_fcff": {"銷售/資本": 2.507, "g1": 0.0038, "永續g": 0.03, "目標營業利益率": 0.0458, "WACC": 0.0862, "終值WACC": 0.0995, "有效稅率": 0.2132, "終值佔比": 0.477}, "ri_pb": {"常態ROE": 0.08, "股權成本r": 0.0995, "留存成長g": 0.0485, "合理PB": 0.617}, "ddm": {"DPS": 0.0748, "g": 0.0675, "r": 0.0995}}</t>
+          <t>{"graham_number": {"EPS(3年均)": 0.1511, "BVPS": 1.7052}, "graham_formula": {"g(上限10%)": 0.1, "Y公司債": 0.056}, "ncav": {"NCAV/股": 0.4212, "NNWC/股": -0.3809, "net-net買點": 0.281}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 1650620000.0, "g1": 0.15, "永續g": 0.03, "門檻報酬r": 0.0905, "非營運投資(折70%)": 1933444800.0}, "epv": {"常態營業利益率": 0.0458, "常態NOPAT": 894448196.0, "WACC": 0.086, "淨現金": 2074648000.0}, "damodaran_fcff": {"銷售/資本": 2.507, "g1": 0.0038, "永續g": 0.03, "目標營業利益率": 0.0458, "WACC": 0.086, "終值WACC": 0.0995, "有效稅率": 0.2132, "終值佔比": 0.477}, "ri_pb": {"常態ROE": 0.08, "股權成本r": 0.0995, "留存成長g": 0.0485, "合理PB": 0.617}, "ddm": {"DPS": 0.0748, "g": 0.0675, "r": 0.0995}}</t>
         </is>
       </c>
     </row>
@@ -9715,10 +9715,10 @@
         </is>
       </c>
       <c r="C9" s="34" t="n">
-        <v>33.22</v>
+        <v>32.8</v>
       </c>
       <c r="D9" s="34" t="n">
-        <v>41.0439</v>
+        <v>41.1148</v>
       </c>
       <c r="E9" s="34" t="n">
         <v>39.2855</v>
@@ -9731,7 +9731,7 @@
       </c>
       <c r="H9" s="34" t="inlineStr"/>
       <c r="I9" s="34" t="n">
-        <v>21.6857</v>
+        <v>21.87</v>
       </c>
       <c r="J9" s="34" t="inlineStr"/>
       <c r="K9" s="34" t="n">
@@ -9741,7 +9741,7 @@
         <v>144.2784</v>
       </c>
       <c r="M9" s="34" t="n">
-        <v>6.03</v>
+        <v>6.01</v>
       </c>
       <c r="N9" s="34" t="n">
         <v>9.949999999999999</v>
@@ -9756,7 +9756,7 @@
       </c>
       <c r="Q9" s="33" t="inlineStr">
         <is>
-          <t>{"graham_number": {"EPS(3年均)": 2.0, "BVPS": 25.3079}, "graham_formula": {"g(上限10%)": 0.1, "Y公司債": 0.056}, "ncav": {"NCAV/股": 3.4455, "NNWC/股": -35.366, "net-net買點": 2.2982}, "epv": {"常態營業利益率": 0.0217, "常態NOPAT": 9489066287.0, "WACC": 0.0603, "淨現金": -107039386000.0}, "damodaran_fcff": {"銷售/資本": 3.044, "g1": 0.0429, "永續g": 0.03, "目標營業利益率": 0.0217, "WACC": 0.0603, "終值WACC": 0.0995, "有效稅率": 0.2628, "終值佔比": 0.745}, "ri_pb": {"常態ROE": 0.0651, "股權成本r": 0.0995, "留存成長g": 0.0434, "合理PB": 0.387}, "ddm": {"DPS": 1.1376, "g": 0.0895, "r": 0.0995}}</t>
+          <t>{"graham_number": {"EPS(3年均)": 2.0, "BVPS": 25.3079}, "graham_formula": {"g(上限10%)": 0.1, "Y公司債": 0.056}, "ncav": {"NCAV/股": 3.4455, "NNWC/股": -35.366, "net-net買點": 2.2982}, "epv": {"常態營業利益率": 0.0217, "常態NOPAT": 9489066287.0, "WACC": 0.0601, "淨現金": -107039386000.0}, "damodaran_fcff": {"銷售/資本": 3.044, "g1": 0.0429, "永續g": 0.03, "目標營業利益率": 0.0217, "WACC": 0.0601, "終值WACC": 0.0995, "有效稅率": 0.2628, "終值佔比": 0.745}, "ri_pb": {"常態ROE": 0.0651, "股權成本r": 0.0995, "留存成長g": 0.0434, "合理PB": 0.387}, "ddm": {"DPS": 1.1376, "g": 0.0895, "r": 0.0995}}</t>
         </is>
       </c>
     </row>
@@ -9772,35 +9772,35 @@
         </is>
       </c>
       <c r="C10" s="34" t="n">
-        <v>4.67</v>
+        <v>4.58</v>
       </c>
       <c r="D10" s="34" t="n">
-        <v>9.299799999999999</v>
+        <v>9.313599999999999</v>
       </c>
       <c r="E10" s="34" t="n">
-        <v>9.2554</v>
+        <v>9.2593</v>
       </c>
       <c r="F10" s="34" t="n">
         <v>3.141</v>
       </c>
       <c r="G10" s="34" t="inlineStr"/>
       <c r="H10" s="34" t="n">
-        <v>24.345</v>
+        <v>24.366</v>
       </c>
       <c r="I10" s="34" t="n">
-        <v>6.168</v>
+        <v>6.2038</v>
       </c>
       <c r="J10" s="34" t="n">
-        <v>1.2827</v>
+        <v>1.285</v>
       </c>
       <c r="K10" s="34" t="n">
-        <v>6.2659</v>
+        <v>6.2714</v>
       </c>
       <c r="L10" s="34" t="n">
-        <v>3.5319</v>
+        <v>3.5349</v>
       </c>
       <c r="M10" s="34" t="n">
-        <v>6.39</v>
+        <v>6.36</v>
       </c>
       <c r="N10" s="34" t="n">
         <v>8.99</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="Q10" s="33" t="inlineStr">
         <is>
-          <t>{"graham_number": {"EPS(3年均)": 0.404, "BVPS": 6.9539}, "graham_formula": {"g(上限10%)": -0.0059, "Y公司債": 0.056}, "ncav": {"NCAV/股": 0.0, "NNWC/股": -6.8094, "net-net買點": 0.0}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 161475000000.0, "g1": -0.0073, "永續g": 0.03, "門檻報酬r": 0.0905, "非營運投資(折70%)": 180806500000.0}, "epv": {"常態營業利益率": 0.0234, "常態NOPAT": 52553004985.0, "WACC": 0.0639, "淨現金": -363061000000.0}, "damodaran_fcff": {"銷售/資本": 2.289, "g1": -0.05, "永續g": 0.03, "目標營業利益率": 0.0234, "WACC": 0.0639, "終值WACC": 0.0995, "有效稅率": 0.1864, "終值佔比": 0.426}, "ri_pb": {"常態ROE": 0.0716, "股權成本r": 0.0899, "留存成長g": 0.0089, "合理PB": 0.774}, "ddm": {"DPS": 0.2556, "g": 0.0052, "r": 0.0899}}</t>
+          <t>{"graham_number": {"EPS(3年均)": 0.404, "BVPS": 6.9599}, "graham_formula": {"g(上限10%)": -0.0059, "Y公司債": 0.056}, "ncav": {"NCAV/股": 0.0, "NNWC/股": -6.8152, "net-net買點": 0.0}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 161475000000.0, "g1": -0.0073, "永續g": 0.03, "門檻報酬r": 0.0905, "非營運投資(折70%)": 180806500000.0}, "epv": {"常態營業利益率": 0.0234, "常態NOPAT": 52553004985.0, "WACC": 0.0636, "淨現金": -363061000000.0}, "damodaran_fcff": {"銷售/資本": 2.289, "g1": -0.05, "永續g": 0.03, "目標營業利益率": 0.0234, "WACC": 0.0636, "終值WACC": 0.0995, "有效稅率": 0.1864, "終值佔比": 0.426}, "ri_pb": {"常態ROE": 0.0716, "股權成本r": 0.0899, "留存成長g": 0.0089, "合理PB": 0.774}, "ddm": {"DPS": 0.2558, "g": 0.0052, "r": 0.0899}}</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
         </is>
       </c>
       <c r="C11" s="34" t="n">
-        <v>396</v>
+        <v>393.6</v>
       </c>
       <c r="D11" s="34" t="n">
         <v>156.7211</v>
@@ -9884,32 +9884,32 @@
         </is>
       </c>
       <c r="C12" s="34" t="n">
-        <v>437.8</v>
+        <v>434.2</v>
       </c>
       <c r="D12" s="34" t="n">
-        <v>659.799</v>
+        <v>660.375</v>
       </c>
       <c r="E12" s="34" t="n">
-        <v>282.2419</v>
+        <v>282.3672</v>
       </c>
       <c r="F12" s="34" t="n">
         <v>469.194</v>
       </c>
       <c r="G12" s="34" t="inlineStr"/>
       <c r="H12" s="34" t="n">
-        <v>684.9798</v>
+        <v>685.5881000000001</v>
       </c>
       <c r="I12" s="34" t="n">
-        <v>368.9535</v>
+        <v>369.4815</v>
       </c>
       <c r="J12" s="34" t="n">
-        <v>459.3207</v>
+        <v>459.7468</v>
       </c>
       <c r="K12" s="34" t="n">
-        <v>3850.9858</v>
+        <v>3854.4057</v>
       </c>
       <c r="L12" s="34" t="n">
-        <v>609.7471</v>
+        <v>610.2885</v>
       </c>
       <c r="M12" s="34" t="n">
         <v>9.16</v>
@@ -9927,7 +9927,7 @@
       </c>
       <c r="Q12" s="33" t="inlineStr">
         <is>
-          <t>{"graham_number": {"EPS(3年均)": 20.938, "BVPS": 124.7757}, "graham_formula": {"g(上限10%)": 0.08, "Y公司債": 0.056}, "ncav": {"NCAV/股": 0.0, "NNWC/股": -47.8878, "net-net買點": 0.0}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 202308000000.0, "g1": 0.1058, "永續g": 0.03, "門檻報酬r": 0.0905, "非營運投資(折70%)": 642665100000.0}, "epv": {"常態營業利益率": 0.3189, "常態NOPAT": 206641814252.0, "WACC": 0.0916, "淨現金": -12924000000.0}, "damodaran_fcff": {"銷售/資本": 0.8, "g1": 0.1076, "永續g": 0.03, "目標營業利益率": 0.3189, "WACC": 0.0916, "終值WACC": 0.0995, "有效稅率": 0.1678, "終值佔比": 0.565}, "ri_pb": {"常態ROE": 0.2271, "股權成本r": 0.0995, "留存成長g": 0.0945, "合理PB": 26.512}, "ddm": {"DPS": 4.8076, "g": 0.0895, "r": 0.0995}}</t>
+          <t>{"graham_number": {"EPS(3年均)": 20.938, "BVPS": 124.8865}, "graham_formula": {"g(上限10%)": 0.08, "Y公司債": 0.056}, "ncav": {"NCAV/股": 0.0, "NNWC/股": -47.9303, "net-net買點": 0.0}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 202308000000.0, "g1": 0.1058, "永續g": 0.03, "門檻報酬r": 0.0905, "非營運投資(折70%)": 642665100000.0}, "epv": {"常態營業利益率": 0.3189, "常態NOPAT": 206641814252.0, "WACC": 0.0916, "淨現金": -12924000000.0}, "damodaran_fcff": {"銷售/資本": 0.8, "g1": 0.1076, "永續g": 0.03, "目標營業利益率": 0.3189, "WACC": 0.0916, "終值WACC": 0.0995, "有效稅率": 0.1678, "終值佔比": 0.565}, "ri_pb": {"常態ROE": 0.2271, "股權成本r": 0.0995, "留存成長g": 0.0945, "合理PB": 26.512}, "ddm": {"DPS": 4.8118, "g": 0.0895, "r": 0.0995}}</t>
         </is>
       </c>
     </row>
@@ -9943,10 +9943,10 @@
         </is>
       </c>
       <c r="C13" s="34" t="n">
-        <v>5.91</v>
+        <v>5.78</v>
       </c>
       <c r="D13" s="34" t="n">
-        <v>11.4397</v>
+        <v>11.4444</v>
       </c>
       <c r="E13" s="34" t="n">
         <v>15.7849</v>
@@ -9959,10 +9959,10 @@
         <v>12.385</v>
       </c>
       <c r="I13" s="34" t="n">
-        <v>11.4749</v>
+        <v>11.4973</v>
       </c>
       <c r="J13" s="34" t="n">
-        <v>8.3782</v>
+        <v>8.3788</v>
       </c>
       <c r="K13" s="34" t="n">
         <v>5.9237</v>
@@ -9971,7 +9971,7 @@
         <v>6.23</v>
       </c>
       <c r="M13" s="34" t="n">
-        <v>7.51</v>
+        <v>7.49</v>
       </c>
       <c r="N13" s="34" t="n">
         <v>8.67</v>
@@ -9986,7 +9986,7 @@
       </c>
       <c r="Q13" s="33" t="inlineStr">
         <is>
-          <t>{"graham_number": {"EPS(3年均)": 0.67, "BVPS": 12.1964}, "graham_formula": {"g(上限10%)": 0.1, "Y公司債": 0.056}, "ncav": {"NCAV/股": 0.0, "NNWC/股": -5.2925, "net-net買點": 0.0}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 22534000000.0, "g1": -0.05, "永續g": 0.03, "門檻報酬r": 0.0905, "非營運投資(折70%)": 52849300000.0}, "epv": {"常態營業利益率": 0.0496, "常態NOPAT": 16364617627.0, "WACC": 0.0751, "淨現金": 30851000000.0}, "damodaran_fcff": {"銷售/資本": 1.149, "g1": 0.0339, "永續g": 0.03, "目標營業利益率": 0.0496, "WACC": 0.0751, "終值WACC": 0.0995, "有效稅率": 0.1621, "終值佔比": 0.692}, "ri_pb": {"常態ROE": 0.0407, "股權成本r": 0.0867, "留存成長g": 0.0078, "合理PB": 0.417}, "ddm": {"DPS": 0.417, "g": 0.0081, "r": 0.0867}}</t>
+          <t>{"graham_number": {"EPS(3年均)": 0.67, "BVPS": 12.1964}, "graham_formula": {"g(上限10%)": 0.1, "Y公司債": 0.056}, "ncav": {"NCAV/股": 0.0, "NNWC/股": -5.2925, "net-net買點": 0.0}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 22534000000.0, "g1": -0.05, "永續g": 0.03, "門檻報酬r": 0.0905, "非營運投資(折70%)": 52849300000.0}, "epv": {"常態營業利益率": 0.0496, "常態NOPAT": 16364617627.0, "WACC": 0.0749, "淨現金": 30851000000.0}, "damodaran_fcff": {"銷售/資本": 1.149, "g1": 0.0339, "永續g": 0.03, "目標營業利益率": 0.0496, "WACC": 0.0749, "終值WACC": 0.0995, "有效稅率": 0.1621, "終值佔比": 0.692}, "ri_pb": {"常態ROE": 0.0407, "股權成本r": 0.0867, "留存成長g": 0.0078, "合理PB": 0.417}, "ddm": {"DPS": 0.417, "g": 0.0081, "r": 0.0867}}</t>
         </is>
       </c>
     </row>
@@ -10002,10 +10002,10 @@
         </is>
       </c>
       <c r="C14" s="34" t="n">
-        <v>9.02</v>
+        <v>8.984999999999999</v>
       </c>
       <c r="D14" s="34" t="n">
-        <v>11.5457</v>
+        <v>11.5478</v>
       </c>
       <c r="E14" s="34" t="n">
         <v>14.7897</v>
@@ -10018,10 +10018,10 @@
         <v>24.6392</v>
       </c>
       <c r="I14" s="34" t="n">
-        <v>5.7686</v>
+        <v>5.7784</v>
       </c>
       <c r="J14" s="34" t="n">
-        <v>2.1405</v>
+        <v>2.1409</v>
       </c>
       <c r="K14" s="34" t="n">
         <v>4.1428</v>
@@ -10030,7 +10030,7 @@
         <v>8.955399999999999</v>
       </c>
       <c r="M14" s="34" t="n">
-        <v>6.37</v>
+        <v>6.36</v>
       </c>
       <c r="N14" s="34" t="n">
         <v>8.67</v>
@@ -10045,7 +10045,7 @@
       </c>
       <c r="Q14" s="33" t="inlineStr">
         <is>
-          <t>{"graham_number": {"EPS(3年均)": 0.6138, "BVPS": 11.6873}, "graham_formula": {"g(上限10%)": 0.1, "Y公司債": 0.056}, "ncav": {"NCAV/股": 0.0, "NNWC/股": -3.1735, "net-net買點": 0.0}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 19679000000.0, "g1": 0.0554, "永續g": 0.03, "門檻報酬r": 0.0905, "非營運投資(折70%)": 0.0}, "epv": {"常態營業利益率": 0.1543, "常態NOPAT": 11583868633.0, "WACC": 0.0637, "淨現金": -94737000000.0}, "damodaran_fcff": {"銷售/資本": 0.8, "g1": 0.029, "永續g": 0.03, "目標營業利益率": 0.1543, "WACC": 0.0637, "終值WACC": 0.0995, "有效稅率": 0.2453, "終值佔比": 0.524}, "ri_pb": {"常態ROE": 0.0366, "股權成本r": 0.0867, "留存成長g": 0.0147, "合理PB": 0.304}, "ddm": {"DPS": 0.4548, "g": 0.026, "r": 0.0867}}</t>
+          <t>{"graham_number": {"EPS(3年均)": 0.6138, "BVPS": 11.6873}, "graham_formula": {"g(上限10%)": 0.1, "Y公司債": 0.056}, "ncav": {"NCAV/股": 0.0, "NNWC/股": -3.1735, "net-net買點": 0.0}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 19679000000.0, "g1": 0.0554, "永續g": 0.03, "門檻報酬r": 0.0905, "非營運投資(折70%)": 0.0}, "epv": {"常態營業利益率": 0.1543, "常態NOPAT": 11583868633.0, "WACC": 0.0636, "淨現金": -94737000000.0}, "damodaran_fcff": {"銷售/資本": 0.8, "g1": 0.029, "永續g": 0.03, "目標營業利益率": 0.1543, "WACC": 0.0636, "終值WACC": 0.0995, "有效稅率": 0.2453, "終值佔比": 0.524}, "ri_pb": {"常態ROE": 0.0366, "股權成本r": 0.0867, "留存成長g": 0.0147, "合理PB": 0.304}, "ddm": {"DPS": 0.4548, "g": 0.026, "r": 0.0867}}</t>
         </is>
       </c>
     </row>
@@ -10061,7 +10061,7 @@
         </is>
       </c>
       <c r="C15" s="34" t="n">
-        <v>18.76</v>
+        <v>18.78</v>
       </c>
       <c r="D15" s="34" t="n">
         <v>53.4079</v>
@@ -10118,10 +10118,10 @@
         </is>
       </c>
       <c r="C16" s="34" t="n">
-        <v>9.91</v>
+        <v>9.994999999999999</v>
       </c>
       <c r="D16" s="34" t="n">
-        <v>22.9966</v>
+        <v>22.9934</v>
       </c>
       <c r="E16" s="34" t="n">
         <v>15.4965</v>
@@ -10134,10 +10134,10 @@
         <v>51.231</v>
       </c>
       <c r="I16" s="34" t="n">
-        <v>14.8296</v>
+        <v>14.8151</v>
       </c>
       <c r="J16" s="34" t="n">
-        <v>9.965</v>
+        <v>9.9642</v>
       </c>
       <c r="K16" s="34" t="n">
         <v>5.2489</v>
@@ -10177,10 +10177,10 @@
         </is>
       </c>
       <c r="C17" s="34" t="n">
-        <v>24.46</v>
+        <v>24.76</v>
       </c>
       <c r="D17" s="34" t="n">
-        <v>71.7371</v>
+        <v>71.7338</v>
       </c>
       <c r="E17" s="34" t="n">
         <v>37.787</v>
@@ -10195,10 +10195,10 @@
         <v>143.8576</v>
       </c>
       <c r="I17" s="34" t="n">
-        <v>41.7481</v>
+        <v>41.7297</v>
       </c>
       <c r="J17" s="34" t="n">
-        <v>41.3365</v>
+        <v>41.3348</v>
       </c>
       <c r="K17" s="34" t="n">
         <v>64.7799</v>
@@ -10238,7 +10238,7 @@
         </is>
       </c>
       <c r="C18" s="34" t="n">
-        <v>9.654999999999999</v>
+        <v>9.625</v>
       </c>
       <c r="D18" s="34" t="n">
         <v>130.7854</v>
@@ -10293,10 +10293,10 @@
         </is>
       </c>
       <c r="C19" s="34" t="n">
-        <v>79.2</v>
+        <v>79.25</v>
       </c>
       <c r="D19" s="34" t="n">
-        <v>89.6084</v>
+        <v>89.608</v>
       </c>
       <c r="E19" s="34" t="n">
         <v>114.0363</v>
@@ -10309,10 +10309,10 @@
         <v>92.48090000000001</v>
       </c>
       <c r="I19" s="34" t="n">
-        <v>87.05289999999999</v>
+        <v>87.05110000000001</v>
       </c>
       <c r="J19" s="34" t="n">
-        <v>77.8374</v>
+        <v>77.8373</v>
       </c>
       <c r="K19" s="34" t="n">
         <v>91.19410000000001</v>
@@ -10352,7 +10352,7 @@
         </is>
       </c>
       <c r="C20" s="34" t="n">
-        <v>5.315</v>
+        <v>5.27</v>
       </c>
       <c r="D20" s="34" t="n">
         <v>158.04</v>
@@ -10409,10 +10409,10 @@
         </is>
       </c>
       <c r="C21" s="34" t="n">
-        <v>61.45</v>
+        <v>61.35</v>
       </c>
       <c r="D21" s="34" t="n">
-        <v>6.9171</v>
+        <v>6.917</v>
       </c>
       <c r="E21" s="34" t="n">
         <v>19.1265</v>
@@ -10423,10 +10423,10 @@
       <c r="G21" s="34" t="inlineStr"/>
       <c r="H21" s="34" t="inlineStr"/>
       <c r="I21" s="34" t="n">
-        <v>10.413</v>
+        <v>10.4125</v>
       </c>
       <c r="J21" s="34" t="n">
-        <v>0.4889</v>
+        <v>0.4888</v>
       </c>
       <c r="K21" s="34" t="n">
         <v>3.7772</v>
@@ -10464,7 +10464,7 @@
         </is>
       </c>
       <c r="C22" s="34" t="n">
-        <v>32.04</v>
+        <v>31.94</v>
       </c>
       <c r="D22" s="34" t="n">
         <v>31.6387</v>
@@ -10480,7 +10480,7 @@
         <v>74.4907</v>
       </c>
       <c r="I22" s="34" t="n">
-        <v>16.8792</v>
+        <v>16.8789</v>
       </c>
       <c r="J22" s="34" t="n">
         <v>19.357</v>
@@ -10523,7 +10523,7 @@
         </is>
       </c>
       <c r="C23" s="34" t="n">
-        <v>7.495</v>
+        <v>7.505</v>
       </c>
       <c r="D23" s="34" t="n">
         <v>98.4873</v>
@@ -10578,10 +10578,10 @@
         </is>
       </c>
       <c r="C24" s="34" t="n">
-        <v>27.16</v>
+        <v>26.04</v>
       </c>
       <c r="D24" s="34" t="n">
-        <v>28.7613</v>
+        <v>28.765</v>
       </c>
       <c r="E24" s="34" t="n">
         <v>17.415</v>
@@ -10596,10 +10596,10 @@
         <v>32.0308</v>
       </c>
       <c r="I24" s="34" t="n">
-        <v>21.332</v>
+        <v>21.3535</v>
       </c>
       <c r="J24" s="34" t="n">
-        <v>26.4501</v>
+        <v>26.4515</v>
       </c>
       <c r="K24" s="34" t="n">
         <v>94.2072</v>
@@ -10608,7 +10608,7 @@
         <v>18.8996</v>
       </c>
       <c r="M24" s="34" t="n">
-        <v>9.550000000000001</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="N24" s="34" t="n">
         <v>9.949999999999999</v>
@@ -10623,7 +10623,7 @@
       </c>
       <c r="Q24" s="33" t="inlineStr">
         <is>
-          <t>{"graham_number": {"EPS(3年均)": 0.95, "BVPS": 10.47}, "graham_formula": {"g(上限10%)": 0.1, "Y公司債": 0.056}, "ncav": {"NCAV/股": 1.2249, "NNWC/股": -2.6098, "net-net買點": 0.817}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 32977230000.0, "g1": 0.0471, "永續g": 0.03, "門檻報酬r": 0.0905, "非營運投資(折70%)": 105737650200.0}, "epv": {"常態營業利益率": 0.0738, "常態NOPAT": 27114237928.0, "WACC": 0.0955, "淨現金": 82446791000.0}, "damodaran_fcff": {"銷售/資本": 2.34, "g1": 0.15, "永續g": 0.03, "目標營業利益率": 0.0738, "WACC": 0.0955, "終值WACC": 0.0995, "有效稅率": 0.1618, "終值佔比": 0.69}, "ri_pb": {"常態ROE": 0.1331, "股權成本r": 0.0995, "留存成長g": 0.0945, "合理PB": 7.729}, "ddm": {"DPS": 0.149, "g": 0.0895, "r": 0.0995}}</t>
+          <t>{"graham_number": {"EPS(3年均)": 0.95, "BVPS": 10.47}, "graham_formula": {"g(上限10%)": 0.1, "Y公司債": 0.056}, "ncav": {"NCAV/股": 1.2249, "NNWC/股": -2.6098, "net-net買點": 0.817}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 32977230000.0, "g1": 0.0471, "永續g": 0.03, "門檻報酬r": 0.0905, "非營運投資(折70%)": 105737650200.0}, "epv": {"常態營業利益率": 0.0738, "常態NOPAT": 27114237928.0, "WACC": 0.0954, "淨現金": 82446791000.0}, "damodaran_fcff": {"銷售/資本": 2.34, "g1": 0.15, "永續g": 0.03, "目標營業利益率": 0.0738, "WACC": 0.0954, "終值WACC": 0.0995, "有效稅率": 0.1618, "終值佔比": 0.69}, "ri_pb": {"常態ROE": 0.1331, "股權成本r": 0.0995, "留存成長g": 0.0945, "合理PB": 7.729}, "ddm": {"DPS": 0.149, "g": 0.0895, "r": 0.0995}}</t>
         </is>
       </c>
     </row>
@@ -10639,7 +10639,7 @@
         </is>
       </c>
       <c r="C25" s="34" t="n">
-        <v>3.015</v>
+        <v>3.04</v>
       </c>
       <c r="D25" s="34" t="n">
         <v>2.3155</v>
@@ -10696,7 +10696,7 @@
         </is>
       </c>
       <c r="C26" s="34" t="n">
-        <v>0.171</v>
+        <v>0.17</v>
       </c>
       <c r="D26" s="34" t="inlineStr"/>
       <c r="E26" s="34" t="inlineStr"/>
@@ -10739,7 +10739,7 @@
         </is>
       </c>
       <c r="C27" s="34" t="n">
-        <v>53.5</v>
+        <v>53.05</v>
       </c>
       <c r="D27" s="34" t="n">
         <v>699.6943</v>
@@ -10796,34 +10796,34 @@
         </is>
       </c>
       <c r="C28" s="34" t="n">
-        <v>196</v>
+        <v>196.8</v>
       </c>
       <c r="D28" s="34" t="n">
-        <v>103.1559</v>
+        <v>103.1534</v>
       </c>
       <c r="E28" s="34" t="n">
-        <v>55.4236</v>
+        <v>55.423</v>
       </c>
       <c r="F28" s="34" t="n">
         <v>94.8874</v>
       </c>
       <c r="G28" s="34" t="n">
-        <v>15.7621</v>
+        <v>15.7617</v>
       </c>
       <c r="H28" s="34" t="n">
-        <v>111.9693</v>
+        <v>111.9667</v>
       </c>
       <c r="I28" s="34" t="n">
-        <v>66.46680000000001</v>
+        <v>66.4631</v>
       </c>
       <c r="J28" s="34" t="n">
-        <v>79.17059999999999</v>
+        <v>79.1686</v>
       </c>
       <c r="K28" s="34" t="n">
-        <v>469.0368</v>
+        <v>469.0262</v>
       </c>
       <c r="L28" s="34" t="n">
-        <v>242.0665</v>
+        <v>242.0611</v>
       </c>
       <c r="M28" s="34" t="n">
         <v>9.84</v>
@@ -10841,7 +10841,7 @@
       </c>
       <c r="Q28" s="33" t="inlineStr">
         <is>
-          <t>{"graham_number": {"EPS(3年均)": 3.64, "BVPS": 27.6764}, "graham_formula": {"g(上限10%)": 0.1, "Y公司債": 0.056}, "ncav": {"NCAV/股": 13.5399, "NNWC/股": 9.3465, "net-net買點": 9.0311}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 10129371000.0, "g1": 0.15, "永續g": 0.03, "門檻報酬r": 0.0905, "非營運投資(折70%)": 7476415100.0}, "epv": {"常態營業利益率": 0.2922, "常態NOPAT": 12432745411.0, "WACC": 0.0984, "淨現金": 38088875000.0}, "damodaran_fcff": {"銷售/資本": 1.184, "g1": 0.0492, "永續g": 0.03, "目標營業利益率": 0.2922, "WACC": 0.0984, "終值WACC": 0.0995, "有效稅率": 0.2054, "終值佔比": 0.493}, "ri_pb": {"常態ROE": 0.1673, "股權成本r": 0.0995, "留存成長g": 0.0945, "合理PB": 14.558}, "ddm": {"DPS": 1.9086, "g": 0.0895, "r": 0.0995}}</t>
+          <t>{"graham_number": {"EPS(3年均)": 3.64, "BVPS": 27.6758}, "graham_formula": {"g(上限10%)": 0.1, "Y公司債": 0.056}, "ncav": {"NCAV/股": 13.5396, "NNWC/股": 9.3462, "net-net買點": 9.0309}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 10129371000.0, "g1": 0.15, "永續g": 0.03, "門檻報酬r": 0.0905, "非營運投資(折70%)": 7476415100.0}, "epv": {"常態營業利益率": 0.2922, "常態NOPAT": 12432745411.0, "WACC": 0.0984, "淨現金": 38088875000.0}, "damodaran_fcff": {"銷售/資本": 1.184, "g1": 0.0492, "永續g": 0.03, "目標營業利益率": 0.2922, "WACC": 0.0984, "終值WACC": 0.0995, "有效稅率": 0.2054, "終值佔比": 0.493}, "ri_pb": {"常態ROE": 0.1673, "股權成本r": 0.0995, "留存成長g": 0.0945, "合理PB": 14.558}, "ddm": {"DPS": 1.9085, "g": 0.0895, "r": 0.0995}}</t>
         </is>
       </c>
     </row>
@@ -10857,7 +10857,7 @@
         </is>
       </c>
       <c r="C29" s="34" t="n">
-        <v>3.295</v>
+        <v>3.325</v>
       </c>
       <c r="D29" s="34" t="n">
         <v>13.2428</v>
@@ -10875,7 +10875,7 @@
         <v>6.861</v>
       </c>
       <c r="I29" s="34" t="n">
-        <v>7.7544</v>
+        <v>7.7541</v>
       </c>
       <c r="J29" s="34" t="n">
         <v>11.2318</v>
@@ -10918,10 +10918,10 @@
         </is>
       </c>
       <c r="C30" s="34" t="n">
-        <v>48.72</v>
+        <v>50.4</v>
       </c>
       <c r="D30" s="34" t="n">
-        <v>84.23309999999999</v>
+        <v>84.1023</v>
       </c>
       <c r="E30" s="34" t="n">
         <v>83.2593</v>
@@ -10934,10 +10934,10 @@
         <v>55.5251</v>
       </c>
       <c r="I30" s="34" t="n">
-        <v>114.4024</v>
+        <v>113.8003</v>
       </c>
       <c r="J30" s="34" t="n">
-        <v>84.4123</v>
+        <v>84.3797</v>
       </c>
       <c r="K30" s="34" t="n">
         <v>165.9242</v>
@@ -10946,7 +10946,7 @@
         <v>106.0289</v>
       </c>
       <c r="M30" s="34" t="n">
-        <v>7.09</v>
+        <v>7.13</v>
       </c>
       <c r="N30" s="34" t="n">
         <v>8.67</v>
@@ -10961,7 +10961,7 @@
       </c>
       <c r="Q30" s="33" t="inlineStr">
         <is>
-          <t>{"graham_number": {"EPS(3年均)": 5.35, "BVPS": 42.4945}, "graham_formula": {"g(上限10%)": -0.0102, "Y公司債": 0.056}, "ncav": {"NCAV/股": 0.0, "NNWC/股": -31.3139, "net-net買點": 0.0}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 3560000000.0, "g1": -0.05, "永續g": 0.03, "門檻報酬r": 0.0905, "非營運投資(折70%)": 10906000000.0}, "epv": {"常態營業利益率": 0.0881, "常態NOPAT": 7889920905.0, "WACC": 0.071, "淨現金": -10879000000.0}, "damodaran_fcff": {"銷售/資本": 1.92, "g1": 0.0056, "永續g": 0.03, "目標營業利益率": 0.0881, "WACC": 0.071, "終值WACC": 0.0995, "有效稅率": 0.2095, "終值佔比": 0.458}, "ri_pb": {"常態ROE": 0.155, "股權成本r": 0.0867, "留存成長g": 0.0577, "合理PB": 3.354}, "ddm": {"DPS": 3.4077, "g": 0.0475, "r": 0.0867}}</t>
+          <t>{"graham_number": {"EPS(3年均)": 5.35, "BVPS": 42.4945}, "graham_formula": {"g(上限10%)": -0.0102, "Y公司債": 0.056}, "ncav": {"NCAV/股": 0.0, "NNWC/股": -31.3139, "net-net買點": 0.0}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 3560000000.0, "g1": -0.05, "永續g": 0.03, "門檻報酬r": 0.0905, "非營運投資(折70%)": 10906000000.0}, "epv": {"常態營業利益率": 0.0881, "常態NOPAT": 7889920905.0, "WACC": 0.0713, "淨現金": -10879000000.0}, "damodaran_fcff": {"銷售/資本": 1.92, "g1": 0.0056, "永續g": 0.03, "目標營業利益率": 0.0881, "WACC": 0.0713, "終值WACC": 0.0995, "有效稅率": 0.2095, "終值佔比": 0.458}, "ri_pb": {"常態ROE": 0.155, "股權成本r": 0.0867, "留存成長g": 0.0577, "合理PB": 3.354}, "ddm": {"DPS": 3.4077, "g": 0.0475, "r": 0.0867}}</t>
         </is>
       </c>
     </row>
@@ -10977,7 +10977,7 @@
         </is>
       </c>
       <c r="C31" s="34" t="n">
-        <v>75.45</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="D31" s="34" t="n">
         <v>13.9617</v>
@@ -11001,7 +11001,7 @@
       </c>
       <c r="L31" s="34" t="inlineStr"/>
       <c r="M31" s="34" t="n">
-        <v>12.12</v>
+        <v>12.14</v>
       </c>
       <c r="N31" s="34" t="n">
         <v>10.91</v>
@@ -11032,10 +11032,10 @@
         </is>
       </c>
       <c r="C32" s="34" t="n">
-        <v>542</v>
+        <v>492.2</v>
       </c>
       <c r="D32" s="34" t="n">
-        <v>382.6044</v>
+        <v>382.8678</v>
       </c>
       <c r="E32" s="34" t="n">
         <v>170.1471</v>
@@ -11050,10 +11050,10 @@
         <v>309.2126</v>
       </c>
       <c r="I32" s="34" t="n">
-        <v>214.207</v>
+        <v>215.3843</v>
       </c>
       <c r="J32" s="34" t="n">
-        <v>266.5657</v>
+        <v>266.6822</v>
       </c>
       <c r="K32" s="34" t="n">
         <v>2201.7699</v>
@@ -11062,7 +11062,7 @@
         <v>1178.879</v>
       </c>
       <c r="M32" s="34" t="n">
-        <v>9.279999999999999</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="N32" s="34" t="n">
         <v>9.949999999999999</v>
@@ -11077,7 +11077,7 @@
       </c>
       <c r="Q32" s="33" t="inlineStr">
         <is>
-          <t>{"graham_number": {"EPS(3年均)": 11.58, "BVPS": 81.9903}, "graham_formula": {"g(上限10%)": 0.03, "Y公司債": 0.056}, "ncav": {"NCAV/股": 7.3385, "NNWC/股": -39.3806, "net-net買點": 4.8948}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 65810402000.0, "g1": 0.05, "永續g": 0.03, "門檻報酬r": 0.0905, "非營運投資(折70%)": 10748265500.0}, "epv": {"常態營業利益率": 0.1491, "常態NOPAT": 66831915950.0, "WACC": 0.0928, "淨現金": 120569062000.0}, "damodaran_fcff": {"銷售/資本": 2.016, "g1": 0.0884, "永續g": 0.03, "目標營業利益率": 0.1491, "WACC": 0.0928, "終值WACC": 0.0995, "有效稅率": 0.1411, "終值佔比": 0.53}, "ri_pb": {"常態ROE": 0.2098, "股權成本r": 0.0995, "留存成長g": 0.0945, "合理PB": 23.068}, "ddm": {"DPS": 9.2949, "g": 0.0895, "r": 0.0995}}</t>
+          <t>{"graham_number": {"EPS(3年均)": 11.58, "BVPS": 81.9903}, "graham_formula": {"g(上限10%)": 0.03, "Y公司債": 0.056}, "ncav": {"NCAV/股": 7.3385, "NNWC/股": -39.3806, "net-net買點": 4.8948}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 65810402000.0, "g1": 0.05, "永續g": 0.03, "門檻報酬r": 0.0905, "非營運投資(折70%)": 10748265500.0}, "epv": {"常態營業利益率": 0.1491, "常態NOPAT": 66831915950.0, "WACC": 0.0922, "淨現金": 120569062000.0}, "damodaran_fcff": {"銷售/資本": 2.016, "g1": 0.0884, "永續g": 0.03, "目標營業利益率": 0.1491, "WACC": 0.0922, "終值WACC": 0.0995, "有效稅率": 0.1411, "終值佔比": 0.529}, "ri_pb": {"常態ROE": 0.2098, "股權成本r": 0.0995, "留存成長g": 0.0945, "合理PB": 23.068}, "ddm": {"DPS": 9.2949, "g": 0.0895, "r": 0.0995}}</t>
         </is>
       </c>
     </row>
@@ -11093,7 +11093,7 @@
         </is>
       </c>
       <c r="C33" s="34" t="n">
-        <v>51.45</v>
+        <v>51.25</v>
       </c>
       <c r="D33" s="34" t="n">
         <v>588.5381</v>
@@ -11148,10 +11148,10 @@
         </is>
       </c>
       <c r="C34" s="34" t="n">
-        <v>4.3</v>
+        <v>4.215</v>
       </c>
       <c r="D34" s="34" t="n">
-        <v>8.3028</v>
+        <v>8.303100000000001</v>
       </c>
       <c r="E34" s="34" t="n">
         <v>3.8731</v>
@@ -11166,10 +11166,10 @@
         <v>14.7347</v>
       </c>
       <c r="I34" s="34" t="n">
-        <v>4.4187</v>
+        <v>4.4207</v>
       </c>
       <c r="J34" s="34" t="n">
-        <v>7.0634</v>
+        <v>7.0636</v>
       </c>
       <c r="K34" s="34" t="n">
         <v>3.6595</v>
@@ -11209,10 +11209,10 @@
         </is>
       </c>
       <c r="C35" s="34" t="n">
-        <v>21.58</v>
+        <v>21.14</v>
       </c>
       <c r="D35" s="34" t="n">
-        <v>12.2091</v>
+        <v>12.2115</v>
       </c>
       <c r="E35" s="34" t="n">
         <v>14.9173</v>
@@ -11225,10 +11225,10 @@
         <v>23.633</v>
       </c>
       <c r="I35" s="34" t="n">
-        <v>8.0388</v>
+        <v>8.0512</v>
       </c>
       <c r="J35" s="34" t="n">
-        <v>6.6242</v>
+        <v>6.6237</v>
       </c>
       <c r="K35" s="34" t="n">
         <v>6.5099</v>
@@ -11237,7 +11237,7 @@
         <v>6.201</v>
       </c>
       <c r="M35" s="34" t="n">
-        <v>10.14</v>
+        <v>10.12</v>
       </c>
       <c r="N35" s="34" t="n">
         <v>10.91</v>
@@ -11252,7 +11252,7 @@
       </c>
       <c r="Q35" s="33" t="inlineStr">
         <is>
-          <t>{"graham_number": {"EPS(3年均)": 0.73, "BVPS": 9.9973}, "graham_formula": {"g(上限10%)": 0.03, "Y公司債": 0.056}, "ncav": {"NCAV/股": 0.0, "NNWC/股": -2.5412, "net-net買點": 0.0}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 5736271000.0, "g1": 0.05, "永續g": 0.03, "門檻報酬r": 0.0905, "非營運投資(折70%)": 980000000.0}, "epv": {"常態營業利益率": 0.0675, "常態NOPAT": 3992648994.0, "WACC": 0.1014, "淨現金": -3912000000.0}, "damodaran_fcff": {"銷售/資本": 1.24, "g1": 0.15, "永續g": 0.03, "目標營業利益率": 0.0675, "WACC": 0.1014, "終值WACC": 0.0995, "有效稅率": 0.1589, "終值佔比": 1.223}, "ri_pb": {"常態ROE": 0.0691, "股權成本r": 0.1091, "留存成長g": 0.0183, "合理PB": 0.559}, "ddm": {"DPS": 0.4803, "g": 0.0174, "r": 0.1091}}</t>
+          <t>{"graham_number": {"EPS(3年均)": 0.73, "BVPS": 9.9973}, "graham_formula": {"g(上限10%)": 0.03, "Y公司債": 0.056}, "ncav": {"NCAV/股": 0.0, "NNWC/股": -2.5412, "net-net買點": 0.0}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 5736271000.0, "g1": 0.05, "永續g": 0.03, "門檻報酬r": 0.0905, "非營運投資(折70%)": 980000000.0}, "epv": {"常態營業利益率": 0.0675, "常態NOPAT": 3992648994.0, "WACC": 0.1012, "淨現金": -3912000000.0}, "damodaran_fcff": {"銷售/資本": 1.24, "g1": 0.15, "永續g": 0.03, "目標營業利益率": 0.0675, "WACC": 0.1012, "終值WACC": 0.0995, "有效稅率": 0.1589, "終值佔比": 1.223}, "ri_pb": {"常態ROE": 0.0691, "股權成本r": 0.1091, "留存成長g": 0.0183, "合理PB": 0.559}, "ddm": {"DPS": 0.4803, "g": 0.0174, "r": 0.1091}}</t>
         </is>
       </c>
     </row>
@@ -11268,10 +11268,10 @@
         </is>
       </c>
       <c r="C36" s="34" t="n">
-        <v>106.3</v>
+        <v>105.2</v>
       </c>
       <c r="D36" s="34" t="n">
-        <v>136.1812</v>
+        <v>136.1718</v>
       </c>
       <c r="E36" s="34" t="n">
         <v>135.02</v>
@@ -11284,10 +11284,10 @@
         <v>245.8763</v>
       </c>
       <c r="I36" s="34" t="n">
-        <v>129.2918</v>
+        <v>129.2469</v>
       </c>
       <c r="J36" s="34" t="n">
-        <v>98.4572</v>
+        <v>98.456</v>
       </c>
       <c r="K36" s="34" t="n">
         <v>54.4545</v>
@@ -11296,7 +11296,7 @@
         <v>55.116</v>
       </c>
       <c r="M36" s="34" t="n">
-        <v>10.75</v>
+        <v>10.76</v>
       </c>
       <c r="N36" s="34" t="n">
         <v>9.949999999999999</v>
@@ -11311,7 +11311,7 @@
       </c>
       <c r="Q36" s="33" t="inlineStr">
         <is>
-          <t>{"graham_number": {"EPS(3年均)": 7.69, "BVPS": 77.7484}, "graham_formula": {"g(上限10%)": -0.1587, "Y公司債": 0.056}, "ncav": {"NCAV/股": 0.0, "NNWC/股": -50.5795, "net-net買點": 0.0}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 49191000000.0, "g1": -0.05, "永續g": 0.03, "門檻報酬r": 0.0905, "非營運投資(折70%)": 0.0}, "epv": {"常態營業利益率": 0.0189, "常態NOPAT": 21147865283.0, "WACC": 0.1075, "淨現金": 116354000000.0}, "damodaran_fcff": {"銷售/資本": 4.0, "g1": 0.0776, "永續g": 0.03, "目標營業利益率": 0.0189, "WACC": 0.1075, "終值WACC": 0.0995, "有效稅率": 0.1459, "終值佔比": 0.828}, "ri_pb": {"常態ROE": 0.0679, "股權成本r": 0.0995, "留存成長g": 0.0203, "合理PB": 0.602}, "ddm": {"DPS": 3.6827, "g": 0.0201, "r": 0.0995}}</t>
+          <t>{"graham_number": {"EPS(3年均)": 7.69, "BVPS": 77.7484}, "graham_formula": {"g(上限10%)": -0.1587, "Y公司債": 0.056}, "ncav": {"NCAV/股": 0.0, "NNWC/股": -50.5795, "net-net買點": 0.0}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 49191000000.0, "g1": -0.05, "永續g": 0.03, "門檻報酬r": 0.0905, "非營運投資(折70%)": 0.0}, "epv": {"常態營業利益率": 0.0189, "常態NOPAT": 21147865283.0, "WACC": 0.1076, "淨現金": 116354000000.0}, "damodaran_fcff": {"銷售/資本": 4.0, "g1": 0.0776, "永續g": 0.03, "目標營業利益率": 0.0189, "WACC": 0.1076, "終值WACC": 0.0995, "有效稅率": 0.1459, "終值佔比": 0.828}, "ri_pb": {"常態ROE": 0.0679, "股權成本r": 0.0995, "留存成長g": 0.0203, "合理PB": 0.602}, "ddm": {"DPS": 3.6827, "g": 0.0201, "r": 0.0995}}</t>
         </is>
       </c>
     </row>
@@ -11327,10 +11327,10 @@
         </is>
       </c>
       <c r="C37" s="34" t="n">
-        <v>308</v>
+        <v>303.6</v>
       </c>
       <c r="D37" s="34" t="n">
-        <v>430.8789</v>
+        <v>430.9458</v>
       </c>
       <c r="E37" s="34" t="n">
         <v>428.4491</v>
@@ -11345,10 +11345,10 @@
         <v>572.925</v>
       </c>
       <c r="I37" s="34" t="n">
-        <v>322.1885</v>
+        <v>322.4943</v>
       </c>
       <c r="J37" s="34" t="n">
-        <v>427.3591</v>
+        <v>427.3832</v>
       </c>
       <c r="K37" s="34" t="n">
         <v>40.2781</v>
@@ -11357,7 +11357,7 @@
         <v>252.0972</v>
       </c>
       <c r="M37" s="34" t="n">
-        <v>9.029999999999999</v>
+        <v>9.02</v>
       </c>
       <c r="N37" s="34" t="n">
         <v>9.949999999999999</v>
@@ -11372,7 +11372,7 @@
       </c>
       <c r="Q37" s="33" t="inlineStr">
         <is>
-          <t>{"graham_number": {"EPS(3年均)": 26.1, "BVPS": 230.6641}, "graham_formula": {"g(上限10%)": 0.1, "Y公司債": 0.056}, "ncav": {"NCAV/股": 37.4485, "NNWC/股": -4.5445, "net-net買點": 24.9782}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 19034000000.0, "g1": 0.05, "永續g": 0.03, "門檻報酬r": 0.0905, "非營運投資(折70%)": 0.0}, "epv": {"常態營業利益率": 0.2756, "常態NOPAT": 13408699793.0, "WACC": 0.0903, "淨現金": 49645000000.0}, "damodaran_fcff": {"銷售/資本": 0.8, "g1": 0.15, "永續g": 0.03, "目標營業利益率": 0.2756, "WACC": 0.0903, "終值WACC": 0.0995, "有效稅率": 0.1611, "終值佔比": 0.631}, "ri_pb": {"常態ROE": 0.0403, "股權成本r": 0.0995, "留存成長g": 0.0385, "合理PB": 0.15}, "ddm": {"DPS": 1.9877, "g": 0.0895, "r": 0.0995}}</t>
+          <t>{"graham_number": {"EPS(3年均)": 26.1, "BVPS": 230.6641}, "graham_formula": {"g(上限10%)": 0.1, "Y公司債": 0.056}, "ncav": {"NCAV/股": 37.4485, "NNWC/股": -4.5445, "net-net買點": 24.9782}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 19034000000.0, "g1": 0.05, "永續g": 0.03, "門檻報酬r": 0.0905, "非營運投資(折70%)": 0.0}, "epv": {"常態營業利益率": 0.2756, "常態NOPAT": 13408699793.0, "WACC": 0.0902, "淨現金": 49645000000.0}, "damodaran_fcff": {"銷售/資本": 0.8, "g1": 0.15, "永續g": 0.03, "目標營業利益率": 0.2756, "WACC": 0.0902, "終值WACC": 0.0995, "有效稅率": 0.1611, "終值佔比": 0.631}, "ri_pb": {"常態ROE": 0.0403, "股權成本r": 0.0995, "留存成長g": 0.0385, "合理PB": 0.15}, "ddm": {"DPS": 1.9877, "g": 0.0895, "r": 0.0995}}</t>
         </is>
       </c>
     </row>
@@ -11388,10 +11388,10 @@
         </is>
       </c>
       <c r="C38" s="34" t="n">
-        <v>106.7</v>
+        <v>106.6</v>
       </c>
       <c r="D38" s="34" t="n">
-        <v>68.1771</v>
+        <v>68.1778</v>
       </c>
       <c r="E38" s="34" t="n">
         <v>96.09999999999999</v>
@@ -11404,10 +11404,10 @@
         <v>85.75449999999999</v>
       </c>
       <c r="I38" s="34" t="n">
-        <v>63.9875</v>
+        <v>63.9907</v>
       </c>
       <c r="J38" s="34" t="n">
-        <v>61.5719</v>
+        <v>61.5721</v>
       </c>
       <c r="K38" s="34" t="n">
         <v>58.5967</v>
@@ -11447,10 +11447,10 @@
         </is>
       </c>
       <c r="C39" s="34" t="n">
-        <v>187.2</v>
+        <v>183.8</v>
       </c>
       <c r="D39" s="34" t="n">
-        <v>300.1348</v>
+        <v>300.141</v>
       </c>
       <c r="E39" s="34" t="n">
         <v>121.3865</v>
@@ -11465,10 +11465,10 @@
         <v>378.6999</v>
       </c>
       <c r="I39" s="34" t="n">
-        <v>153.3619</v>
+        <v>153.3892</v>
       </c>
       <c r="J39" s="34" t="n">
-        <v>184.6525</v>
+        <v>184.6558</v>
       </c>
       <c r="K39" s="34" t="n">
         <v>1407.6936</v>
@@ -11508,10 +11508,10 @@
         </is>
       </c>
       <c r="C40" s="34" t="n">
-        <v>84.58</v>
+        <v>83.75</v>
       </c>
       <c r="D40" s="34" t="n">
-        <v>126.3725</v>
+        <v>126.3758</v>
       </c>
       <c r="E40" s="34" t="n">
         <v>53.8044</v>
@@ -11526,10 +11526,10 @@
         <v>147.8206</v>
       </c>
       <c r="I40" s="34" t="n">
-        <v>67.53319999999999</v>
+        <v>67.5508</v>
       </c>
       <c r="J40" s="34" t="n">
-        <v>108.1128</v>
+        <v>108.1147</v>
       </c>
       <c r="K40" s="34" t="n">
         <v>403.9189</v>
@@ -11569,10 +11569,10 @@
         </is>
       </c>
       <c r="C41" s="34" t="n">
-        <v>159.68</v>
+        <v>158.92</v>
       </c>
       <c r="D41" s="34" t="n">
-        <v>200.3015</v>
+        <v>200.3016</v>
       </c>
       <c r="E41" s="34" t="n">
         <v>84.8402</v>
@@ -11587,7 +11587,7 @@
         <v>124.1863</v>
       </c>
       <c r="I41" s="34" t="n">
-        <v>116.6307</v>
+        <v>116.6312</v>
       </c>
       <c r="J41" s="34" t="n">
         <v>134.5588</v>
@@ -11630,7 +11630,7 @@
         </is>
       </c>
       <c r="C42" s="34" t="n">
-        <v>43.26</v>
+        <v>43.22</v>
       </c>
       <c r="D42" s="34" t="n">
         <v>28.4781</v>
@@ -11651,7 +11651,7 @@
         <v>16.153</v>
       </c>
       <c r="J42" s="34" t="n">
-        <v>22.6237</v>
+        <v>22.6238</v>
       </c>
       <c r="K42" s="34" t="n">
         <v>171.9871</v>
@@ -11691,10 +11691,10 @@
         </is>
       </c>
       <c r="C43" s="34" t="n">
-        <v>118.28</v>
+        <v>116.82</v>
       </c>
       <c r="D43" s="34" t="n">
-        <v>50.5519</v>
+        <v>50.5532</v>
       </c>
       <c r="E43" s="34" t="n">
         <v>50.2832</v>
@@ -11709,10 +11709,10 @@
         <v>38.8126</v>
       </c>
       <c r="I43" s="34" t="n">
-        <v>46.6192</v>
+        <v>46.625</v>
       </c>
       <c r="J43" s="34" t="n">
-        <v>50.2374</v>
+        <v>50.2379</v>
       </c>
       <c r="K43" s="34" t="n">
         <v>57.5582</v>
@@ -11736,7 +11736,7 @@
       </c>
       <c r="Q43" s="33" t="inlineStr">
         <is>
-          <t>{"graham_number": {"EPS(3年均)": 4.64, "BVPS": 24.2184}, "graham_formula": {"g(上限10%)": 0.0526, "Y公司債": 0.04}, "ncav": {"NCAV/股": 12.9157, "NNWC/股": 4.1254, "net-net買點": 8.6148}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 1248793852.0, "g1": 0.0526, "永續g": 0.021, "門檻報酬r": 0.085, "非營運投資(折70%)": 680214571.0}, "epv": {"常態營業利益率": 0.3374, "常態NOPAT": 2321531655.0, "WACC": 0.0881, "淨現金": 1080366024.0}, "damodaran_fcff": {"銷售/資本": 0.8, "g1": 0.0117, "永續g": 0.021, "目標營業利益率": 0.3374, "WACC": 0.0881, "終值WACC": 0.089, "有效稅率": 0.1604, "終值佔比": 0.485}, "ri_pb": {"常態ROE": 0.2115, "股權成本r": 0.089, "留存成長g": 0.0, "合理PB": 2.377}, "ddm": {"DPS": 3.2624, "g": 0.0061, "r": 0.089}}</t>
+          <t>{"graham_number": {"EPS(3年均)": 4.64, "BVPS": 24.2184}, "graham_formula": {"g(上限10%)": 0.0526, "Y公司債": 0.04}, "ncav": {"NCAV/股": 12.9157, "NNWC/股": 4.1254, "net-net買點": 8.6148}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 1248793852.0, "g1": 0.0526, "永續g": 0.021, "門檻報酬r": 0.085, "非營運投資(折70%)": 680214571.0}, "epv": {"常態營業利益率": 0.3374, "常態NOPAT": 2321531655.0, "WACC": 0.088, "淨現金": 1080366024.0}, "damodaran_fcff": {"銷售/資本": 0.8, "g1": 0.0117, "永續g": 0.021, "目標營業利益率": 0.3374, "WACC": 0.088, "終值WACC": 0.089, "有效稅率": 0.1604, "終值佔比": 0.485}, "ri_pb": {"常態ROE": 0.2115, "股權成本r": 0.089, "留存成長g": 0.0, "合理PB": 2.377}, "ddm": {"DPS": 3.2624, "g": 0.0061, "r": 0.089}}</t>
         </is>
       </c>
     </row>
@@ -11752,10 +11752,10 @@
         </is>
       </c>
       <c r="C44" s="34" t="n">
-        <v>1276.81</v>
+        <v>1264.75</v>
       </c>
       <c r="D44" s="34" t="n">
-        <v>1186.8346</v>
+        <v>1186.8348</v>
       </c>
       <c r="E44" s="34" t="n">
         <v>544.9149</v>
@@ -11770,10 +11770,10 @@
         <v>869.8927</v>
       </c>
       <c r="I44" s="34" t="n">
-        <v>838.7845</v>
+        <v>838.7854</v>
       </c>
       <c r="J44" s="34" t="n">
-        <v>1283.6282</v>
+        <v>1283.6283</v>
       </c>
       <c r="K44" s="34" t="n">
         <v>2189.9672</v>
@@ -11813,10 +11813,10 @@
         </is>
       </c>
       <c r="C45" s="34" t="n">
-        <v>28.5</v>
+        <v>28.36</v>
       </c>
       <c r="D45" s="34" t="n">
-        <v>20.5648</v>
+        <v>20.5689</v>
       </c>
       <c r="E45" s="34" t="n">
         <v>16.2467</v>
@@ -11829,10 +11829,10 @@
         <v>31.8328</v>
       </c>
       <c r="I45" s="34" t="n">
-        <v>15.5879</v>
+        <v>15.6067</v>
       </c>
       <c r="J45" s="34" t="n">
-        <v>12.7737</v>
+        <v>12.7745</v>
       </c>
       <c r="K45" s="34" t="n">
         <v>22.7622</v>
@@ -11841,7 +11841,7 @@
         <v>25.8636</v>
       </c>
       <c r="M45" s="34" t="n">
-        <v>5.64</v>
+        <v>5.63</v>
       </c>
       <c r="N45" s="34" t="n">
         <v>6.86</v>
@@ -11856,7 +11856,7 @@
       </c>
       <c r="Q45" s="33" t="inlineStr">
         <is>
-          <t>{"graham_number": {"EPS(3年均)": 1.3281, "BVPS": 8.8331}, "graham_formula": {"g(上限10%)": 0.0353, "Y公司債": 0.04}, "ncav": {"NCAV/股": 0.0, "NNWC/股": -12.9023, "net-net買點": 0.0}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 45014393233.0, "g1": 0.0238, "永續g": 0.021, "門檻報酬r": 0.085, "非營運投資(折70%)": 52328014359.0}, "epv": {"常態營業利益率": 0.4692, "常態NOPAT": 34008540377.0, "WACC": 0.0564, "淨現金": -273993253986.0}, "damodaran_fcff": {"銷售/資本": 0.8, "g1": 0.0779, "永續g": 0.021, "目標營業利益率": 0.4692, "WACC": 0.0564, "終值WACC": 0.089, "有效稅率": 0.1714, "終值佔比": 0.521}, "ri_pb": {"常態ROE": 0.1553, "股權成本r": 0.0686, "留存成長g": 0.0136, "合理PB": 2.577}, "ddm": {"DPS": 1.3682, "g": 0.0149, "r": 0.0686}}</t>
+          <t>{"graham_number": {"EPS(3年均)": 1.3281, "BVPS": 8.8331}, "graham_formula": {"g(上限10%)": 0.0353, "Y公司債": 0.04}, "ncav": {"NCAV/股": 0.0, "NNWC/股": -12.9023, "net-net買點": 0.0}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 45014393233.0, "g1": 0.0238, "永續g": 0.021, "門檻報酬r": 0.085, "非營運投資(折70%)": 52328014359.0}, "epv": {"常態營業利益率": 0.4692, "常態NOPAT": 34008540377.0, "WACC": 0.0563, "淨現金": -273993253986.0}, "damodaran_fcff": {"銷售/資本": 0.8, "g1": 0.0779, "永續g": 0.021, "目標營業利益率": 0.4692, "WACC": 0.0563, "終值WACC": 0.089, "有效稅率": 0.1714, "終值佔比": 0.521}, "ri_pb": {"常態ROE": 0.1553, "股權成本r": 0.0686, "留存成長g": 0.0136, "合理PB": 2.577}, "ddm": {"DPS": 1.3682, "g": 0.0149, "r": 0.0686}}</t>
         </is>
       </c>
     </row>
@@ -11872,10 +11872,10 @@
         </is>
       </c>
       <c r="C46" s="34" t="n">
-        <v>61.82</v>
+        <v>60.94</v>
       </c>
       <c r="D46" s="34" t="n">
-        <v>35.7611</v>
+        <v>35.7648</v>
       </c>
       <c r="E46" s="34" t="n">
         <v>15.2693</v>
@@ -11890,10 +11890,10 @@
         <v>25.7507</v>
       </c>
       <c r="I46" s="34" t="n">
-        <v>25.558</v>
+        <v>25.5798</v>
       </c>
       <c r="J46" s="34" t="n">
-        <v>36.6872</v>
+        <v>36.6885</v>
       </c>
       <c r="K46" s="34" t="n">
         <v>164.8877</v>
@@ -11902,7 +11902,7 @@
         <v>130.8639</v>
       </c>
       <c r="M46" s="34" t="n">
-        <v>8.369999999999999</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="N46" s="34" t="n">
         <v>8.9</v>
@@ -11917,7 +11917,7 @@
       </c>
       <c r="Q46" s="33" t="inlineStr">
         <is>
-          <t>{"graham_number": {"EPS(3年均)": 1.17, "BVPS": 8.8567}, "graham_formula": {"g(上限10%)": 0.1, "Y公司債": 0.04}, "ncav": {"NCAV/股": 6.0294, "NNWC/股": -2.245, "net-net買點": 4.0216}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 18769275000.0, "g1": 0.15, "永續g": 0.021, "門檻報酬r": 0.085, "非營運投資(折70%)": 3053026900.0}, "epv": {"常態營業利益率": 0.0455, "常態NOPAT": 42806605742.0, "WACC": 0.0837, "淨現金": -7517740000.0}, "damodaran_fcff": {"銷售/資本": 4.0, "g1": 0.15, "永續g": 0.021, "目標營業利益率": 0.0455, "WACC": 0.0837, "終值WACC": 0.089, "有效稅率": 0.144, "終值佔比": 0.681}, "ri_pb": {"常態ROE": 0.1771, "股權成本r": 0.089, "留存成長g": 0.084, "合理PB": 18.617}, "ddm": {"DPS": 1.2128, "g": 0.079, "r": 0.089}}</t>
+          <t>{"graham_number": {"EPS(3年均)": 1.17, "BVPS": 8.8567}, "graham_formula": {"g(上限10%)": 0.1, "Y公司債": 0.04}, "ncav": {"NCAV/股": 6.0294, "NNWC/股": -2.245, "net-net買點": 4.0216}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 18769275000.0, "g1": 0.15, "永續g": 0.021, "門檻報酬r": 0.085, "非營運投資(折70%)": 3053026900.0}, "epv": {"常態營業利益率": 0.0455, "常態NOPAT": 42806605742.0, "WACC": 0.0836, "淨現金": -7517740000.0}, "damodaran_fcff": {"銷售/資本": 4.0, "g1": 0.15, "永續g": 0.021, "目標營業利益率": 0.0455, "WACC": 0.0836, "終值WACC": 0.089, "有效稅率": 0.144, "終值佔比": 0.681}, "ri_pb": {"常態ROE": 0.1771, "股權成本r": 0.089, "留存成長g": 0.084, "合理PB": 18.617}, "ddm": {"DPS": 1.2128, "g": 0.079, "r": 0.089}}</t>
         </is>
       </c>
     </row>
@@ -11933,10 +11933,10 @@
         </is>
       </c>
       <c r="C47" s="34" t="n">
-        <v>56.71</v>
+        <v>56</v>
       </c>
       <c r="D47" s="34" t="n">
-        <v>100.9416</v>
+        <v>100.9447</v>
       </c>
       <c r="E47" s="34" t="n">
         <v>38.1089</v>
@@ -11951,10 +11951,10 @@
         <v>94.1225</v>
       </c>
       <c r="I47" s="34" t="n">
-        <v>56.4547</v>
+        <v>56.4713</v>
       </c>
       <c r="J47" s="34" t="n">
-        <v>92.614</v>
+        <v>92.616</v>
       </c>
       <c r="K47" s="34" t="n">
         <v>442.9869</v>
@@ -11963,7 +11963,7 @@
         <v>89.2491</v>
       </c>
       <c r="M47" s="34" t="n">
-        <v>8.640000000000001</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="N47" s="34" t="n">
         <v>8.9</v>
@@ -11994,10 +11994,10 @@
         </is>
       </c>
       <c r="C48" s="34" t="n">
-        <v>85.59999999999999</v>
+        <v>85.59</v>
       </c>
       <c r="D48" s="34" t="n">
-        <v>113.1287</v>
+        <v>113.1288</v>
       </c>
       <c r="E48" s="34" t="n">
         <v>31.0139</v>
@@ -12012,7 +12012,7 @@
         <v>95.557</v>
       </c>
       <c r="I48" s="34" t="n">
-        <v>61.033</v>
+        <v>61.0332</v>
       </c>
       <c r="J48" s="34" t="n">
         <v>108.9325</v>
@@ -12055,10 +12055,10 @@
         </is>
       </c>
       <c r="C49" s="34" t="n">
-        <v>328.65</v>
+        <v>339.53</v>
       </c>
       <c r="D49" s="34" t="n">
-        <v>79.0136</v>
+        <v>79.0124</v>
       </c>
       <c r="E49" s="34" t="n">
         <v>56.7199</v>
@@ -12073,10 +12073,10 @@
         <v>56.4053</v>
       </c>
       <c r="I49" s="34" t="n">
-        <v>72.8623</v>
+        <v>72.8562</v>
       </c>
       <c r="J49" s="34" t="n">
-        <v>119.6888</v>
+        <v>119.6881</v>
       </c>
       <c r="K49" s="34" t="n">
         <v>17.3885</v>
@@ -12085,7 +12085,7 @@
         <v>76.496</v>
       </c>
       <c r="M49" s="34" t="n">
-        <v>10.22</v>
+        <v>10.23</v>
       </c>
       <c r="N49" s="34" t="n">
         <v>10.26</v>
@@ -12100,7 +12100,7 @@
       </c>
       <c r="Q49" s="33" t="inlineStr">
         <is>
-          <t>{"graham_number": {"EPS(3年均)": 2.89, "BVPS": 49.4756}, "graham_formula": {"g(上限10%)": 0.1, "Y公司債": 0.04}, "ncav": {"NCAV/股": 24.4954, "NNWC/股": 13.9145, "net-net買點": 16.3384}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 1208767747.0, "g1": 0.15, "永續g": 0.021, "門檻報酬r": 0.085, "非營運投資(折70%)": 1532482246.0}, "epv": {"常態營業利益率": 0.2664, "常態NOPAT": 3460108036.0, "WACC": 0.1022, "淨現金": 8863734876.0}, "damodaran_fcff": {"銷售/資本": 0.8, "g1": 0.15, "永續g": 0.021, "目標營業利益率": 0.2664, "WACC": 0.1022, "終值WACC": 0.089, "有效稅率": 0.08, "終值佔比": 0.645}, "ri_pb": {"常態ROE": 0.0864, "股權成本r": 0.1026, "留存成長g": 0.0776, "合理PB": 0.351}, "ddm": {"DPS": 0.7001, "g": 0.0926, "r": 0.1026}}</t>
+          <t>{"graham_number": {"EPS(3年均)": 2.89, "BVPS": 49.4756}, "graham_formula": {"g(上限10%)": 0.1, "Y公司債": 0.04}, "ncav": {"NCAV/股": 24.4954, "NNWC/股": 13.9145, "net-net買點": 16.3384}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 1208767747.0, "g1": 0.15, "永續g": 0.021, "門檻報酬r": 0.085, "非營運投資(折70%)": 1532482246.0}, "epv": {"常態營業利益率": 0.2664, "常態NOPAT": 3460108036.0, "WACC": 0.1023, "淨現金": 8863734876.0}, "damodaran_fcff": {"銷售/資本": 0.8, "g1": 0.15, "永續g": 0.021, "目標營業利益率": 0.2664, "WACC": 0.1023, "終值WACC": 0.089, "有效稅率": 0.08, "終值佔比": 0.645}, "ri_pb": {"常態ROE": 0.0864, "股權成本r": 0.1026, "留存成長g": 0.0776, "合理PB": 0.351}, "ddm": {"DPS": 0.7001, "g": 0.0926, "r": 0.1026}}</t>
         </is>
       </c>
     </row>
@@ -12116,7 +12116,7 @@
         </is>
       </c>
       <c r="C50" s="34" t="n">
-        <v>281.34</v>
+        <v>279.49</v>
       </c>
       <c r="D50" s="34" t="n">
         <v>10.4095</v>
@@ -12177,7 +12177,7 @@
         </is>
       </c>
       <c r="C51" s="34" t="n">
-        <v>473.18</v>
+        <v>462.6</v>
       </c>
       <c r="D51" s="34" t="n">
         <v>6.6805</v>
@@ -13360,7 +13360,7 @@
         </is>
       </c>
       <c r="C2" s="24" t="n">
-        <v>161.4</v>
+        <v>160.6</v>
       </c>
       <c r="D2" s="22" t="inlineStr">
         <is>
@@ -13388,7 +13388,7 @@
         </is>
       </c>
       <c r="K2" s="24" t="n">
-        <v>1.7437</v>
+        <v>1.735</v>
       </c>
       <c r="L2" s="24" t="n">
         <v>69.4229</v>
@@ -13406,7 +13406,7 @@
         </is>
       </c>
       <c r="C3" s="29" t="n">
-        <v>5.49</v>
+        <v>5.36</v>
       </c>
       <c r="D3" s="27" t="inlineStr">
         <is>
@@ -13414,19 +13414,19 @@
         </is>
       </c>
       <c r="E3" s="29" t="n">
-        <v>1.9486</v>
+        <v>1.967</v>
       </c>
       <c r="F3" s="29" t="n">
-        <v>2.9229</v>
+        <v>2.9505</v>
       </c>
       <c r="G3" s="29" t="n">
-        <v>4.4817</v>
+        <v>4.5241</v>
       </c>
       <c r="H3" s="29" t="n">
-        <v>5.8457</v>
+        <v>5.901</v>
       </c>
       <c r="I3" s="29" t="n">
-        <v>5.8457</v>
+        <v>5.901</v>
       </c>
       <c r="J3" s="31" t="inlineStr">
         <is>
@@ -13434,10 +13434,10 @@
         </is>
       </c>
       <c r="K3" s="29" t="n">
-        <v>1.4087</v>
+        <v>1.3625</v>
       </c>
       <c r="L3" s="29" t="n">
-        <v>2.9229</v>
+        <v>2.9505</v>
       </c>
     </row>
     <row r="4">
@@ -13452,7 +13452,7 @@
         </is>
       </c>
       <c r="C4" s="24" t="n">
-        <v>1.265</v>
+        <v>1.2</v>
       </c>
       <c r="D4" s="22" t="inlineStr">
         <is>
@@ -13480,7 +13480,7 @@
         </is>
       </c>
       <c r="K4" s="24" t="n">
-        <v>13.1409</v>
+        <v>12.4657</v>
       </c>
       <c r="L4" s="24" t="n">
         <v>0.0722</v>
@@ -13498,7 +13498,7 @@
         </is>
       </c>
       <c r="C5" s="14" t="n">
-        <v>87.89</v>
+        <v>86</v>
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
@@ -13506,19 +13506,19 @@
         </is>
       </c>
       <c r="E5" s="14" t="n">
-        <v>53.5801</v>
+        <v>53.592</v>
       </c>
       <c r="F5" s="14" t="n">
-        <v>80.3702</v>
+        <v>80.38809999999999</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>123.2343</v>
+        <v>123.2617</v>
       </c>
       <c r="H5" s="14" t="n">
-        <v>160.7404</v>
+        <v>160.7761</v>
       </c>
       <c r="I5" s="14" t="n">
-        <v>160.7404</v>
+        <v>160.7761</v>
       </c>
       <c r="J5" s="16" t="inlineStr">
         <is>
@@ -13526,10 +13526,10 @@
         </is>
       </c>
       <c r="K5" s="14" t="n">
-        <v>0.8202</v>
+        <v>0.8024</v>
       </c>
       <c r="L5" s="14" t="n">
-        <v>80.3702</v>
+        <v>80.38809999999999</v>
       </c>
     </row>
     <row r="6">
@@ -13544,7 +13544,7 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>38.61</v>
+        <v>38.23</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -13552,19 +13552,19 @@
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>71.26260000000001</v>
+        <v>71.2736</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>106.8939</v>
+        <v>106.9104</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>163.9041</v>
+        <v>163.9292</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>213.7879</v>
+        <v>213.8207</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>213.7879</v>
+        <v>213.8207</v>
       </c>
       <c r="J6" s="6" t="inlineStr">
         <is>
@@ -13572,10 +13572,10 @@
         </is>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.2709</v>
+        <v>0.2682</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>106.8939</v>
+        <v>106.9104</v>
       </c>
     </row>
     <row r="7">
@@ -13590,7 +13590,7 @@
         </is>
       </c>
       <c r="C7" s="19" t="n">
-        <v>29</v>
+        <v>28.69</v>
       </c>
       <c r="D7" s="17" t="inlineStr">
         <is>
@@ -13598,19 +13598,19 @@
         </is>
       </c>
       <c r="E7" s="19" t="n">
-        <v>11.5305</v>
+        <v>11.5314</v>
       </c>
       <c r="F7" s="19" t="n">
-        <v>17.2958</v>
+        <v>17.297</v>
       </c>
       <c r="G7" s="19" t="n">
-        <v>26.5202</v>
+        <v>26.5221</v>
       </c>
       <c r="H7" s="19" t="n">
-        <v>34.5916</v>
+        <v>34.5941</v>
       </c>
       <c r="I7" s="19" t="n">
-        <v>34.5916</v>
+        <v>34.5941</v>
       </c>
       <c r="J7" s="21" t="inlineStr">
         <is>
@@ -13618,10 +13618,10 @@
         </is>
       </c>
       <c r="K7" s="19" t="n">
-        <v>1.2575</v>
+        <v>1.244</v>
       </c>
       <c r="L7" s="19" t="n">
-        <v>17.2958</v>
+        <v>17.297</v>
       </c>
     </row>
     <row r="8">
@@ -13636,7 +13636,7 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -13644,19 +13644,19 @@
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>1.9012</v>
+        <v>1.9015</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>2.8517</v>
+        <v>2.8523</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>4.3727</v>
+        <v>4.3735</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>5.7035</v>
+        <v>5.7046</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>5.7035</v>
+        <v>5.7046</v>
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
@@ -13664,10 +13664,10 @@
         </is>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.334</v>
+        <v>0.3287</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>2.8517</v>
+        <v>2.8523</v>
       </c>
     </row>
     <row r="9">
@@ -13682,7 +13682,7 @@
         </is>
       </c>
       <c r="C9" s="14" t="n">
-        <v>33.22</v>
+        <v>32.8</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
@@ -13690,19 +13690,19 @@
         </is>
       </c>
       <c r="E9" s="14" t="n">
-        <v>20.522</v>
+        <v>20.5574</v>
       </c>
       <c r="F9" s="14" t="n">
-        <v>30.7829</v>
+        <v>30.8361</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>47.2005</v>
+        <v>47.282</v>
       </c>
       <c r="H9" s="14" t="n">
-        <v>61.5659</v>
+        <v>61.6722</v>
       </c>
       <c r="I9" s="14" t="n">
-        <v>61.5659</v>
+        <v>61.6722</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
@@ -13710,56 +13710,56 @@
         </is>
       </c>
       <c r="K9" s="14" t="n">
-        <v>0.8094</v>
+        <v>0.7978</v>
       </c>
       <c r="L9" s="14" t="n">
-        <v>26.6785</v>
+        <v>26.7246</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>00386</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>中国石油化工股份</t>
         </is>
       </c>
-      <c r="C10" s="9" t="n">
-        <v>4.67</v>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="C10" s="4" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>HKD</t>
         </is>
       </c>
-      <c r="E10" s="9" t="n">
-        <v>4.6499</v>
-      </c>
-      <c r="F10" s="9" t="n">
-        <v>6.9748</v>
-      </c>
-      <c r="G10" s="9" t="n">
-        <v>10.6947</v>
-      </c>
-      <c r="H10" s="9" t="n">
-        <v>13.9496</v>
-      </c>
-      <c r="I10" s="9" t="n">
-        <v>13.9496</v>
-      </c>
-      <c r="J10" s="11" t="inlineStr">
-        <is>
-          <t>便宜</t>
-        </is>
-      </c>
-      <c r="K10" s="9" t="n">
-        <v>0.5022</v>
-      </c>
-      <c r="L10" s="9" t="n">
-        <v>6.9748</v>
+      <c r="E10" s="4" t="n">
+        <v>4.6568</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>6.9852</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>10.7106</v>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>13.9704</v>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>13.9704</v>
+      </c>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>非常便宜</t>
+        </is>
+      </c>
+      <c r="K10" s="4" t="n">
+        <v>0.4918</v>
+      </c>
+      <c r="L10" s="4" t="n">
+        <v>6.9852</v>
       </c>
     </row>
     <row r="11">
@@ -13774,7 +13774,7 @@
         </is>
       </c>
       <c r="C11" s="24" t="n">
-        <v>396</v>
+        <v>393.6</v>
       </c>
       <c r="D11" s="22" t="inlineStr">
         <is>
@@ -13802,7 +13802,7 @@
         </is>
       </c>
       <c r="K11" s="24" t="n">
-        <v>2.5268</v>
+        <v>2.5115</v>
       </c>
       <c r="L11" s="24" t="n">
         <v>117.5408</v>
@@ -13820,7 +13820,7 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>437.8</v>
+        <v>434.2</v>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
@@ -13828,19 +13828,19 @@
         </is>
       </c>
       <c r="E12" s="9" t="n">
-        <v>329.8995</v>
+        <v>330.1875</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>494.8493</v>
+        <v>495.2813</v>
       </c>
       <c r="G12" s="9" t="n">
-        <v>758.7689</v>
+        <v>759.4313</v>
       </c>
       <c r="H12" s="9" t="n">
-        <v>989.6986000000001</v>
+        <v>990.5625</v>
       </c>
       <c r="I12" s="9" t="n">
-        <v>989.6986000000001</v>
+        <v>990.5625</v>
       </c>
       <c r="J12" s="11" t="inlineStr">
         <is>
@@ -13848,10 +13848,10 @@
         </is>
       </c>
       <c r="K12" s="9" t="n">
-        <v>0.6635</v>
+        <v>0.6575</v>
       </c>
       <c r="L12" s="9" t="n">
-        <v>494.8493</v>
+        <v>495.2813</v>
       </c>
     </row>
     <row r="13">
@@ -13866,7 +13866,7 @@
         </is>
       </c>
       <c r="C13" s="9" t="n">
-        <v>5.91</v>
+        <v>5.78</v>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
@@ -13874,19 +13874,19 @@
         </is>
       </c>
       <c r="E13" s="9" t="n">
-        <v>5.7198</v>
+        <v>5.7222</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>8.579800000000001</v>
+        <v>8.583299999999999</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>13.1556</v>
+        <v>13.161</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>17.1595</v>
+        <v>17.1666</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>17.1595</v>
+        <v>17.1666</v>
       </c>
       <c r="J13" s="11" t="inlineStr">
         <is>
@@ -13894,10 +13894,10 @@
         </is>
       </c>
       <c r="K13" s="9" t="n">
-        <v>0.5165999999999999</v>
+        <v>0.5051</v>
       </c>
       <c r="L13" s="9" t="n">
-        <v>8.579800000000001</v>
+        <v>8.583299999999999</v>
       </c>
     </row>
     <row r="14">
@@ -13912,7 +13912,7 @@
         </is>
       </c>
       <c r="C14" s="14" t="n">
-        <v>9.02</v>
+        <v>8.984999999999999</v>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
@@ -13920,19 +13920,19 @@
         </is>
       </c>
       <c r="E14" s="14" t="n">
-        <v>5.7729</v>
+        <v>5.7739</v>
       </c>
       <c r="F14" s="14" t="n">
-        <v>8.6593</v>
+        <v>8.6608</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>13.2776</v>
+        <v>13.2799</v>
       </c>
       <c r="H14" s="14" t="n">
-        <v>17.3186</v>
+        <v>17.3217</v>
       </c>
       <c r="I14" s="14" t="n">
-        <v>17.3186</v>
+        <v>17.3217</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
@@ -13940,10 +13940,10 @@
         </is>
       </c>
       <c r="K14" s="14" t="n">
-        <v>0.7812</v>
+        <v>0.7781</v>
       </c>
       <c r="L14" s="14" t="n">
-        <v>8.6593</v>
+        <v>8.6608</v>
       </c>
     </row>
     <row r="15">
@@ -13958,7 +13958,7 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>18.76</v>
+        <v>18.78</v>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
@@ -13986,7 +13986,7 @@
         </is>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.3513</v>
+        <v>0.3516</v>
       </c>
       <c r="L15" s="4" t="n">
         <v>40.056</v>
@@ -14004,7 +14004,7 @@
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>9.91</v>
+        <v>9.994999999999999</v>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
@@ -14012,19 +14012,19 @@
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>11.4983</v>
+        <v>11.4967</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>17.2474</v>
+        <v>17.2451</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>26.4461</v>
+        <v>26.4424</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>34.4949</v>
+        <v>34.4901</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>34.4949</v>
+        <v>34.4901</v>
       </c>
       <c r="J16" s="6" t="inlineStr">
         <is>
@@ -14032,10 +14032,10 @@
         </is>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.4309</v>
+        <v>0.4347</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>17.2474</v>
+        <v>17.2451</v>
       </c>
     </row>
     <row r="17">
@@ -14050,7 +14050,7 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>24.46</v>
+        <v>24.76</v>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
@@ -14058,19 +14058,19 @@
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>35.8686</v>
+        <v>35.8669</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>53.8028</v>
+        <v>53.8004</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>82.49769999999999</v>
+        <v>82.4939</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>107.6057</v>
+        <v>107.6007</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>107.6057</v>
+        <v>107.6007</v>
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
@@ -14078,10 +14078,10 @@
         </is>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.341</v>
+        <v>0.3452</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>53.8028</v>
+        <v>53.8004</v>
       </c>
     </row>
     <row r="18">
@@ -14096,7 +14096,7 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>9.654999999999999</v>
+        <v>9.625</v>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
@@ -14124,7 +14124,7 @@
         </is>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.0738</v>
+        <v>0.0736</v>
       </c>
       <c r="L18" s="4" t="n">
         <v>98.0891</v>
@@ -14142,7 +14142,7 @@
         </is>
       </c>
       <c r="C19" s="14" t="n">
-        <v>79.2</v>
+        <v>79.25</v>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
@@ -14150,19 +14150,19 @@
         </is>
       </c>
       <c r="E19" s="14" t="n">
-        <v>44.8042</v>
+        <v>44.804</v>
       </c>
       <c r="F19" s="14" t="n">
-        <v>67.2063</v>
+        <v>67.206</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>103.0497</v>
+        <v>103.0492</v>
       </c>
       <c r="H19" s="14" t="n">
-        <v>134.4126</v>
+        <v>134.4121</v>
       </c>
       <c r="I19" s="14" t="n">
-        <v>134.4126</v>
+        <v>134.4121</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
@@ -14170,10 +14170,10 @@
         </is>
       </c>
       <c r="K19" s="14" t="n">
-        <v>0.8838</v>
+        <v>0.8844</v>
       </c>
       <c r="L19" s="14" t="n">
-        <v>67.2063</v>
+        <v>67.206</v>
       </c>
     </row>
     <row r="20">
@@ -14188,7 +14188,7 @@
         </is>
       </c>
       <c r="C20" s="29" t="n">
-        <v>5.315</v>
+        <v>5.27</v>
       </c>
       <c r="D20" s="27" t="inlineStr">
         <is>
@@ -14216,7 +14216,7 @@
         </is>
       </c>
       <c r="K20" s="29" t="n">
-        <v>0.0336</v>
+        <v>0.0333</v>
       </c>
       <c r="L20" s="29" t="n">
         <v>102.726</v>
@@ -14234,7 +14234,7 @@
         </is>
       </c>
       <c r="C21" s="24" t="n">
-        <v>61.45</v>
+        <v>61.35</v>
       </c>
       <c r="D21" s="22" t="inlineStr">
         <is>
@@ -14242,19 +14242,19 @@
         </is>
       </c>
       <c r="E21" s="24" t="n">
-        <v>3.4586</v>
+        <v>3.4585</v>
       </c>
       <c r="F21" s="24" t="n">
-        <v>5.1879</v>
+        <v>5.1877</v>
       </c>
       <c r="G21" s="24" t="n">
-        <v>7.9547</v>
+        <v>7.9545</v>
       </c>
       <c r="H21" s="24" t="n">
-        <v>10.3757</v>
+        <v>10.3755</v>
       </c>
       <c r="I21" s="24" t="n">
-        <v>10.3757</v>
+        <v>10.3755</v>
       </c>
       <c r="J21" s="26" t="inlineStr">
         <is>
@@ -14262,10 +14262,10 @@
         </is>
       </c>
       <c r="K21" s="24" t="n">
-        <v>8.883699999999999</v>
+        <v>8.8695</v>
       </c>
       <c r="L21" s="24" t="n">
-        <v>5.1879</v>
+        <v>5.1877</v>
       </c>
     </row>
     <row r="22">
@@ -14280,7 +14280,7 @@
         </is>
       </c>
       <c r="C22" s="14" t="n">
-        <v>32.04</v>
+        <v>31.94</v>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
@@ -14288,7 +14288,7 @@
         </is>
       </c>
       <c r="E22" s="14" t="n">
-        <v>15.8194</v>
+        <v>15.8193</v>
       </c>
       <c r="F22" s="14" t="n">
         <v>23.729</v>
@@ -14297,10 +14297,10 @@
         <v>36.3845</v>
       </c>
       <c r="H22" s="14" t="n">
-        <v>47.4581</v>
+        <v>47.458</v>
       </c>
       <c r="I22" s="14" t="n">
-        <v>47.4581</v>
+        <v>47.458</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
@@ -14308,7 +14308,7 @@
         </is>
       </c>
       <c r="K22" s="14" t="n">
-        <v>1.0127</v>
+        <v>1.0095</v>
       </c>
       <c r="L22" s="14" t="n">
         <v>23.729</v>
@@ -14326,7 +14326,7 @@
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>7.495</v>
+        <v>7.505</v>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
@@ -14354,7 +14354,7 @@
         </is>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0.0761</v>
+        <v>0.0762</v>
       </c>
       <c r="L23" s="4" t="n">
         <v>73.8655</v>
@@ -14372,7 +14372,7 @@
         </is>
       </c>
       <c r="C24" s="14" t="n">
-        <v>27.16</v>
+        <v>26.04</v>
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
@@ -14380,19 +14380,19 @@
         </is>
       </c>
       <c r="E24" s="14" t="n">
-        <v>14.3807</v>
+        <v>14.3825</v>
       </c>
       <c r="F24" s="14" t="n">
-        <v>21.571</v>
+        <v>21.5738</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>33.0755</v>
+        <v>33.0798</v>
       </c>
       <c r="H24" s="14" t="n">
-        <v>43.142</v>
+        <v>43.1475</v>
       </c>
       <c r="I24" s="14" t="n">
-        <v>43.142</v>
+        <v>43.1475</v>
       </c>
       <c r="J24" s="16" t="inlineStr">
         <is>
@@ -14400,10 +14400,10 @@
         </is>
       </c>
       <c r="K24" s="14" t="n">
-        <v>0.9443</v>
+        <v>0.9053</v>
       </c>
       <c r="L24" s="14" t="n">
-        <v>21.571</v>
+        <v>21.5738</v>
       </c>
     </row>
     <row r="25">
@@ -14418,7 +14418,7 @@
         </is>
       </c>
       <c r="C25" s="19" t="n">
-        <v>3.015</v>
+        <v>3.04</v>
       </c>
       <c r="D25" s="17" t="inlineStr">
         <is>
@@ -14446,7 +14446,7 @@
         </is>
       </c>
       <c r="K25" s="19" t="n">
-        <v>1.3021</v>
+        <v>1.3129</v>
       </c>
       <c r="L25" s="19" t="n">
         <v>1.7366</v>
@@ -14464,7 +14464,7 @@
         </is>
       </c>
       <c r="C26" s="29" t="n">
-        <v>0.171</v>
+        <v>0.17</v>
       </c>
       <c r="D26" s="27" t="inlineStr">
         <is>
@@ -14496,7 +14496,7 @@
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>53.5</v>
+        <v>53.05</v>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
@@ -14524,7 +14524,7 @@
         </is>
       </c>
       <c r="K27" s="4" t="n">
-        <v>0.0765</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="L27" s="4" t="n">
         <v>524.7707</v>
@@ -14542,7 +14542,7 @@
         </is>
       </c>
       <c r="C28" s="24" t="n">
-        <v>196</v>
+        <v>196.8</v>
       </c>
       <c r="D28" s="22" t="inlineStr">
         <is>
@@ -14550,19 +14550,19 @@
         </is>
       </c>
       <c r="E28" s="24" t="n">
-        <v>51.5779</v>
+        <v>51.5767</v>
       </c>
       <c r="F28" s="24" t="n">
-        <v>77.3669</v>
+        <v>77.36499999999999</v>
       </c>
       <c r="G28" s="24" t="n">
-        <v>118.6292</v>
+        <v>118.6264</v>
       </c>
       <c r="H28" s="24" t="n">
-        <v>154.7338</v>
+        <v>154.7301</v>
       </c>
       <c r="I28" s="24" t="n">
-        <v>154.7338</v>
+        <v>154.7301</v>
       </c>
       <c r="J28" s="26" t="inlineStr">
         <is>
@@ -14570,10 +14570,10 @@
         </is>
       </c>
       <c r="K28" s="24" t="n">
-        <v>1.9</v>
+        <v>1.9078</v>
       </c>
       <c r="L28" s="24" t="n">
-        <v>77.3669</v>
+        <v>77.36499999999999</v>
       </c>
     </row>
     <row r="29">
@@ -14588,7 +14588,7 @@
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>3.295</v>
+        <v>3.325</v>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
@@ -14602,13 +14602,13 @@
         <v>9.9321</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>15.2293</v>
+        <v>15.2292</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>19.8643</v>
+        <v>19.8642</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>19.8643</v>
+        <v>19.8642</v>
       </c>
       <c r="J29" s="6" t="inlineStr">
         <is>
@@ -14616,7 +14616,7 @@
         </is>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0.2488</v>
+        <v>0.2511</v>
       </c>
       <c r="L29" s="4" t="n">
         <v>9.9321</v>
@@ -14634,7 +14634,7 @@
         </is>
       </c>
       <c r="C30" s="9" t="n">
-        <v>48.72</v>
+        <v>50.4</v>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
@@ -14642,19 +14642,19 @@
         </is>
       </c>
       <c r="E30" s="9" t="n">
-        <v>42.1166</v>
+        <v>42.0511</v>
       </c>
       <c r="F30" s="9" t="n">
-        <v>63.1748</v>
+        <v>63.0767</v>
       </c>
       <c r="G30" s="9" t="n">
-        <v>96.8681</v>
+        <v>96.7176</v>
       </c>
       <c r="H30" s="9" t="n">
-        <v>126.3497</v>
+        <v>126.1534</v>
       </c>
       <c r="I30" s="9" t="n">
-        <v>126.3497</v>
+        <v>126.1534</v>
       </c>
       <c r="J30" s="11" t="inlineStr">
         <is>
@@ -14662,10 +14662,10 @@
         </is>
       </c>
       <c r="K30" s="9" t="n">
-        <v>0.5784</v>
+        <v>0.5993000000000001</v>
       </c>
       <c r="L30" s="9" t="n">
-        <v>63.1748</v>
+        <v>63.0767</v>
       </c>
     </row>
     <row r="31">
@@ -14680,7 +14680,7 @@
         </is>
       </c>
       <c r="C31" s="24" t="n">
-        <v>75.45</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="D31" s="22" t="inlineStr">
         <is>
@@ -14708,7 +14708,7 @@
         </is>
       </c>
       <c r="K31" s="24" t="n">
-        <v>5.4041</v>
+        <v>5.2931</v>
       </c>
       <c r="L31" s="24" t="n">
         <v>10.4713</v>
@@ -14726,7 +14726,7 @@
         </is>
       </c>
       <c r="C32" s="19" t="n">
-        <v>542</v>
+        <v>492.2</v>
       </c>
       <c r="D32" s="17" t="inlineStr">
         <is>
@@ -14734,19 +14734,19 @@
         </is>
       </c>
       <c r="E32" s="19" t="n">
-        <v>191.3022</v>
+        <v>191.4339</v>
       </c>
       <c r="F32" s="19" t="n">
-        <v>286.9533</v>
+        <v>287.1508</v>
       </c>
       <c r="G32" s="19" t="n">
-        <v>439.995</v>
+        <v>440.2979</v>
       </c>
       <c r="H32" s="19" t="n">
-        <v>573.9065000000001</v>
+        <v>574.3017</v>
       </c>
       <c r="I32" s="19" t="n">
-        <v>573.9065000000001</v>
+        <v>574.3017</v>
       </c>
       <c r="J32" s="21" t="inlineStr">
         <is>
@@ -14754,10 +14754,10 @@
         </is>
       </c>
       <c r="K32" s="19" t="n">
-        <v>1.4166</v>
+        <v>1.2856</v>
       </c>
       <c r="L32" s="19" t="n">
-        <v>286.9533</v>
+        <v>287.1508</v>
       </c>
     </row>
     <row r="33">
@@ -14772,7 +14772,7 @@
         </is>
       </c>
       <c r="C33" s="4" t="n">
-        <v>51.45</v>
+        <v>51.25</v>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
@@ -14800,7 +14800,7 @@
         </is>
       </c>
       <c r="K33" s="4" t="n">
-        <v>0.08740000000000001</v>
+        <v>0.0871</v>
       </c>
       <c r="L33" s="4" t="n">
         <v>441.4036</v>
@@ -14818,7 +14818,7 @@
         </is>
       </c>
       <c r="C34" s="9" t="n">
-        <v>4.3</v>
+        <v>4.215</v>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
@@ -14826,19 +14826,19 @@
         </is>
       </c>
       <c r="E34" s="9" t="n">
-        <v>4.1514</v>
+        <v>4.1516</v>
       </c>
       <c r="F34" s="9" t="n">
-        <v>6.2271</v>
+        <v>6.2274</v>
       </c>
       <c r="G34" s="9" t="n">
-        <v>9.5482</v>
+        <v>9.5486</v>
       </c>
       <c r="H34" s="9" t="n">
-        <v>12.4542</v>
+        <v>12.4547</v>
       </c>
       <c r="I34" s="9" t="n">
-        <v>12.4542</v>
+        <v>12.4547</v>
       </c>
       <c r="J34" s="11" t="inlineStr">
         <is>
@@ -14846,10 +14846,10 @@
         </is>
       </c>
       <c r="K34" s="9" t="n">
-        <v>0.5179</v>
+        <v>0.5076000000000001</v>
       </c>
       <c r="L34" s="9" t="n">
-        <v>6.2271</v>
+        <v>6.2274</v>
       </c>
     </row>
     <row r="35">
@@ -14864,7 +14864,7 @@
         </is>
       </c>
       <c r="C35" s="24" t="n">
-        <v>21.58</v>
+        <v>21.14</v>
       </c>
       <c r="D35" s="22" t="inlineStr">
         <is>
@@ -14872,19 +14872,19 @@
         </is>
       </c>
       <c r="E35" s="24" t="n">
-        <v>6.1046</v>
+        <v>6.1058</v>
       </c>
       <c r="F35" s="24" t="n">
-        <v>9.1568</v>
+        <v>9.1586</v>
       </c>
       <c r="G35" s="24" t="n">
-        <v>14.0405</v>
+        <v>14.0432</v>
       </c>
       <c r="H35" s="24" t="n">
-        <v>18.3137</v>
+        <v>18.3173</v>
       </c>
       <c r="I35" s="24" t="n">
-        <v>18.3137</v>
+        <v>18.3173</v>
       </c>
       <c r="J35" s="26" t="inlineStr">
         <is>
@@ -14892,10 +14892,10 @@
         </is>
       </c>
       <c r="K35" s="24" t="n">
-        <v>1.7675</v>
+        <v>1.7312</v>
       </c>
       <c r="L35" s="24" t="n">
-        <v>9.1568</v>
+        <v>9.1586</v>
       </c>
     </row>
     <row r="36">
@@ -14910,7 +14910,7 @@
         </is>
       </c>
       <c r="C36" s="14" t="n">
-        <v>106.3</v>
+        <v>105.2</v>
       </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
@@ -14918,19 +14918,19 @@
         </is>
       </c>
       <c r="E36" s="14" t="n">
-        <v>68.09059999999999</v>
+        <v>68.0859</v>
       </c>
       <c r="F36" s="14" t="n">
-        <v>102.1359</v>
+        <v>102.1288</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>156.6084</v>
+        <v>156.5976</v>
       </c>
       <c r="H36" s="14" t="n">
-        <v>204.2719</v>
+        <v>204.2577</v>
       </c>
       <c r="I36" s="14" t="n">
-        <v>204.2719</v>
+        <v>204.2577</v>
       </c>
       <c r="J36" s="16" t="inlineStr">
         <is>
@@ -14938,10 +14938,10 @@
         </is>
       </c>
       <c r="K36" s="14" t="n">
-        <v>0.7806</v>
+        <v>0.7726</v>
       </c>
       <c r="L36" s="14" t="n">
-        <v>102.1359</v>
+        <v>102.1288</v>
       </c>
     </row>
     <row r="37">
@@ -14956,7 +14956,7 @@
         </is>
       </c>
       <c r="C37" s="9" t="n">
-        <v>308</v>
+        <v>303.6</v>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
@@ -14964,19 +14964,19 @@
         </is>
       </c>
       <c r="E37" s="9" t="n">
-        <v>215.4394</v>
+        <v>215.4729</v>
       </c>
       <c r="F37" s="9" t="n">
-        <v>323.1591</v>
+        <v>323.2093</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>495.5107</v>
+        <v>495.5877</v>
       </c>
       <c r="H37" s="9" t="n">
-        <v>646.3183</v>
+        <v>646.4186999999999</v>
       </c>
       <c r="I37" s="9" t="n">
-        <v>646.3183</v>
+        <v>646.4186999999999</v>
       </c>
       <c r="J37" s="11" t="inlineStr">
         <is>
@@ -14984,10 +14984,10 @@
         </is>
       </c>
       <c r="K37" s="9" t="n">
-        <v>0.7148</v>
+        <v>0.7045</v>
       </c>
       <c r="L37" s="9" t="n">
-        <v>323.1591</v>
+        <v>323.2093</v>
       </c>
     </row>
     <row r="38">
@@ -15002,7 +15002,7 @@
         </is>
       </c>
       <c r="C38" s="24" t="n">
-        <v>106.7</v>
+        <v>106.6</v>
       </c>
       <c r="D38" s="22" t="inlineStr">
         <is>
@@ -15010,19 +15010,19 @@
         </is>
       </c>
       <c r="E38" s="24" t="n">
-        <v>34.0885</v>
+        <v>34.0889</v>
       </c>
       <c r="F38" s="24" t="n">
-        <v>51.1328</v>
+        <v>51.1333</v>
       </c>
       <c r="G38" s="24" t="n">
-        <v>78.4036</v>
+        <v>78.4045</v>
       </c>
       <c r="H38" s="24" t="n">
-        <v>102.2656</v>
+        <v>102.2667</v>
       </c>
       <c r="I38" s="24" t="n">
-        <v>102.2656</v>
+        <v>102.2667</v>
       </c>
       <c r="J38" s="26" t="inlineStr">
         <is>
@@ -15030,10 +15030,10 @@
         </is>
       </c>
       <c r="K38" s="24" t="n">
-        <v>1.565</v>
+        <v>1.5636</v>
       </c>
       <c r="L38" s="24" t="n">
-        <v>51.1328</v>
+        <v>51.1333</v>
       </c>
     </row>
     <row r="39">
@@ -15048,7 +15048,7 @@
         </is>
       </c>
       <c r="C39" s="9" t="n">
-        <v>187.2</v>
+        <v>183.8</v>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
@@ -15056,19 +15056,19 @@
         </is>
       </c>
       <c r="E39" s="9" t="n">
-        <v>150.0674</v>
+        <v>150.0705</v>
       </c>
       <c r="F39" s="9" t="n">
-        <v>225.1011</v>
+        <v>225.1058</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>345.155</v>
+        <v>345.1622</v>
       </c>
       <c r="H39" s="9" t="n">
-        <v>450.2022</v>
+        <v>450.2116</v>
       </c>
       <c r="I39" s="9" t="n">
-        <v>450.2022</v>
+        <v>450.2116</v>
       </c>
       <c r="J39" s="11" t="inlineStr">
         <is>
@@ -15076,10 +15076,10 @@
         </is>
       </c>
       <c r="K39" s="9" t="n">
-        <v>0.6237</v>
+        <v>0.6124000000000001</v>
       </c>
       <c r="L39" s="9" t="n">
-        <v>225.1011</v>
+        <v>225.1058</v>
       </c>
     </row>
     <row r="40">
@@ -15094,7 +15094,7 @@
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>84.58</v>
+        <v>83.75</v>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
@@ -15102,19 +15102,19 @@
         </is>
       </c>
       <c r="E40" s="9" t="n">
-        <v>63.1863</v>
+        <v>63.1879</v>
       </c>
       <c r="F40" s="9" t="n">
-        <v>94.7794</v>
+        <v>94.7818</v>
       </c>
       <c r="G40" s="9" t="n">
-        <v>145.3284</v>
+        <v>145.3321</v>
       </c>
       <c r="H40" s="9" t="n">
-        <v>189.5588</v>
+        <v>189.5637</v>
       </c>
       <c r="I40" s="9" t="n">
-        <v>189.5588</v>
+        <v>189.5637</v>
       </c>
       <c r="J40" s="11" t="inlineStr">
         <is>
@@ -15122,10 +15122,10 @@
         </is>
       </c>
       <c r="K40" s="9" t="n">
-        <v>0.6693</v>
+        <v>0.6627</v>
       </c>
       <c r="L40" s="9" t="n">
-        <v>94.7794</v>
+        <v>94.7818</v>
       </c>
     </row>
     <row r="41">
@@ -15140,7 +15140,7 @@
         </is>
       </c>
       <c r="C41" s="14" t="n">
-        <v>159.68</v>
+        <v>158.92</v>
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
@@ -15148,19 +15148,19 @@
         </is>
       </c>
       <c r="E41" s="14" t="n">
-        <v>100.1507</v>
+        <v>100.1508</v>
       </c>
       <c r="F41" s="14" t="n">
-        <v>150.2261</v>
+        <v>150.2262</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>230.3467</v>
+        <v>230.3468</v>
       </c>
       <c r="H41" s="14" t="n">
-        <v>300.4522</v>
+        <v>300.4524</v>
       </c>
       <c r="I41" s="14" t="n">
-        <v>300.4522</v>
+        <v>300.4524</v>
       </c>
       <c r="J41" s="16" t="inlineStr">
         <is>
@@ -15168,10 +15168,10 @@
         </is>
       </c>
       <c r="K41" s="14" t="n">
-        <v>0.7972</v>
+        <v>0.7934</v>
       </c>
       <c r="L41" s="14" t="n">
-        <v>150.2261</v>
+        <v>150.2262</v>
       </c>
     </row>
     <row r="42">
@@ -15186,7 +15186,7 @@
         </is>
       </c>
       <c r="C42" s="24" t="n">
-        <v>43.26</v>
+        <v>43.22</v>
       </c>
       <c r="D42" s="22" t="inlineStr">
         <is>
@@ -15214,7 +15214,7 @@
         </is>
       </c>
       <c r="K42" s="24" t="n">
-        <v>1.5191</v>
+        <v>1.5177</v>
       </c>
       <c r="L42" s="24" t="n">
         <v>21.3586</v>
@@ -15232,7 +15232,7 @@
         </is>
       </c>
       <c r="C43" s="24" t="n">
-        <v>118.28</v>
+        <v>116.82</v>
       </c>
       <c r="D43" s="22" t="inlineStr">
         <is>
@@ -15240,19 +15240,19 @@
         </is>
       </c>
       <c r="E43" s="24" t="n">
-        <v>25.276</v>
+        <v>25.2766</v>
       </c>
       <c r="F43" s="24" t="n">
-        <v>37.9139</v>
+        <v>37.9149</v>
       </c>
       <c r="G43" s="24" t="n">
-        <v>58.1347</v>
+        <v>58.1362</v>
       </c>
       <c r="H43" s="24" t="n">
-        <v>75.8279</v>
+        <v>75.82980000000001</v>
       </c>
       <c r="I43" s="24" t="n">
-        <v>75.8279</v>
+        <v>75.82980000000001</v>
       </c>
       <c r="J43" s="26" t="inlineStr">
         <is>
@@ -15260,10 +15260,10 @@
         </is>
       </c>
       <c r="K43" s="24" t="n">
-        <v>2.3398</v>
+        <v>2.3108</v>
       </c>
       <c r="L43" s="24" t="n">
-        <v>37.9139</v>
+        <v>37.9149</v>
       </c>
     </row>
     <row r="44">
@@ -15278,7 +15278,7 @@
         </is>
       </c>
       <c r="C44" s="14" t="n">
-        <v>1276.81</v>
+        <v>1264.75</v>
       </c>
       <c r="D44" s="12" t="inlineStr">
         <is>
@@ -15286,19 +15286,19 @@
         </is>
       </c>
       <c r="E44" s="14" t="n">
-        <v>593.4173</v>
+        <v>593.4174</v>
       </c>
       <c r="F44" s="14" t="n">
-        <v>890.1259</v>
+        <v>890.1261</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>1364.8597</v>
+        <v>1364.86</v>
       </c>
       <c r="H44" s="14" t="n">
-        <v>1780.2518</v>
+        <v>1780.2522</v>
       </c>
       <c r="I44" s="14" t="n">
-        <v>1780.2518</v>
+        <v>1780.2522</v>
       </c>
       <c r="J44" s="16" t="inlineStr">
         <is>
@@ -15306,10 +15306,10 @@
         </is>
       </c>
       <c r="K44" s="14" t="n">
-        <v>1.0758</v>
+        <v>1.0656</v>
       </c>
       <c r="L44" s="14" t="n">
-        <v>890.1259</v>
+        <v>890.1261</v>
       </c>
     </row>
     <row r="45">
@@ -15324,7 +15324,7 @@
         </is>
       </c>
       <c r="C45" s="19" t="n">
-        <v>28.5</v>
+        <v>28.36</v>
       </c>
       <c r="D45" s="17" t="inlineStr">
         <is>
@@ -15332,19 +15332,19 @@
         </is>
       </c>
       <c r="E45" s="19" t="n">
-        <v>10.2824</v>
+        <v>10.2844</v>
       </c>
       <c r="F45" s="19" t="n">
-        <v>15.4236</v>
+        <v>15.4266</v>
       </c>
       <c r="G45" s="19" t="n">
-        <v>23.6496</v>
+        <v>23.6542</v>
       </c>
       <c r="H45" s="19" t="n">
-        <v>30.8473</v>
+        <v>30.8533</v>
       </c>
       <c r="I45" s="19" t="n">
-        <v>30.8473</v>
+        <v>30.8533</v>
       </c>
       <c r="J45" s="21" t="inlineStr">
         <is>
@@ -15352,10 +15352,10 @@
         </is>
       </c>
       <c r="K45" s="19" t="n">
-        <v>1.3859</v>
+        <v>1.3788</v>
       </c>
       <c r="L45" s="19" t="n">
-        <v>15.4236</v>
+        <v>15.4266</v>
       </c>
     </row>
     <row r="46">
@@ -15370,7 +15370,7 @@
         </is>
       </c>
       <c r="C46" s="24" t="n">
-        <v>61.82</v>
+        <v>60.94</v>
       </c>
       <c r="D46" s="22" t="inlineStr">
         <is>
@@ -15378,19 +15378,19 @@
         </is>
       </c>
       <c r="E46" s="24" t="n">
-        <v>17.8805</v>
+        <v>17.8824</v>
       </c>
       <c r="F46" s="24" t="n">
-        <v>26.8208</v>
+        <v>26.8236</v>
       </c>
       <c r="G46" s="24" t="n">
-        <v>41.1252</v>
+        <v>41.1295</v>
       </c>
       <c r="H46" s="24" t="n">
-        <v>53.6416</v>
+        <v>53.6471</v>
       </c>
       <c r="I46" s="24" t="n">
-        <v>53.6416</v>
+        <v>53.6471</v>
       </c>
       <c r="J46" s="26" t="inlineStr">
         <is>
@@ -15398,10 +15398,10 @@
         </is>
       </c>
       <c r="K46" s="24" t="n">
-        <v>1.7287</v>
+        <v>1.7039</v>
       </c>
       <c r="L46" s="24" t="n">
-        <v>26.8208</v>
+        <v>26.8236</v>
       </c>
     </row>
     <row r="47">
@@ -15416,7 +15416,7 @@
         </is>
       </c>
       <c r="C47" s="9" t="n">
-        <v>56.71</v>
+        <v>56</v>
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
@@ -15424,19 +15424,19 @@
         </is>
       </c>
       <c r="E47" s="9" t="n">
-        <v>50.4708</v>
+        <v>50.4724</v>
       </c>
       <c r="F47" s="9" t="n">
-        <v>75.7062</v>
+        <v>75.7086</v>
       </c>
       <c r="G47" s="9" t="n">
-        <v>116.0828</v>
+        <v>116.0864</v>
       </c>
       <c r="H47" s="9" t="n">
-        <v>151.4124</v>
+        <v>151.4171</v>
       </c>
       <c r="I47" s="9" t="n">
-        <v>151.4124</v>
+        <v>151.4171</v>
       </c>
       <c r="J47" s="11" t="inlineStr">
         <is>
@@ -15444,10 +15444,10 @@
         </is>
       </c>
       <c r="K47" s="9" t="n">
-        <v>0.5618</v>
+        <v>0.5548</v>
       </c>
       <c r="L47" s="9" t="n">
-        <v>75.7062</v>
+        <v>75.7086</v>
       </c>
     </row>
     <row r="48">
@@ -15462,7 +15462,7 @@
         </is>
       </c>
       <c r="C48" s="14" t="n">
-        <v>85.59999999999999</v>
+        <v>85.59</v>
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
@@ -15473,10 +15473,10 @@
         <v>56.5644</v>
       </c>
       <c r="F48" s="14" t="n">
-        <v>84.84650000000001</v>
+        <v>84.8466</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>130.098</v>
+        <v>130.0981</v>
       </c>
       <c r="H48" s="14" t="n">
         <v>169.6931</v>
@@ -15490,10 +15490,10 @@
         </is>
       </c>
       <c r="K48" s="14" t="n">
-        <v>0.7567</v>
+        <v>0.7566000000000001</v>
       </c>
       <c r="L48" s="14" t="n">
-        <v>84.84650000000001</v>
+        <v>84.8466</v>
       </c>
     </row>
     <row r="49">
@@ -15508,7 +15508,7 @@
         </is>
       </c>
       <c r="C49" s="24" t="n">
-        <v>328.65</v>
+        <v>339.53</v>
       </c>
       <c r="D49" s="22" t="inlineStr">
         <is>
@@ -15516,19 +15516,19 @@
         </is>
       </c>
       <c r="E49" s="24" t="n">
-        <v>39.5068</v>
+        <v>39.5062</v>
       </c>
       <c r="F49" s="24" t="n">
-        <v>59.2602</v>
+        <v>59.2593</v>
       </c>
       <c r="G49" s="24" t="n">
-        <v>90.8656</v>
+        <v>90.8643</v>
       </c>
       <c r="H49" s="24" t="n">
-        <v>118.5204</v>
+        <v>118.5187</v>
       </c>
       <c r="I49" s="24" t="n">
-        <v>118.5204</v>
+        <v>118.5187</v>
       </c>
       <c r="J49" s="26" t="inlineStr">
         <is>
@@ -15536,10 +15536,10 @@
         </is>
       </c>
       <c r="K49" s="24" t="n">
-        <v>4.1594</v>
+        <v>4.2972</v>
       </c>
       <c r="L49" s="24" t="n">
-        <v>59.2602</v>
+        <v>59.2593</v>
       </c>
     </row>
     <row r="50">
@@ -15554,7 +15554,7 @@
         </is>
       </c>
       <c r="C50" s="24" t="n">
-        <v>281.34</v>
+        <v>279.49</v>
       </c>
       <c r="D50" s="22" t="inlineStr">
         <is>
@@ -15582,7 +15582,7 @@
         </is>
       </c>
       <c r="K50" s="24" t="n">
-        <v>27.0272</v>
+        <v>26.8495</v>
       </c>
       <c r="L50" s="24" t="n">
         <v>7.8071</v>
@@ -15600,7 +15600,7 @@
         </is>
       </c>
       <c r="C51" s="24" t="n">
-        <v>473.18</v>
+        <v>462.6</v>
       </c>
       <c r="D51" s="22" t="inlineStr">
         <is>
@@ -15628,7 +15628,7 @@
         </is>
       </c>
       <c r="K51" s="24" t="n">
-        <v>70.8306</v>
+        <v>69.24679999999999</v>
       </c>
       <c r="L51" s="24" t="n">
         <v>5.0103</v>
@@ -16719,7 +16719,7 @@
         </is>
       </c>
       <c r="C2" s="34" t="n">
-        <v>161.4</v>
+        <v>160.6</v>
       </c>
       <c r="D2" s="32" t="inlineStr"/>
       <c r="E2" s="32" t="n">
@@ -16799,7 +16799,7 @@
         </is>
       </c>
       <c r="C3" s="34" t="n">
-        <v>5.49</v>
+        <v>5.36</v>
       </c>
       <c r="D3" s="32" t="n">
         <v>41534000000</v>
@@ -16895,7 +16895,7 @@
         </is>
       </c>
       <c r="C4" s="34" t="n">
-        <v>1.265</v>
+        <v>1.2</v>
       </c>
       <c r="D4" s="32" t="n">
         <v>5567388000</v>
@@ -16987,7 +16987,7 @@
         </is>
       </c>
       <c r="C5" s="34" t="n">
-        <v>87.89</v>
+        <v>86</v>
       </c>
       <c r="D5" s="32" t="n">
         <v>467223292000</v>
@@ -17085,7 +17085,7 @@
         </is>
       </c>
       <c r="C6" s="34" t="n">
-        <v>38.61</v>
+        <v>38.23</v>
       </c>
       <c r="D6" s="32" t="n">
         <v>163171733641.44</v>
@@ -17183,7 +17183,7 @@
         </is>
       </c>
       <c r="C7" s="34" t="n">
-        <v>29</v>
+        <v>28.69</v>
       </c>
       <c r="D7" s="32" t="n">
         <v>8311446273.629999</v>
@@ -17281,7 +17281,7 @@
         </is>
       </c>
       <c r="C8" s="34" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="D8" s="32" t="n">
         <v>24829258000</v>
@@ -17379,7 +17379,7 @@
         </is>
       </c>
       <c r="C9" s="34" t="n">
-        <v>33.22</v>
+        <v>32.8</v>
       </c>
       <c r="D9" s="32" t="n">
         <v>592527830000</v>
@@ -17477,7 +17477,7 @@
         </is>
       </c>
       <c r="C10" s="34" t="n">
-        <v>4.67</v>
+        <v>4.58</v>
       </c>
       <c r="D10" s="32" t="n">
         <v>2755453000000</v>
@@ -17571,7 +17571,7 @@
         </is>
       </c>
       <c r="C11" s="34" t="n">
-        <v>396</v>
+        <v>393.6</v>
       </c>
       <c r="D11" s="32" t="inlineStr"/>
       <c r="E11" s="32" t="n">
@@ -17651,7 +17651,7 @@
         </is>
       </c>
       <c r="C12" s="34" t="n">
-        <v>437.8</v>
+        <v>434.2</v>
       </c>
       <c r="D12" s="32" t="n">
         <v>778561000000</v>
@@ -17749,7 +17749,7 @@
         </is>
       </c>
       <c r="C13" s="34" t="n">
-        <v>5.91</v>
+        <v>5.78</v>
       </c>
       <c r="D13" s="32" t="n">
         <v>393385000000</v>
@@ -17847,7 +17847,7 @@
         </is>
       </c>
       <c r="C14" s="34" t="n">
-        <v>9.02</v>
+        <v>8.984999999999999</v>
       </c>
       <c r="D14" s="32" t="n">
         <v>99503000000</v>
@@ -17945,7 +17945,7 @@
         </is>
       </c>
       <c r="C15" s="34" t="n">
-        <v>18.76</v>
+        <v>18.78</v>
       </c>
       <c r="D15" s="32" t="n">
         <v>106719928000</v>
@@ -18043,7 +18043,7 @@
         </is>
       </c>
       <c r="C16" s="34" t="n">
-        <v>9.91</v>
+        <v>9.994999999999999</v>
       </c>
       <c r="D16" s="32" t="n">
         <v>2941939000000</v>
@@ -18141,7 +18141,7 @@
         </is>
       </c>
       <c r="C17" s="34" t="n">
-        <v>24.46</v>
+        <v>24.76</v>
       </c>
       <c r="D17" s="32" t="n">
         <v>424075000000</v>
@@ -18235,7 +18235,7 @@
         </is>
       </c>
       <c r="C18" s="34" t="n">
-        <v>9.654999999999999</v>
+        <v>9.625</v>
       </c>
       <c r="D18" s="32" t="inlineStr"/>
       <c r="E18" s="32" t="n">
@@ -18315,7 +18315,7 @@
         </is>
       </c>
       <c r="C19" s="34" t="n">
-        <v>79.2</v>
+        <v>79.25</v>
       </c>
       <c r="D19" s="32" t="n">
         <v>881204000000</v>
@@ -18413,7 +18413,7 @@
         </is>
       </c>
       <c r="C20" s="34" t="n">
-        <v>5.315</v>
+        <v>5.27</v>
       </c>
       <c r="D20" s="32" t="n">
         <v>78353551000</v>
@@ -18511,7 +18511,7 @@
         </is>
       </c>
       <c r="C21" s="34" t="n">
-        <v>61.45</v>
+        <v>61.35</v>
       </c>
       <c r="D21" s="32" t="n">
         <v>10381607000</v>
@@ -18607,7 +18607,7 @@
         </is>
       </c>
       <c r="C22" s="34" t="n">
-        <v>32.04</v>
+        <v>31.94</v>
       </c>
       <c r="D22" s="32" t="n">
         <v>91187452000</v>
@@ -18703,7 +18703,7 @@
         </is>
       </c>
       <c r="C23" s="34" t="n">
-        <v>7.495</v>
+        <v>7.505</v>
       </c>
       <c r="D23" s="32" t="inlineStr"/>
       <c r="E23" s="32" t="n">
@@ -18783,7 +18783,7 @@
         </is>
       </c>
       <c r="C24" s="34" t="n">
-        <v>27.16</v>
+        <v>26.04</v>
       </c>
       <c r="D24" s="32" t="n">
         <v>438100486000</v>
@@ -18881,7 +18881,7 @@
         </is>
       </c>
       <c r="C25" s="34" t="n">
-        <v>3.015</v>
+        <v>3.04</v>
       </c>
       <c r="D25" s="32" t="n">
         <v>74803686551.5</v>
@@ -18979,7 +18979,7 @@
         </is>
       </c>
       <c r="C26" s="34" t="n">
-        <v>0.171</v>
+        <v>0.17</v>
       </c>
       <c r="D26" s="32" t="n">
         <v>126404000000</v>
@@ -19071,7 +19071,7 @@
         </is>
       </c>
       <c r="C27" s="34" t="n">
-        <v>53.5</v>
+        <v>53.05</v>
       </c>
       <c r="D27" s="32" t="n">
         <v>73638000000</v>
@@ -19165,7 +19165,7 @@
         </is>
       </c>
       <c r="C28" s="34" t="n">
-        <v>196</v>
+        <v>196.8</v>
       </c>
       <c r="D28" s="32" t="n">
         <v>53554363000</v>
@@ -19263,7 +19263,7 @@
         </is>
       </c>
       <c r="C29" s="34" t="n">
-        <v>3.295</v>
+        <v>3.325</v>
       </c>
       <c r="D29" s="32" t="n">
         <v>15283876000</v>
@@ -19361,7 +19361,7 @@
         </is>
       </c>
       <c r="C30" s="34" t="n">
-        <v>48.72</v>
+        <v>50.4</v>
       </c>
       <c r="D30" s="32" t="n">
         <v>113253000000</v>
@@ -19459,7 +19459,7 @@
         </is>
       </c>
       <c r="C31" s="34" t="n">
-        <v>75.45</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="D31" s="32" t="n">
         <v>382840334000</v>
@@ -19553,7 +19553,7 @@
         </is>
       </c>
       <c r="C32" s="34" t="n">
-        <v>542</v>
+        <v>492.2</v>
       </c>
       <c r="D32" s="32" t="n">
         <v>521732161000</v>
@@ -19645,7 +19645,7 @@
         </is>
       </c>
       <c r="C33" s="34" t="n">
-        <v>51.45</v>
+        <v>51.25</v>
       </c>
       <c r="D33" s="32" t="inlineStr"/>
       <c r="E33" s="32" t="n">
@@ -19725,7 +19725,7 @@
         </is>
       </c>
       <c r="C34" s="34" t="n">
-        <v>4.3</v>
+        <v>4.215</v>
       </c>
       <c r="D34" s="32" t="n">
         <v>27349980000</v>
@@ -19823,7 +19823,7 @@
         </is>
       </c>
       <c r="C35" s="34" t="n">
-        <v>21.58</v>
+        <v>21.14</v>
       </c>
       <c r="D35" s="32" t="n">
         <v>70315732000</v>
@@ -19915,7 +19915,7 @@
         </is>
       </c>
       <c r="C36" s="34" t="n">
-        <v>106.3</v>
+        <v>105.2</v>
       </c>
       <c r="D36" s="32" t="n">
         <v>1313438000000</v>
@@ -20011,7 +20011,7 @@
         </is>
       </c>
       <c r="C37" s="34" t="n">
-        <v>308</v>
+        <v>303.6</v>
       </c>
       <c r="D37" s="32" t="n">
         <v>58007000000</v>
@@ -20105,7 +20105,7 @@
         </is>
       </c>
       <c r="C38" s="34" t="n">
-        <v>106.7</v>
+        <v>106.6</v>
       </c>
       <c r="D38" s="32" t="n">
         <v>1044971000000</v>
@@ -20201,7 +20201,7 @@
         </is>
       </c>
       <c r="C39" s="34" t="n">
-        <v>187.2</v>
+        <v>183.8</v>
       </c>
       <c r="D39" s="32" t="n">
         <v>116603425000</v>
@@ -20297,7 +20297,7 @@
         </is>
       </c>
       <c r="C40" s="34" t="n">
-        <v>84.58</v>
+        <v>83.75</v>
       </c>
       <c r="D40" s="32" t="n">
         <v>76563498483.70999</v>
@@ -20395,7 +20395,7 @@
         </is>
       </c>
       <c r="C41" s="34" t="n">
-        <v>159.68</v>
+        <v>158.92</v>
       </c>
       <c r="D41" s="32" t="n">
         <v>34286125154</v>
@@ -20493,7 +20493,7 @@
         </is>
       </c>
       <c r="C42" s="34" t="n">
-        <v>43.26</v>
+        <v>43.22</v>
       </c>
       <c r="D42" s="32" t="n">
         <v>31323806293.04</v>
@@ -20591,7 +20591,7 @@
         </is>
       </c>
       <c r="C43" s="34" t="n">
-        <v>118.28</v>
+        <v>116.82</v>
       </c>
       <c r="D43" s="32" t="n">
         <v>8195718293.669999</v>
@@ -20689,7 +20689,7 @@
         </is>
       </c>
       <c r="C44" s="34" t="n">
-        <v>1276.81</v>
+        <v>1264.75</v>
       </c>
       <c r="D44" s="32" t="n">
         <v>173238481420.15</v>
@@ -20787,7 +20787,7 @@
         </is>
       </c>
       <c r="C45" s="34" t="n">
-        <v>28.5</v>
+        <v>28.36</v>
       </c>
       <c r="D45" s="32" t="n">
         <v>87473595082.66</v>
@@ -20885,7 +20885,7 @@
         </is>
       </c>
       <c r="C46" s="34" t="n">
-        <v>61.82</v>
+        <v>60.94</v>
       </c>
       <c r="D46" s="32" t="n">
         <v>1099988180000</v>
@@ -20983,7 +20983,7 @@
         </is>
       </c>
       <c r="C47" s="34" t="n">
-        <v>56.71</v>
+        <v>56</v>
       </c>
       <c r="D47" s="32" t="n">
         <v>10610338770.93</v>
@@ -21081,7 +21081,7 @@
         </is>
       </c>
       <c r="C48" s="34" t="n">
-        <v>85.59999999999999</v>
+        <v>85.59</v>
       </c>
       <c r="D48" s="32" t="n">
         <v>17329374760.94</v>
@@ -21177,7 +21177,7 @@
         </is>
       </c>
       <c r="C49" s="34" t="n">
-        <v>328.65</v>
+        <v>339.53</v>
       </c>
       <c r="D49" s="32" t="n">
         <v>14115324325.74</v>
@@ -21273,7 +21273,7 @@
         </is>
       </c>
       <c r="C50" s="34" t="n">
-        <v>281.34</v>
+        <v>279.49</v>
       </c>
       <c r="D50" s="32" t="n">
         <v>667851292.67</v>
@@ -21369,7 +21369,7 @@
         </is>
       </c>
       <c r="C51" s="34" t="n">
-        <v>473.18</v>
+        <v>462.6</v>
       </c>
       <c r="D51" s="32" t="n">
         <v>2075795642.82</v>
@@ -23190,7 +23190,7 @@
         </is>
       </c>
       <c r="C2" s="24" t="n">
-        <v>161.4</v>
+        <v>160.6</v>
       </c>
       <c r="D2" s="22" t="n">
         <v>4</v>
@@ -23251,7 +23251,7 @@
         </is>
       </c>
       <c r="C3" s="29" t="n">
-        <v>5.49</v>
+        <v>5.36</v>
       </c>
       <c r="D3" s="27" t="n">
         <v>2</v>
@@ -23312,7 +23312,7 @@
         </is>
       </c>
       <c r="C4" s="24" t="n">
-        <v>1.265</v>
+        <v>1.2</v>
       </c>
       <c r="D4" s="22" t="n">
         <v>1.5</v>
@@ -23373,7 +23373,7 @@
         </is>
       </c>
       <c r="C5" s="14" t="n">
-        <v>87.89</v>
+        <v>86</v>
       </c>
       <c r="D5" s="12" t="n">
         <v>7</v>
@@ -23434,7 +23434,7 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>38.61</v>
+        <v>38.23</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>8</v>
@@ -23495,7 +23495,7 @@
         </is>
       </c>
       <c r="C7" s="19" t="n">
-        <v>29</v>
+        <v>28.69</v>
       </c>
       <c r="D7" s="17" t="n">
         <v>3.5</v>
@@ -23556,7 +23556,7 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>7.2</v>
@@ -23617,7 +23617,7 @@
         </is>
       </c>
       <c r="C9" s="14" t="n">
-        <v>33.22</v>
+        <v>32.8</v>
       </c>
       <c r="D9" s="12" t="n">
         <v>3.4</v>
@@ -23638,7 +23638,7 @@
         </is>
       </c>
       <c r="H9" s="12" t="n">
-        <v>82.09999999999999</v>
+        <v>82.2</v>
       </c>
       <c r="I9" s="13" t="inlineStr">
         <is>
@@ -23667,61 +23667,61 @@
       </c>
     </row>
     <row r="10" ht="118" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>00386</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>中国石油化工股份</t>
         </is>
       </c>
-      <c r="C10" s="9" t="n">
-        <v>4.67</v>
-      </c>
-      <c r="D10" s="7" t="n">
+      <c r="C10" s="4" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="D10" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E10" s="7" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>★★☆☆☆</t>
         </is>
       </c>
-      <c r="F10" s="11" t="inlineStr">
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>非常便宜</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>便宜</t>
         </is>
       </c>
-      <c r="G10" s="7" t="inlineStr">
-        <is>
-          <t>便宜</t>
-        </is>
-      </c>
-      <c r="H10" s="7" t="n">
+      <c r="H10" s="2" t="n">
         <v>92.59999999999999</v>
       </c>
-      <c r="I10" s="8" t="inlineStr">
+      <c r="I10" s="3" t="inlineStr">
         <is>
           <t>獲利極薄、營收衰退，但現金流穩健且連續派息</t>
         </is>
       </c>
-      <c r="J10" s="8" t="inlineStr">
+      <c r="J10" s="3" t="inlineStr">
         <is>
           <t>獲利品質：TTM經營現金流1,640億遠超歸母淨利353億，現金轉換能力佳，但營業利益率僅1.9%、淨利率1.28%，獲利極薄。資產負債：負債權益比0.67尚可，惟流動比率僅0.86、利息保障倍數2.74倍，短期償債與付息壓力偏大。成長與再投資：三年營收CAGR為-5.76%，五年EPS CAGR為-0.59%，ROIC僅3.54%，資本回報低迷。估值：加權內在價值9.29港元，現價4.78對應0.51倍，已達25%安全邊際；然達摩達蘭FCFF模型僅估1.28港元，嚴厲反映薄利與負成長。結論：屬低品質便宜，宜小倉位配置，重點追蹤營業利益率能否回升至3%以上及資本支出方向。</t>
         </is>
       </c>
-      <c r="K10" s="8" t="inlineStr">
+      <c r="K10" s="3" t="inlineStr">
         <is>
           <t>營業利益率僅1.9%，獲利極薄 / 流動比率0.86，短期償債承壓 / 三年營收CAGR -5.76%，需求走弱</t>
         </is>
       </c>
-      <c r="L10" s="7" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>qwen3.8-max</t>
         </is>
       </c>
-      <c r="M10" s="7" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>2026-09-12</t>
         </is>
@@ -23739,7 +23739,7 @@
         </is>
       </c>
       <c r="C11" s="24" t="n">
-        <v>396</v>
+        <v>393.6</v>
       </c>
       <c r="D11" s="22" t="n">
         <v>3.2</v>
@@ -23800,7 +23800,7 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>437.8</v>
+        <v>434.2</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>7.2</v>
@@ -23861,7 +23861,7 @@
         </is>
       </c>
       <c r="C13" s="9" t="n">
-        <v>5.91</v>
+        <v>5.78</v>
       </c>
       <c r="D13" s="7" t="n">
         <v>7.2</v>
@@ -23922,7 +23922,7 @@
         </is>
       </c>
       <c r="C14" s="14" t="n">
-        <v>9.02</v>
+        <v>8.984999999999999</v>
       </c>
       <c r="D14" s="12" t="n">
         <v>6.2</v>
@@ -23943,7 +23943,7 @@
         </is>
       </c>
       <c r="H14" s="12" t="n">
-        <v>85.90000000000001</v>
+        <v>86</v>
       </c>
       <c r="I14" s="13" t="inlineStr">
         <is>
@@ -23983,7 +23983,7 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>18.76</v>
+        <v>18.78</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>6.5</v>
@@ -24044,7 +24044,7 @@
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>9.91</v>
+        <v>9.994999999999999</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>8.199999999999999</v>
@@ -24105,7 +24105,7 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>24.46</v>
+        <v>24.76</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>8.5</v>
@@ -24166,7 +24166,7 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>9.654999999999999</v>
+        <v>9.625</v>
       </c>
       <c r="D18" s="2" t="n">
         <v>5</v>
@@ -24227,7 +24227,7 @@
         </is>
       </c>
       <c r="C19" s="14" t="n">
-        <v>79.2</v>
+        <v>79.25</v>
       </c>
       <c r="D19" s="12" t="n">
         <v>7</v>
@@ -24288,7 +24288,7 @@
         </is>
       </c>
       <c r="C20" s="29" t="n">
-        <v>5.315</v>
+        <v>5.27</v>
       </c>
       <c r="D20" s="27" t="n">
         <v>3.3</v>
@@ -24349,7 +24349,7 @@
         </is>
       </c>
       <c r="C21" s="24" t="n">
-        <v>61.45</v>
+        <v>61.35</v>
       </c>
       <c r="D21" s="22" t="n">
         <v>1.7</v>
@@ -24410,7 +24410,7 @@
         </is>
       </c>
       <c r="C22" s="14" t="n">
-        <v>32.04</v>
+        <v>31.94</v>
       </c>
       <c r="D22" s="12" t="n">
         <v>3.8</v>
@@ -24471,7 +24471,7 @@
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>7.495</v>
+        <v>7.505</v>
       </c>
       <c r="D23" s="2" t="n">
         <v>4.5</v>
@@ -24532,7 +24532,7 @@
         </is>
       </c>
       <c r="C24" s="14" t="n">
-        <v>27.16</v>
+        <v>26.04</v>
       </c>
       <c r="D24" s="12" t="n">
         <v>5.5</v>
@@ -24593,7 +24593,7 @@
         </is>
       </c>
       <c r="C25" s="19" t="n">
-        <v>3.015</v>
+        <v>3.04</v>
       </c>
       <c r="D25" s="17" t="n">
         <v>4</v>
@@ -24654,7 +24654,7 @@
         </is>
       </c>
       <c r="C26" s="29" t="n">
-        <v>0.171</v>
+        <v>0.17</v>
       </c>
       <c r="D26" s="27" t="n">
         <v>1</v>
@@ -24715,7 +24715,7 @@
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>53.5</v>
+        <v>53.05</v>
       </c>
       <c r="D27" s="2" t="n">
         <v>4.5</v>
@@ -24776,7 +24776,7 @@
         </is>
       </c>
       <c r="C28" s="24" t="n">
-        <v>196</v>
+        <v>196.8</v>
       </c>
       <c r="D28" s="22" t="n">
         <v>4.3</v>
@@ -24837,7 +24837,7 @@
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>3.295</v>
+        <v>3.325</v>
       </c>
       <c r="D29" s="2" t="n">
         <v>8.300000000000001</v>
@@ -24898,7 +24898,7 @@
         </is>
       </c>
       <c r="C30" s="9" t="n">
-        <v>48.72</v>
+        <v>50.4</v>
       </c>
       <c r="D30" s="7" t="n">
         <v>7</v>
@@ -24959,7 +24959,7 @@
         </is>
       </c>
       <c r="C31" s="24" t="n">
-        <v>75.45</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="D31" s="22" t="n">
         <v>1.5</v>
@@ -25020,7 +25020,7 @@
         </is>
       </c>
       <c r="C32" s="19" t="n">
-        <v>542</v>
+        <v>492.2</v>
       </c>
       <c r="D32" s="17" t="n">
         <v>4.5</v>
@@ -25081,7 +25081,7 @@
         </is>
       </c>
       <c r="C33" s="4" t="n">
-        <v>51.45</v>
+        <v>51.25</v>
       </c>
       <c r="D33" s="2" t="n">
         <v>6.8</v>
@@ -25142,7 +25142,7 @@
         </is>
       </c>
       <c r="C34" s="9" t="n">
-        <v>4.3</v>
+        <v>4.215</v>
       </c>
       <c r="D34" s="7" t="n">
         <v>8.199999999999999</v>
@@ -25203,7 +25203,7 @@
         </is>
       </c>
       <c r="C35" s="24" t="n">
-        <v>21.58</v>
+        <v>21.14</v>
       </c>
       <c r="D35" s="22" t="n">
         <v>3</v>
@@ -25264,7 +25264,7 @@
         </is>
       </c>
       <c r="C36" s="14" t="n">
-        <v>106.3</v>
+        <v>105.2</v>
       </c>
       <c r="D36" s="12" t="n">
         <v>4.5</v>
@@ -25325,7 +25325,7 @@
         </is>
       </c>
       <c r="C37" s="9" t="n">
-        <v>308</v>
+        <v>303.6</v>
       </c>
       <c r="D37" s="7" t="n">
         <v>6.5</v>
@@ -25386,7 +25386,7 @@
         </is>
       </c>
       <c r="C38" s="24" t="n">
-        <v>106.7</v>
+        <v>106.6</v>
       </c>
       <c r="D38" s="22" t="n">
         <v>3.2</v>
@@ -25447,7 +25447,7 @@
         </is>
       </c>
       <c r="C39" s="9" t="n">
-        <v>187.2</v>
+        <v>183.8</v>
       </c>
       <c r="D39" s="7" t="n">
         <v>7.8</v>
@@ -25508,7 +25508,7 @@
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>84.58</v>
+        <v>83.75</v>
       </c>
       <c r="D40" s="7" t="n">
         <v>7.8</v>
@@ -25569,7 +25569,7 @@
         </is>
       </c>
       <c r="C41" s="14" t="n">
-        <v>159.68</v>
+        <v>158.92</v>
       </c>
       <c r="D41" s="12" t="n">
         <v>6.8</v>
@@ -25630,7 +25630,7 @@
         </is>
       </c>
       <c r="C42" s="24" t="n">
-        <v>43.26</v>
+        <v>43.22</v>
       </c>
       <c r="D42" s="22" t="n">
         <v>4.3</v>
@@ -25691,7 +25691,7 @@
         </is>
       </c>
       <c r="C43" s="24" t="n">
-        <v>118.28</v>
+        <v>116.82</v>
       </c>
       <c r="D43" s="22" t="n">
         <v>3.8</v>
@@ -25752,7 +25752,7 @@
         </is>
       </c>
       <c r="C44" s="14" t="n">
-        <v>1276.81</v>
+        <v>1264.75</v>
       </c>
       <c r="D44" s="12" t="n">
         <v>7.2</v>
@@ -25813,7 +25813,7 @@
         </is>
       </c>
       <c r="C45" s="19" t="n">
-        <v>28.5</v>
+        <v>28.36</v>
       </c>
       <c r="D45" s="17" t="n">
         <v>4.5</v>
@@ -25874,7 +25874,7 @@
         </is>
       </c>
       <c r="C46" s="24" t="n">
-        <v>61.82</v>
+        <v>60.94</v>
       </c>
       <c r="D46" s="22" t="n">
         <v>2.7</v>
@@ -25895,7 +25895,7 @@
         </is>
       </c>
       <c r="H46" s="22" t="n">
-        <v>92.2</v>
+        <v>92.3</v>
       </c>
       <c r="I46" s="23" t="inlineStr">
         <is>
@@ -25935,7 +25935,7 @@
         </is>
       </c>
       <c r="C47" s="9" t="n">
-        <v>56.71</v>
+        <v>56</v>
       </c>
       <c r="D47" s="7" t="n">
         <v>8</v>
@@ -25996,7 +25996,7 @@
         </is>
       </c>
       <c r="C48" s="14" t="n">
-        <v>85.59999999999999</v>
+        <v>85.59</v>
       </c>
       <c r="D48" s="12" t="n">
         <v>7.2</v>
@@ -26057,7 +26057,7 @@
         </is>
       </c>
       <c r="C49" s="24" t="n">
-        <v>328.65</v>
+        <v>339.53</v>
       </c>
       <c r="D49" s="22" t="n">
         <v>3.5</v>
@@ -26118,7 +26118,7 @@
         </is>
       </c>
       <c r="C50" s="24" t="n">
-        <v>281.34</v>
+        <v>279.49</v>
       </c>
       <c r="D50" s="22" t="n">
         <v>2.5</v>
@@ -26179,7 +26179,7 @@
         </is>
       </c>
       <c r="C51" s="24" t="n">
-        <v>473.18</v>
+        <v>462.6</v>
       </c>
       <c r="D51" s="22" t="n">
         <v>1.8</v>

--- a/docs/reports/內在價值報告_20260916.xlsx
+++ b/docs/reports/內在價值報告_20260916.xlsx
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>413.19</v>
+        <v>418.52</v>
       </c>
       <c r="E6" s="3" t="inlineStr"/>
       <c r="F6" s="2" t="inlineStr">
@@ -1316,22 +1316,22 @@
       </c>
       <c r="H6" s="3" t="inlineStr"/>
       <c r="I6" s="4" t="n">
-        <v>6265.3259</v>
+        <v>6265.3212</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>539.357</v>
+        <v>539.3388</v>
       </c>
       <c r="K6" s="4" t="n">
         <v>5285.4917</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>-93.40000000000001</v>
+        <v>-93.3</v>
       </c>
       <c r="M6" s="5" t="n">
         <v>25</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>4698.9944</v>
+        <v>4698.9909</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>515.035</v>
+        <v>520.47</v>
       </c>
       <c r="E10" s="3" t="inlineStr"/>
       <c r="F10" s="2" t="inlineStr">
@@ -3357,7 +3357,7 @@
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>264.28</v>
+        <v>267.14</v>
       </c>
       <c r="E23" s="8" t="inlineStr"/>
       <c r="F23" s="7" t="inlineStr">
@@ -3372,22 +3372,22 @@
       </c>
       <c r="H23" s="8" t="inlineStr"/>
       <c r="I23" s="9" t="n">
-        <v>480.8095</v>
+        <v>480.8071</v>
       </c>
       <c r="J23" s="9" t="n">
         <v>9.3416</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>17.7693</v>
+        <v>17.7687</v>
       </c>
       <c r="L23" s="10" t="n">
-        <v>-45</v>
+        <v>-44.4</v>
       </c>
       <c r="M23" s="10" t="n">
         <v>25</v>
       </c>
       <c r="N23" s="9" t="n">
-        <v>360.6071</v>
+        <v>360.6053</v>
       </c>
       <c r="O23" s="7" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="D34" s="14" t="n">
-        <v>376.82</v>
+        <v>378.87</v>
       </c>
       <c r="E34" s="13" t="inlineStr"/>
       <c r="F34" s="12" t="inlineStr">
@@ -4702,7 +4702,7 @@
       </c>
       <c r="H34" s="13" t="inlineStr"/>
       <c r="I34" s="14" t="n">
-        <v>369.4246</v>
+        <v>369.4242</v>
       </c>
       <c r="J34" s="14" t="n">
         <v>64.4277</v>
@@ -4711,13 +4711,13 @@
         <v>314.2098</v>
       </c>
       <c r="L34" s="15" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="M34" s="15" t="n">
         <v>25</v>
       </c>
       <c r="N34" s="14" t="n">
-        <v>277.0685</v>
+        <v>277.0682</v>
       </c>
       <c r="O34" s="12" t="inlineStr">
         <is>
@@ -5897,7 +5897,7 @@
         </is>
       </c>
       <c r="D44" s="24" t="n">
-        <v>211.864</v>
+        <v>216.05</v>
       </c>
       <c r="E44" s="23" t="inlineStr"/>
       <c r="F44" s="22" t="inlineStr">
@@ -5912,16 +5912,16 @@
       </c>
       <c r="H44" s="23" t="inlineStr"/>
       <c r="I44" s="24" t="n">
-        <v>45.7475</v>
+        <v>45.7474</v>
       </c>
       <c r="J44" s="24" t="n">
-        <v>6.8367</v>
+        <v>6.8365</v>
       </c>
       <c r="K44" s="24" t="n">
         <v>31.5866</v>
       </c>
       <c r="L44" s="25" t="n">
-        <v>363.1</v>
+        <v>372.3</v>
       </c>
       <c r="M44" s="25" t="n">
         <v>25</v>
@@ -6381,7 +6381,7 @@
         </is>
       </c>
       <c r="D48" s="24" t="n">
-        <v>330.16</v>
+        <v>333.72</v>
       </c>
       <c r="E48" s="23" t="inlineStr"/>
       <c r="F48" s="22" t="inlineStr">
@@ -6396,7 +6396,7 @@
       </c>
       <c r="H48" s="23" t="inlineStr"/>
       <c r="I48" s="24" t="n">
-        <v>49.1606</v>
+        <v>49.1605</v>
       </c>
       <c r="J48" s="24" t="n">
         <v>9.446</v>
@@ -6405,13 +6405,13 @@
         <v>34.7808</v>
       </c>
       <c r="L48" s="25" t="n">
-        <v>571.6</v>
+        <v>578.8</v>
       </c>
       <c r="M48" s="25" t="n">
         <v>25</v>
       </c>
       <c r="N48" s="24" t="n">
-        <v>36.8705</v>
+        <v>36.8704</v>
       </c>
       <c r="O48" s="22" t="inlineStr">
         <is>
@@ -6503,7 +6503,7 @@
         </is>
       </c>
       <c r="D49" s="24" t="n">
-        <v>170.905</v>
+        <v>172.795</v>
       </c>
       <c r="E49" s="23" t="inlineStr"/>
       <c r="F49" s="22" t="inlineStr">
@@ -6518,16 +6518,16 @@
       </c>
       <c r="H49" s="23" t="inlineStr"/>
       <c r="I49" s="24" t="n">
-        <v>21.4774</v>
+        <v>21.4773</v>
       </c>
       <c r="J49" s="24" t="n">
         <v>4.7985</v>
       </c>
       <c r="K49" s="24" t="n">
-        <v>5.0403</v>
+        <v>5.0402</v>
       </c>
       <c r="L49" s="25" t="n">
-        <v>695.7</v>
+        <v>704.5</v>
       </c>
       <c r="M49" s="25" t="n">
         <v>25</v>
@@ -6623,7 +6623,7 @@
         </is>
       </c>
       <c r="D50" s="24" t="n">
-        <v>500.25</v>
+        <v>494.77</v>
       </c>
       <c r="E50" s="23" t="inlineStr"/>
       <c r="F50" s="22" t="inlineStr">
@@ -6641,13 +6641,13 @@
         <v>81.6729</v>
       </c>
       <c r="J50" s="24" t="n">
-        <v>3.4476</v>
+        <v>3.4477</v>
       </c>
       <c r="K50" s="24" t="n">
         <v>86.59699999999999</v>
       </c>
       <c r="L50" s="25" t="n">
-        <v>512.5</v>
+        <v>505.8</v>
       </c>
       <c r="M50" s="25" t="n">
         <v>25</v>
@@ -6985,7 +6985,7 @@
         </is>
       </c>
       <c r="D53" s="24" t="n">
-        <v>1141.305</v>
+        <v>1143.525</v>
       </c>
       <c r="E53" s="23" t="inlineStr"/>
       <c r="F53" s="22" t="inlineStr">
@@ -7000,22 +7000,22 @@
       </c>
       <c r="H53" s="23" t="inlineStr"/>
       <c r="I53" s="24" t="n">
-        <v>544.7405</v>
+        <v>544.7394</v>
       </c>
       <c r="J53" s="24" t="n">
-        <v>58.8492</v>
+        <v>58.849</v>
       </c>
       <c r="K53" s="24" t="n">
         <v>202.834</v>
       </c>
       <c r="L53" s="25" t="n">
-        <v>109.5</v>
+        <v>109.9</v>
       </c>
       <c r="M53" s="25" t="n">
         <v>25</v>
       </c>
       <c r="N53" s="24" t="n">
-        <v>408.5553</v>
+        <v>408.5545</v>
       </c>
       <c r="O53" s="22" t="inlineStr">
         <is>
@@ -7107,7 +7107,7 @@
         </is>
       </c>
       <c r="D54" s="24" t="n">
-        <v>374.57</v>
+        <v>372.25</v>
       </c>
       <c r="E54" s="23" t="inlineStr"/>
       <c r="F54" s="22" t="inlineStr">
@@ -7131,7 +7131,7 @@
         <v>61.9902</v>
       </c>
       <c r="L54" s="25" t="n">
-        <v>590.3</v>
+        <v>586.1</v>
       </c>
       <c r="M54" s="25" t="n">
         <v>25</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="D55" s="24" t="n">
-        <v>249.04</v>
+        <v>247.96</v>
       </c>
       <c r="E55" s="23" t="inlineStr"/>
       <c r="F55" s="22" t="inlineStr">
@@ -7253,7 +7253,7 @@
         <v>487.2973</v>
       </c>
       <c r="L55" s="25" t="n">
-        <v>132.6</v>
+        <v>131.6</v>
       </c>
       <c r="M55" s="25" t="n">
         <v>25</v>
@@ -7351,7 +7351,7 @@
         </is>
       </c>
       <c r="D56" s="24" t="n">
-        <v>344.15</v>
+        <v>346.815</v>
       </c>
       <c r="E56" s="23" t="inlineStr"/>
       <c r="F56" s="22" t="inlineStr">
@@ -7375,7 +7375,7 @@
         <v>15.3128</v>
       </c>
       <c r="L56" s="25" t="n">
-        <v>447.5</v>
+        <v>451.8</v>
       </c>
       <c r="M56" s="25" t="n">
         <v>25</v>
@@ -7473,7 +7473,7 @@
         </is>
       </c>
       <c r="D57" s="24" t="n">
-        <v>34.325</v>
+        <v>34.255</v>
       </c>
       <c r="E57" s="23" t="inlineStr"/>
       <c r="F57" s="22" t="inlineStr">
@@ -7497,7 +7497,7 @@
         <v>5.2053</v>
       </c>
       <c r="L57" s="25" t="n">
-        <v>687</v>
+        <v>685.4</v>
       </c>
       <c r="M57" s="25" t="n">
         <v>25</v>
@@ -7595,7 +7595,7 @@
         </is>
       </c>
       <c r="D58" s="24" t="n">
-        <v>108.54</v>
+        <v>108.39</v>
       </c>
       <c r="E58" s="23" t="inlineStr"/>
       <c r="F58" s="22" t="inlineStr">
@@ -7619,7 +7619,7 @@
         <v>28.2934</v>
       </c>
       <c r="L58" s="25" t="n">
-        <v>817.4</v>
+        <v>816.1</v>
       </c>
       <c r="M58" s="25" t="n">
         <v>25</v>
@@ -7717,7 +7717,7 @@
         </is>
       </c>
       <c r="D59" s="24" t="n">
-        <v>275.895</v>
+        <v>280.01</v>
       </c>
       <c r="E59" s="23" t="inlineStr"/>
       <c r="F59" s="22" t="inlineStr">
@@ -7732,7 +7732,7 @@
       </c>
       <c r="H59" s="23" t="inlineStr"/>
       <c r="I59" s="24" t="n">
-        <v>26.967</v>
+        <v>26.9669</v>
       </c>
       <c r="J59" s="24" t="n">
         <v>1.7995</v>
@@ -7741,7 +7741,7 @@
         <v>8.8208</v>
       </c>
       <c r="L59" s="25" t="n">
-        <v>923.1</v>
+        <v>938.3</v>
       </c>
       <c r="M59" s="25" t="n">
         <v>25</v>
@@ -7839,7 +7839,7 @@
         </is>
       </c>
       <c r="D60" s="24" t="n">
-        <v>88.315</v>
+        <v>88.34</v>
       </c>
       <c r="E60" s="23" t="inlineStr"/>
       <c r="F60" s="22" t="inlineStr">
@@ -7863,7 +7863,7 @@
         <v>11.4611</v>
       </c>
       <c r="L60" s="25" t="n">
-        <v>528.6</v>
+        <v>528.8</v>
       </c>
       <c r="M60" s="25" t="n">
         <v>25</v>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="D61" s="24" t="n">
-        <v>146.86</v>
+        <v>147.64</v>
       </c>
       <c r="E61" s="23" t="inlineStr"/>
       <c r="F61" s="22" t="inlineStr">
@@ -7985,7 +7985,7 @@
         <v>13.4653</v>
       </c>
       <c r="L61" s="25" t="n">
-        <v>626.2</v>
+        <v>630.1</v>
       </c>
       <c r="M61" s="25" t="n">
         <v>25</v>
@@ -8571,7 +8571,7 @@
         </is>
       </c>
       <c r="D66" s="24" t="n">
-        <v>360.75</v>
+        <v>364.31</v>
       </c>
       <c r="E66" s="23" t="inlineStr"/>
       <c r="F66" s="22" t="inlineStr">
@@ -8595,7 +8595,7 @@
         <v>4.6574</v>
       </c>
       <c r="L66" s="25" t="n">
-        <v>7865.7</v>
+        <v>7944.3</v>
       </c>
       <c r="M66" s="25" t="n">
         <v>25</v>
@@ -9053,7 +9053,7 @@
         </is>
       </c>
       <c r="D70" s="29" t="n">
-        <v>131.955</v>
+        <v>126.455</v>
       </c>
       <c r="E70" s="28" t="inlineStr"/>
       <c r="F70" s="27" t="inlineStr">
@@ -12238,10 +12238,10 @@
         </is>
       </c>
       <c r="C52" s="34" t="n">
-        <v>330.16</v>
+        <v>333.72</v>
       </c>
       <c r="D52" s="34" t="n">
-        <v>49.1606</v>
+        <v>49.1605</v>
       </c>
       <c r="E52" s="34" t="n">
         <v>9.446</v>
@@ -12252,10 +12252,10 @@
       <c r="G52" s="34" t="inlineStr"/>
       <c r="H52" s="34" t="inlineStr"/>
       <c r="I52" s="34" t="n">
-        <v>8.899900000000001</v>
+        <v>8.8996</v>
       </c>
       <c r="J52" s="34" t="n">
-        <v>12.4165</v>
+        <v>12.4164</v>
       </c>
       <c r="K52" s="34" t="n">
         <v>494.7644</v>
@@ -12293,7 +12293,7 @@
         </is>
       </c>
       <c r="C53" s="34" t="n">
-        <v>249.04</v>
+        <v>247.96</v>
       </c>
       <c r="D53" s="34" t="n">
         <v>107.0856</v>
@@ -12344,7 +12344,7 @@
         </is>
       </c>
       <c r="C54" s="34" t="n">
-        <v>515.035</v>
+        <v>520.47</v>
       </c>
       <c r="D54" s="34" t="n">
         <v>1600617.8442</v>
@@ -12364,7 +12364,7 @@
       </c>
       <c r="L54" s="34" t="inlineStr"/>
       <c r="M54" s="34" t="n">
-        <v>7.33</v>
+        <v>7.34</v>
       </c>
       <c r="N54" s="34" t="n">
         <v>8.800000000000001</v>
@@ -12395,10 +12395,10 @@
         </is>
       </c>
       <c r="C55" s="34" t="n">
-        <v>275.895</v>
+        <v>280.01</v>
       </c>
       <c r="D55" s="34" t="n">
-        <v>26.967</v>
+        <v>26.9669</v>
       </c>
       <c r="E55" s="34" t="n">
         <v>7.0983</v>
@@ -12409,7 +12409,7 @@
       <c r="G55" s="34" t="inlineStr"/>
       <c r="H55" s="34" t="inlineStr"/>
       <c r="I55" s="34" t="n">
-        <v>0.7776999999999999</v>
+        <v>0.7776</v>
       </c>
       <c r="J55" s="34" t="n">
         <v>1.7995</v>
@@ -12450,10 +12450,10 @@
         </is>
       </c>
       <c r="C56" s="34" t="n">
-        <v>170.905</v>
+        <v>172.795</v>
       </c>
       <c r="D56" s="34" t="n">
-        <v>21.4774</v>
+        <v>21.4773</v>
       </c>
       <c r="E56" s="34" t="n">
         <v>3.6112</v>
@@ -12464,7 +12464,7 @@
       <c r="G56" s="34" t="inlineStr"/>
       <c r="H56" s="34" t="inlineStr"/>
       <c r="I56" s="34" t="n">
-        <v>5.0403</v>
+        <v>5.0402</v>
       </c>
       <c r="J56" s="34" t="inlineStr"/>
       <c r="K56" s="34" t="n">
@@ -12503,7 +12503,7 @@
         </is>
       </c>
       <c r="C57" s="34" t="n">
-        <v>344.15</v>
+        <v>346.815</v>
       </c>
       <c r="D57" s="34" t="n">
         <v>62.856</v>
@@ -12560,10 +12560,10 @@
         </is>
       </c>
       <c r="C58" s="34" t="n">
-        <v>264.28</v>
+        <v>267.14</v>
       </c>
       <c r="D58" s="34" t="n">
-        <v>480.8095</v>
+        <v>480.8071</v>
       </c>
       <c r="E58" s="34" t="n">
         <v>9.3416</v>
@@ -12574,10 +12574,10 @@
       <c r="G58" s="34" t="inlineStr"/>
       <c r="H58" s="34" t="inlineStr"/>
       <c r="I58" s="34" t="n">
-        <v>15.4644</v>
+        <v>15.4569</v>
       </c>
       <c r="J58" s="34" t="n">
-        <v>17.7693</v>
+        <v>17.7687</v>
       </c>
       <c r="K58" s="34" t="n">
         <v>6466.5299</v>
@@ -12615,7 +12615,7 @@
         </is>
       </c>
       <c r="C59" s="34" t="n">
-        <v>88.315</v>
+        <v>88.34</v>
       </c>
       <c r="D59" s="34" t="n">
         <v>14.0496</v>
@@ -12668,10 +12668,10 @@
         </is>
       </c>
       <c r="C60" s="34" t="n">
-        <v>1141.305</v>
+        <v>1143.525</v>
       </c>
       <c r="D60" s="34" t="n">
-        <v>544.7405</v>
+        <v>544.7394</v>
       </c>
       <c r="E60" s="34" t="n">
         <v>83.318</v>
@@ -12682,10 +12682,10 @@
       <c r="G60" s="34" t="inlineStr"/>
       <c r="H60" s="34" t="inlineStr"/>
       <c r="I60" s="34" t="n">
-        <v>15.5395</v>
+        <v>15.5361</v>
       </c>
       <c r="J60" s="34" t="n">
-        <v>58.8492</v>
+        <v>58.849</v>
       </c>
       <c r="K60" s="34" t="n">
         <v>6600.4801</v>
@@ -12723,7 +12723,7 @@
         </is>
       </c>
       <c r="C61" s="34" t="n">
-        <v>500.25</v>
+        <v>494.77</v>
       </c>
       <c r="D61" s="34" t="n">
         <v>81.6729</v>
@@ -12737,7 +12737,7 @@
       <c r="G61" s="34" t="inlineStr"/>
       <c r="H61" s="34" t="inlineStr"/>
       <c r="I61" s="34" t="n">
-        <v>3.4476</v>
+        <v>3.4477</v>
       </c>
       <c r="J61" s="34" t="n">
         <v>3.3891</v>
@@ -12778,7 +12778,7 @@
         </is>
       </c>
       <c r="C62" s="34" t="n">
-        <v>131.955</v>
+        <v>126.455</v>
       </c>
       <c r="D62" s="34" t="n">
         <v>21296.5965</v>
@@ -12794,7 +12794,7 @@
       </c>
       <c r="L62" s="34" t="inlineStr"/>
       <c r="M62" s="34" t="n">
-        <v>9.4</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="N62" s="34" t="n">
         <v>10.15</v>
@@ -12825,10 +12825,10 @@
         </is>
       </c>
       <c r="C63" s="34" t="n">
-        <v>211.864</v>
+        <v>216.05</v>
       </c>
       <c r="D63" s="34" t="n">
-        <v>45.7475</v>
+        <v>45.7474</v>
       </c>
       <c r="E63" s="34" t="n">
         <v>8.797599999999999</v>
@@ -12841,7 +12841,7 @@
       </c>
       <c r="H63" s="34" t="inlineStr"/>
       <c r="I63" s="34" t="n">
-        <v>6.8367</v>
+        <v>6.8365</v>
       </c>
       <c r="J63" s="34" t="n">
         <v>15.1803</v>
@@ -12882,7 +12882,7 @@
         </is>
       </c>
       <c r="C64" s="34" t="n">
-        <v>146.86</v>
+        <v>147.64</v>
       </c>
       <c r="D64" s="34" t="n">
         <v>20.2227</v>
@@ -12937,7 +12937,7 @@
         </is>
       </c>
       <c r="C65" s="34" t="n">
-        <v>34.325</v>
+        <v>34.255</v>
       </c>
       <c r="D65" s="34" t="n">
         <v>4.3617</v>
@@ -12992,7 +12992,7 @@
         </is>
       </c>
       <c r="C66" s="34" t="n">
-        <v>360.75</v>
+        <v>364.31</v>
       </c>
       <c r="D66" s="34" t="n">
         <v>4.5288</v>
@@ -13049,10 +13049,10 @@
         </is>
       </c>
       <c r="C67" s="34" t="n">
-        <v>413.19</v>
+        <v>418.52</v>
       </c>
       <c r="D67" s="34" t="n">
-        <v>6265.3259</v>
+        <v>6265.3212</v>
       </c>
       <c r="E67" s="34" t="n">
         <v>1397.4929</v>
@@ -13065,10 +13065,10 @@
       </c>
       <c r="H67" s="34" t="inlineStr"/>
       <c r="I67" s="34" t="n">
-        <v>539.357</v>
+        <v>539.3388</v>
       </c>
       <c r="J67" s="34" t="n">
-        <v>905.7941</v>
+        <v>905.7919000000001</v>
       </c>
       <c r="K67" s="34" t="n">
         <v>70736.5186</v>
@@ -13106,10 +13106,10 @@
         </is>
       </c>
       <c r="C68" s="34" t="n">
-        <v>376.82</v>
+        <v>378.87</v>
       </c>
       <c r="D68" s="34" t="n">
-        <v>369.4246</v>
+        <v>369.4242</v>
       </c>
       <c r="E68" s="34" t="n">
         <v>64.4277</v>
@@ -13120,7 +13120,7 @@
       <c r="G68" s="34" t="inlineStr"/>
       <c r="H68" s="34" t="inlineStr"/>
       <c r="I68" s="34" t="n">
-        <v>4.9385</v>
+        <v>4.9376</v>
       </c>
       <c r="J68" s="34" t="inlineStr"/>
       <c r="K68" s="34" t="n">
@@ -13128,7 +13128,7 @@
       </c>
       <c r="L68" s="34" t="inlineStr"/>
       <c r="M68" s="34" t="n">
-        <v>8.66</v>
+        <v>8.67</v>
       </c>
       <c r="N68" s="34" t="n">
         <v>8.800000000000001</v>
@@ -13159,7 +13159,7 @@
         </is>
       </c>
       <c r="C69" s="34" t="n">
-        <v>374.57</v>
+        <v>372.25</v>
       </c>
       <c r="D69" s="34" t="n">
         <v>54.2596</v>
@@ -13214,7 +13214,7 @@
         </is>
       </c>
       <c r="C70" s="34" t="n">
-        <v>108.54</v>
+        <v>108.39</v>
       </c>
       <c r="D70" s="34" t="n">
         <v>11.8315</v>
@@ -15646,7 +15646,7 @@
         </is>
       </c>
       <c r="C52" s="24" t="n">
-        <v>330.16</v>
+        <v>333.72</v>
       </c>
       <c r="D52" s="22" t="inlineStr">
         <is>
@@ -15657,16 +15657,16 @@
         <v>24.5803</v>
       </c>
       <c r="F52" s="24" t="n">
-        <v>36.8705</v>
+        <v>36.8704</v>
       </c>
       <c r="G52" s="24" t="n">
-        <v>56.5347</v>
+        <v>56.5346</v>
       </c>
       <c r="H52" s="24" t="n">
-        <v>73.741</v>
+        <v>73.74079999999999</v>
       </c>
       <c r="I52" s="24" t="n">
-        <v>73.741</v>
+        <v>73.74079999999999</v>
       </c>
       <c r="J52" s="26" t="inlineStr">
         <is>
@@ -15674,10 +15674,10 @@
         </is>
       </c>
       <c r="K52" s="24" t="n">
-        <v>6.7159</v>
+        <v>6.7884</v>
       </c>
       <c r="L52" s="24" t="n">
-        <v>36.8705</v>
+        <v>36.8704</v>
       </c>
     </row>
     <row r="53">
@@ -15692,7 +15692,7 @@
         </is>
       </c>
       <c r="C53" s="24" t="n">
-        <v>249.04</v>
+        <v>247.96</v>
       </c>
       <c r="D53" s="22" t="inlineStr">
         <is>
@@ -15720,7 +15720,7 @@
         </is>
       </c>
       <c r="K53" s="24" t="n">
-        <v>2.3256</v>
+        <v>2.3155</v>
       </c>
       <c r="L53" s="24" t="n">
         <v>80.3142</v>
@@ -15738,7 +15738,7 @@
         </is>
       </c>
       <c r="C54" s="4" t="n">
-        <v>515.035</v>
+        <v>520.47</v>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
@@ -15784,7 +15784,7 @@
         </is>
       </c>
       <c r="C55" s="24" t="n">
-        <v>275.895</v>
+        <v>280.01</v>
       </c>
       <c r="D55" s="22" t="inlineStr">
         <is>
@@ -15812,7 +15812,7 @@
         </is>
       </c>
       <c r="K55" s="24" t="n">
-        <v>10.2309</v>
+        <v>10.3835</v>
       </c>
       <c r="L55" s="24" t="n">
         <v>20.2252</v>
@@ -15830,7 +15830,7 @@
         </is>
       </c>
       <c r="C56" s="24" t="n">
-        <v>170.905</v>
+        <v>172.795</v>
       </c>
       <c r="D56" s="22" t="inlineStr">
         <is>
@@ -15844,7 +15844,7 @@
         <v>16.108</v>
       </c>
       <c r="G56" s="24" t="n">
-        <v>24.699</v>
+        <v>24.6989</v>
       </c>
       <c r="H56" s="24" t="n">
         <v>32.216</v>
@@ -15858,7 +15858,7 @@
         </is>
       </c>
       <c r="K56" s="24" t="n">
-        <v>7.9575</v>
+        <v>8.045500000000001</v>
       </c>
       <c r="L56" s="24" t="n">
         <v>16.108</v>
@@ -15876,7 +15876,7 @@
         </is>
       </c>
       <c r="C57" s="24" t="n">
-        <v>344.15</v>
+        <v>346.815</v>
       </c>
       <c r="D57" s="22" t="inlineStr">
         <is>
@@ -15904,7 +15904,7 @@
         </is>
       </c>
       <c r="K57" s="24" t="n">
-        <v>5.4752</v>
+        <v>5.5176</v>
       </c>
       <c r="L57" s="24" t="n">
         <v>47.142</v>
@@ -15922,7 +15922,7 @@
         </is>
       </c>
       <c r="C58" s="9" t="n">
-        <v>264.28</v>
+        <v>267.14</v>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
@@ -15930,19 +15930,19 @@
         </is>
       </c>
       <c r="E58" s="9" t="n">
-        <v>240.4047</v>
+        <v>240.4035</v>
       </c>
       <c r="F58" s="9" t="n">
-        <v>360.6071</v>
+        <v>360.6053</v>
       </c>
       <c r="G58" s="9" t="n">
-        <v>552.9309</v>
+        <v>552.9281999999999</v>
       </c>
       <c r="H58" s="9" t="n">
-        <v>721.2142</v>
+        <v>721.2106</v>
       </c>
       <c r="I58" s="9" t="n">
-        <v>721.2142</v>
+        <v>721.2106</v>
       </c>
       <c r="J58" s="11" t="inlineStr">
         <is>
@@ -15950,10 +15950,10 @@
         </is>
       </c>
       <c r="K58" s="9" t="n">
-        <v>0.5497</v>
+        <v>0.5556</v>
       </c>
       <c r="L58" s="9" t="n">
-        <v>360.6071</v>
+        <v>360.6053</v>
       </c>
     </row>
     <row r="59">
@@ -15968,7 +15968,7 @@
         </is>
       </c>
       <c r="C59" s="24" t="n">
-        <v>88.315</v>
+        <v>88.34</v>
       </c>
       <c r="D59" s="22" t="inlineStr">
         <is>
@@ -15996,7 +15996,7 @@
         </is>
       </c>
       <c r="K59" s="24" t="n">
-        <v>6.2859</v>
+        <v>6.2877</v>
       </c>
       <c r="L59" s="24" t="n">
         <v>10.5372</v>
@@ -16014,7 +16014,7 @@
         </is>
       </c>
       <c r="C60" s="24" t="n">
-        <v>1141.305</v>
+        <v>1143.525</v>
       </c>
       <c r="D60" s="22" t="inlineStr">
         <is>
@@ -16022,19 +16022,19 @@
         </is>
       </c>
       <c r="E60" s="24" t="n">
-        <v>272.3702</v>
+        <v>272.3697</v>
       </c>
       <c r="F60" s="24" t="n">
-        <v>408.5553</v>
+        <v>408.5545</v>
       </c>
       <c r="G60" s="24" t="n">
-        <v>626.4515</v>
+        <v>626.4503</v>
       </c>
       <c r="H60" s="24" t="n">
-        <v>817.1107</v>
+        <v>817.1091</v>
       </c>
       <c r="I60" s="24" t="n">
-        <v>817.1107</v>
+        <v>817.1091</v>
       </c>
       <c r="J60" s="26" t="inlineStr">
         <is>
@@ -16042,10 +16042,10 @@
         </is>
       </c>
       <c r="K60" s="24" t="n">
-        <v>2.0951</v>
+        <v>2.0992</v>
       </c>
       <c r="L60" s="24" t="n">
-        <v>408.5553</v>
+        <v>408.5545</v>
       </c>
     </row>
     <row r="61">
@@ -16060,7 +16060,7 @@
         </is>
       </c>
       <c r="C61" s="24" t="n">
-        <v>500.25</v>
+        <v>494.77</v>
       </c>
       <c r="D61" s="22" t="inlineStr">
         <is>
@@ -16074,7 +16074,7 @@
         <v>61.2547</v>
       </c>
       <c r="G61" s="24" t="n">
-        <v>93.9238</v>
+        <v>93.9239</v>
       </c>
       <c r="H61" s="24" t="n">
         <v>122.5094</v>
@@ -16088,7 +16088,7 @@
         </is>
       </c>
       <c r="K61" s="24" t="n">
-        <v>6.125</v>
+        <v>6.0579</v>
       </c>
       <c r="L61" s="24" t="n">
         <v>61.2547</v>
@@ -16106,7 +16106,7 @@
         </is>
       </c>
       <c r="C62" s="29" t="n">
-        <v>131.955</v>
+        <v>126.455</v>
       </c>
       <c r="D62" s="27" t="inlineStr">
         <is>
@@ -16134,7 +16134,7 @@
         </is>
       </c>
       <c r="K62" s="29" t="n">
-        <v>0.0062</v>
+        <v>0.0059</v>
       </c>
       <c r="L62" s="29" t="n">
         <v>15972.4474</v>
@@ -16152,7 +16152,7 @@
         </is>
       </c>
       <c r="C63" s="24" t="n">
-        <v>211.864</v>
+        <v>216.05</v>
       </c>
       <c r="D63" s="22" t="inlineStr">
         <is>
@@ -16166,13 +16166,13 @@
         <v>34.3106</v>
       </c>
       <c r="G63" s="24" t="n">
-        <v>52.6096</v>
+        <v>52.6095</v>
       </c>
       <c r="H63" s="24" t="n">
-        <v>68.6212</v>
+        <v>68.6211</v>
       </c>
       <c r="I63" s="24" t="n">
-        <v>68.6212</v>
+        <v>68.6211</v>
       </c>
       <c r="J63" s="26" t="inlineStr">
         <is>
@@ -16180,7 +16180,7 @@
         </is>
       </c>
       <c r="K63" s="24" t="n">
-        <v>4.6312</v>
+        <v>4.7227</v>
       </c>
       <c r="L63" s="24" t="n">
         <v>34.3106</v>
@@ -16198,7 +16198,7 @@
         </is>
       </c>
       <c r="C64" s="24" t="n">
-        <v>146.86</v>
+        <v>147.64</v>
       </c>
       <c r="D64" s="22" t="inlineStr">
         <is>
@@ -16226,7 +16226,7 @@
         </is>
       </c>
       <c r="K64" s="24" t="n">
-        <v>7.2621</v>
+        <v>7.3007</v>
       </c>
       <c r="L64" s="24" t="n">
         <v>15.167</v>
@@ -16244,7 +16244,7 @@
         </is>
       </c>
       <c r="C65" s="24" t="n">
-        <v>34.325</v>
+        <v>34.255</v>
       </c>
       <c r="D65" s="22" t="inlineStr">
         <is>
@@ -16272,7 +16272,7 @@
         </is>
       </c>
       <c r="K65" s="24" t="n">
-        <v>7.8697</v>
+        <v>7.8536</v>
       </c>
       <c r="L65" s="24" t="n">
         <v>3.2713</v>
@@ -16290,7 +16290,7 @@
         </is>
       </c>
       <c r="C66" s="24" t="n">
-        <v>360.75</v>
+        <v>364.31</v>
       </c>
       <c r="D66" s="22" t="inlineStr">
         <is>
@@ -16318,7 +16318,7 @@
         </is>
       </c>
       <c r="K66" s="24" t="n">
-        <v>79.6571</v>
+        <v>80.4432</v>
       </c>
       <c r="L66" s="24" t="n">
         <v>3.3966</v>
@@ -16336,7 +16336,7 @@
         </is>
       </c>
       <c r="C67" s="4" t="n">
-        <v>413.19</v>
+        <v>418.52</v>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
@@ -16344,19 +16344,19 @@
         </is>
       </c>
       <c r="E67" s="4" t="n">
-        <v>3132.663</v>
+        <v>3132.6606</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>4698.9944</v>
+        <v>4698.9909</v>
       </c>
       <c r="G67" s="4" t="n">
-        <v>7205.1248</v>
+        <v>7205.1193</v>
       </c>
       <c r="H67" s="4" t="n">
-        <v>9397.9889</v>
+        <v>9397.9817</v>
       </c>
       <c r="I67" s="4" t="n">
-        <v>9397.9889</v>
+        <v>9397.9817</v>
       </c>
       <c r="J67" s="6" t="inlineStr">
         <is>
@@ -16364,10 +16364,10 @@
         </is>
       </c>
       <c r="K67" s="4" t="n">
-        <v>0.0659</v>
+        <v>0.0668</v>
       </c>
       <c r="L67" s="4" t="n">
-        <v>4698.9944</v>
+        <v>4698.9909</v>
       </c>
     </row>
     <row r="68">
@@ -16382,7 +16382,7 @@
         </is>
       </c>
       <c r="C68" s="14" t="n">
-        <v>376.82</v>
+        <v>378.87</v>
       </c>
       <c r="D68" s="12" t="inlineStr">
         <is>
@@ -16390,19 +16390,19 @@
         </is>
       </c>
       <c r="E68" s="14" t="n">
-        <v>184.7123</v>
+        <v>184.7121</v>
       </c>
       <c r="F68" s="14" t="n">
-        <v>277.0685</v>
+        <v>277.0682</v>
       </c>
       <c r="G68" s="14" t="n">
-        <v>424.8383</v>
+        <v>424.8379</v>
       </c>
       <c r="H68" s="14" t="n">
-        <v>554.1369999999999</v>
+        <v>554.1364</v>
       </c>
       <c r="I68" s="14" t="n">
-        <v>554.1369999999999</v>
+        <v>554.1364</v>
       </c>
       <c r="J68" s="16" t="inlineStr">
         <is>
@@ -16410,10 +16410,10 @@
         </is>
       </c>
       <c r="K68" s="14" t="n">
-        <v>1.02</v>
+        <v>1.0256</v>
       </c>
       <c r="L68" s="14" t="n">
-        <v>277.0685</v>
+        <v>277.0682</v>
       </c>
     </row>
     <row r="69">
@@ -16428,7 +16428,7 @@
         </is>
       </c>
       <c r="C69" s="24" t="n">
-        <v>374.57</v>
+        <v>372.25</v>
       </c>
       <c r="D69" s="22" t="inlineStr">
         <is>
@@ -16442,7 +16442,7 @@
         <v>40.6947</v>
       </c>
       <c r="G69" s="24" t="n">
-        <v>62.3985</v>
+        <v>62.3986</v>
       </c>
       <c r="H69" s="24" t="n">
         <v>81.38939999999999</v>
@@ -16456,7 +16456,7 @@
         </is>
       </c>
       <c r="K69" s="24" t="n">
-        <v>6.9033</v>
+        <v>6.8605</v>
       </c>
       <c r="L69" s="24" t="n">
         <v>40.6947</v>
@@ -16474,7 +16474,7 @@
         </is>
       </c>
       <c r="C70" s="24" t="n">
-        <v>108.54</v>
+        <v>108.39</v>
       </c>
       <c r="D70" s="22" t="inlineStr">
         <is>
@@ -16502,7 +16502,7 @@
         </is>
       </c>
       <c r="K70" s="24" t="n">
-        <v>9.1738</v>
+        <v>9.161099999999999</v>
       </c>
       <c r="L70" s="24" t="n">
         <v>8.873699999999999</v>
@@ -21461,7 +21461,7 @@
         </is>
       </c>
       <c r="C52" s="34" t="n">
-        <v>330.16</v>
+        <v>333.72</v>
       </c>
       <c r="D52" s="32" t="n">
         <v>152198000000</v>
@@ -21547,7 +21547,7 @@
         </is>
       </c>
       <c r="C53" s="34" t="n">
-        <v>249.04</v>
+        <v>247.96</v>
       </c>
       <c r="D53" s="32" t="n">
         <v>90623000000</v>
@@ -21635,7 +21635,7 @@
         </is>
       </c>
       <c r="C54" s="34" t="n">
-        <v>515.035</v>
+        <v>520.47</v>
       </c>
       <c r="D54" s="32" t="inlineStr"/>
       <c r="E54" s="32" t="n">
@@ -21707,7 +21707,7 @@
         </is>
       </c>
       <c r="C55" s="34" t="n">
-        <v>275.895</v>
+        <v>280.01</v>
       </c>
       <c r="D55" s="32" t="n">
         <v>1749124000</v>
@@ -21793,7 +21793,7 @@
         </is>
       </c>
       <c r="C56" s="34" t="n">
-        <v>170.905</v>
+        <v>172.795</v>
       </c>
       <c r="D56" s="32" t="n">
         <v>2322900000</v>
@@ -21879,7 +21879,7 @@
         </is>
       </c>
       <c r="C57" s="34" t="n">
-        <v>344.15</v>
+        <v>346.815</v>
       </c>
       <c r="D57" s="32" t="n">
         <v>137196000000</v>
@@ -21967,7 +21967,7 @@
         </is>
       </c>
       <c r="C58" s="34" t="n">
-        <v>264.28</v>
+        <v>267.14</v>
       </c>
       <c r="D58" s="32" t="n">
         <v>31538000000</v>
@@ -22051,7 +22051,7 @@
         </is>
       </c>
       <c r="C59" s="34" t="n">
-        <v>88.315</v>
+        <v>88.34</v>
       </c>
       <c r="D59" s="32" t="n">
         <v>13046000000</v>
@@ -22139,7 +22139,7 @@
         </is>
       </c>
       <c r="C60" s="34" t="n">
-        <v>1141.305</v>
+        <v>1143.525</v>
       </c>
       <c r="D60" s="32" t="n">
         <v>26708000000</v>
@@ -22225,7 +22225,7 @@
         </is>
       </c>
       <c r="C61" s="34" t="n">
-        <v>500.25</v>
+        <v>494.77</v>
       </c>
       <c r="D61" s="32" t="n">
         <v>90007000000</v>
@@ -22311,7 +22311,7 @@
         </is>
       </c>
       <c r="C62" s="34" t="n">
-        <v>131.955</v>
+        <v>126.455</v>
       </c>
       <c r="D62" s="32" t="n">
         <v>130869000</v>
@@ -22397,7 +22397,7 @@
         </is>
       </c>
       <c r="C63" s="34" t="n">
-        <v>211.864</v>
+        <v>216.05</v>
       </c>
       <c r="D63" s="32" t="n">
         <v>160482000000</v>
@@ -22485,7 +22485,7 @@
         </is>
       </c>
       <c r="C64" s="34" t="n">
-        <v>146.86</v>
+        <v>147.64</v>
       </c>
       <c r="D64" s="32" t="n">
         <v>21203000000</v>
@@ -22571,7 +22571,7 @@
         </is>
       </c>
       <c r="C65" s="34" t="n">
-        <v>34.325</v>
+        <v>34.255</v>
       </c>
       <c r="D65" s="32" t="n">
         <v>991962000</v>
@@ -22659,7 +22659,7 @@
         </is>
       </c>
       <c r="C66" s="34" t="n">
-        <v>360.75</v>
+        <v>364.31</v>
       </c>
       <c r="D66" s="32" t="n">
         <v>30641000000</v>
@@ -22747,7 +22747,7 @@
         </is>
       </c>
       <c r="C67" s="34" t="n">
-        <v>413.19</v>
+        <v>418.52</v>
       </c>
       <c r="D67" s="32" t="n">
         <v>1382678381000</v>
@@ -22835,7 +22835,7 @@
         </is>
       </c>
       <c r="C68" s="34" t="n">
-        <v>376.82</v>
+        <v>378.87</v>
       </c>
       <c r="D68" s="32" t="n">
         <v>113631000000</v>
@@ -22921,7 +22921,7 @@
         </is>
       </c>
       <c r="C69" s="34" t="n">
-        <v>374.57</v>
+        <v>372.25</v>
       </c>
       <c r="D69" s="32" t="n">
         <v>12362000000</v>
@@ -23007,7 +23007,7 @@
         </is>
       </c>
       <c r="C70" s="34" t="n">
-        <v>108.54</v>
+        <v>108.39</v>
       </c>
       <c r="D70" s="32" t="n">
         <v>201191000000</v>
@@ -26240,7 +26240,7 @@
         </is>
       </c>
       <c r="C52" s="24" t="n">
-        <v>330.16</v>
+        <v>333.72</v>
       </c>
       <c r="D52" s="22" t="n">
         <v>3</v>
@@ -26301,7 +26301,7 @@
         </is>
       </c>
       <c r="C53" s="24" t="n">
-        <v>249.04</v>
+        <v>247.96</v>
       </c>
       <c r="D53" s="22" t="n">
         <v>2.3</v>
@@ -26362,7 +26362,7 @@
         </is>
       </c>
       <c r="C54" s="4" t="n">
-        <v>515.035</v>
+        <v>520.47</v>
       </c>
       <c r="D54" s="2" t="n">
         <v>5.5</v>
@@ -26423,7 +26423,7 @@
         </is>
       </c>
       <c r="C55" s="24" t="n">
-        <v>275.895</v>
+        <v>280.01</v>
       </c>
       <c r="D55" s="22" t="n">
         <v>2</v>
@@ -26484,7 +26484,7 @@
         </is>
       </c>
       <c r="C56" s="24" t="n">
-        <v>170.905</v>
+        <v>172.795</v>
       </c>
       <c r="D56" s="22" t="n">
         <v>3</v>
@@ -26545,7 +26545,7 @@
         </is>
       </c>
       <c r="C57" s="24" t="n">
-        <v>344.15</v>
+        <v>346.815</v>
       </c>
       <c r="D57" s="22" t="n">
         <v>2.3</v>
@@ -26606,7 +26606,7 @@
         </is>
       </c>
       <c r="C58" s="9" t="n">
-        <v>264.28</v>
+        <v>267.14</v>
       </c>
       <c r="D58" s="7" t="n">
         <v>3.5</v>
@@ -26667,7 +26667,7 @@
         </is>
       </c>
       <c r="C59" s="24" t="n">
-        <v>88.315</v>
+        <v>88.34</v>
       </c>
       <c r="D59" s="22" t="n">
         <v>2</v>
@@ -26728,7 +26728,7 @@
         </is>
       </c>
       <c r="C60" s="24" t="n">
-        <v>1141.305</v>
+        <v>1143.525</v>
       </c>
       <c r="D60" s="22" t="n">
         <v>2.5</v>
@@ -26789,7 +26789,7 @@
         </is>
       </c>
       <c r="C61" s="24" t="n">
-        <v>500.25</v>
+        <v>494.77</v>
       </c>
       <c r="D61" s="22" t="n">
         <v>2.8</v>
@@ -26850,7 +26850,7 @@
         </is>
       </c>
       <c r="C62" s="29" t="n">
-        <v>131.955</v>
+        <v>126.455</v>
       </c>
       <c r="D62" s="27" t="n">
         <v>1</v>
@@ -26911,7 +26911,7 @@
         </is>
       </c>
       <c r="C63" s="24" t="n">
-        <v>211.864</v>
+        <v>216.05</v>
       </c>
       <c r="D63" s="22" t="n">
         <v>3.5</v>
@@ -26972,7 +26972,7 @@
         </is>
       </c>
       <c r="C64" s="24" t="n">
-        <v>146.86</v>
+        <v>147.64</v>
       </c>
       <c r="D64" s="22" t="n">
         <v>2</v>
@@ -27033,7 +27033,7 @@
         </is>
       </c>
       <c r="C65" s="24" t="n">
-        <v>34.325</v>
+        <v>34.255</v>
       </c>
       <c r="D65" s="22" t="n">
         <v>2.3</v>
@@ -27094,7 +27094,7 @@
         </is>
       </c>
       <c r="C66" s="24" t="n">
-        <v>360.75</v>
+        <v>364.31</v>
       </c>
       <c r="D66" s="22" t="n">
         <v>1.2</v>
@@ -27155,7 +27155,7 @@
         </is>
       </c>
       <c r="C67" s="4" t="n">
-        <v>413.19</v>
+        <v>418.52</v>
       </c>
       <c r="D67" s="2" t="n">
         <v>7.5</v>
@@ -27216,7 +27216,7 @@
         </is>
       </c>
       <c r="C68" s="14" t="n">
-        <v>376.82</v>
+        <v>378.87</v>
       </c>
       <c r="D68" s="12" t="n">
         <v>2.5</v>
@@ -27277,7 +27277,7 @@
         </is>
       </c>
       <c r="C69" s="24" t="n">
-        <v>374.57</v>
+        <v>372.25</v>
       </c>
       <c r="D69" s="22" t="n">
         <v>2.5</v>
@@ -27338,7 +27338,7 @@
         </is>
       </c>
       <c r="C70" s="24" t="n">
-        <v>108.54</v>
+        <v>108.39</v>
       </c>
       <c r="D70" s="22" t="n">
         <v>2.2</v>
